--- a/input_processing/clean_excel_files_PL/reg_wages.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_wages.xlsx
@@ -97,16 +97,16 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Deh_c3_Medium</t>
+    <t>Deh_c4_Medium</t>
   </si>
   <si>
-    <t>Deh_c3_Low</t>
+    <t>Deh_c4_Low</t>
   </si>
   <si>
-    <t>Deh_c3_Medium_Dag</t>
+    <t>Deh_c4_Medium_Dag</t>
   </si>
   <si>
-    <t>Deh_c3_Low_Dag</t>
+    <t>Deh_c4_Low_Dag</t>
   </si>
   <si>
     <t>Dhe_Fair</t>
@@ -413,67 +413,67 @@
         <v>24</v>
       </c>
       <c r="B2" s="1">
-        <v>0.028221828099084537</v>
+        <v>0.028309785683914079</v>
       </c>
       <c r="C2" s="1">
-        <v>3.9396741039147485e-06</v>
+        <v>3.9237723992144306e-06</v>
       </c>
       <c r="D2" s="1">
-        <v>-4.3760528138607293e-08</v>
+        <v>-4.3578828011779575e-08</v>
       </c>
       <c r="E2" s="1">
-        <v>9.0172567293530358e-06</v>
+        <v>9.028763376195629e-06</v>
       </c>
       <c r="F2" s="1">
-        <v>5.7520151669549876e-06</v>
+        <v>6.0905256688416381e-06</v>
       </c>
       <c r="G2" s="1">
-        <v>-2.1038325735775862e-07</v>
+        <v>-2.1053151397809115e-07</v>
       </c>
       <c r="H2" s="1">
-        <v>-1.3192741494577839e-07</v>
+        <v>-1.3798096233381978e-07</v>
       </c>
       <c r="I2" s="1">
-        <v>3.7178418995536255e-07</v>
+        <v>3.4611761059732826e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>8.4317372271401765e-07</v>
+        <v>8.0560785472384637e-07</v>
       </c>
       <c r="K2" s="1">
-        <v>8.4767150119303543e-07</v>
+        <v>8.0501637712487228e-07</v>
       </c>
       <c r="L2" s="1">
-        <v>2.9566368279724079e-06</v>
+        <v>2.9146711988959332e-06</v>
       </c>
       <c r="M2" s="1">
-        <v>1.2068090182804621e-07</v>
+        <v>1.16862605197988e-07</v>
       </c>
       <c r="N2" s="1">
-        <v>3.3810341724291634e-07</v>
+        <v>3.3487589984349276e-07</v>
       </c>
       <c r="O2" s="1">
-        <v>-1.238364991441445e-07</v>
+        <v>-1.2680547077806725e-07</v>
       </c>
       <c r="P2" s="1">
-        <v>1.0215912513359728e-07</v>
+        <v>9.9288964455779719e-08</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.2868869503707406e-06</v>
+        <v>1.287307148851817e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>-3.0443273059907e-09</v>
+        <v>-2.9939101071275917e-09</v>
       </c>
       <c r="S2" s="1">
-        <v>-2.3621210190511055e-08</v>
+        <v>-2.363891108272477e-08</v>
       </c>
       <c r="T2" s="1">
-        <v>-3.1352851083403726e-08</v>
+        <v>-3.0197262695497932e-08</v>
       </c>
       <c r="U2" s="1">
-        <v>-8.5567216401620963e-05</v>
+        <v>-8.5183728788814278e-05</v>
       </c>
       <c r="V2" s="1">
-        <v>5.6012429124135965e-06</v>
+        <v>5.5128227794583851e-06</v>
       </c>
     </row>
     <row r="3">
@@ -481,67 +481,67 @@
         <v>25</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.00015206973770748617</v>
+        <v>-0.00015300908593136279</v>
       </c>
       <c r="C3" s="1">
-        <v>-4.3760528138607293e-08</v>
+        <v>-4.3578828011779575e-08</v>
       </c>
       <c r="D3" s="1">
-        <v>5.1147553653755985e-10</v>
+        <v>5.0940121716740847e-10</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.7409428068997644e-08</v>
+        <v>-1.7533033409082453e-08</v>
       </c>
       <c r="F3" s="1">
-        <v>2.147288220377858e-08</v>
+        <v>1.7564077998267628e-08</v>
       </c>
       <c r="G3" s="1">
-        <v>2.997519392597074e-10</v>
+        <v>3.0132495294207875e-10</v>
       </c>
       <c r="H3" s="1">
-        <v>-6.2279718514557152e-10</v>
+        <v>-5.5278575708977537e-10</v>
       </c>
       <c r="I3" s="1">
-        <v>-5.5333636605713003e-09</v>
+        <v>-5.2454748825419065e-09</v>
       </c>
       <c r="J3" s="1">
-        <v>-1.1059373311137032e-08</v>
+        <v>-1.0639772280442241e-08</v>
       </c>
       <c r="K3" s="1">
-        <v>-7.2260118268646708e-09</v>
+        <v>-6.7493646964925625e-09</v>
       </c>
       <c r="L3" s="1">
-        <v>-2.5332271651949638e-08</v>
+        <v>-2.4863785919431147e-08</v>
       </c>
       <c r="M3" s="1">
-        <v>-2.1767320020637379e-09</v>
+        <v>-2.1332918573891626e-09</v>
       </c>
       <c r="N3" s="1">
-        <v>-4.5538198974041156e-09</v>
+        <v>-4.5161858490145676e-09</v>
       </c>
       <c r="O3" s="1">
-        <v>5.3624008225968987e-10</v>
+        <v>5.7129912385489015e-10</v>
       </c>
       <c r="P3" s="1">
-        <v>-1.6669059656836359e-09</v>
+        <v>-1.6337578635212726e-09</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.6399631699118336e-08</v>
+        <v>-1.6400371512060319e-08</v>
       </c>
       <c r="R3" s="1">
-        <v>-8.6130814858915289e-11</v>
+        <v>-8.6702841544028043e-11</v>
       </c>
       <c r="S3" s="1">
-        <v>1.2166375867943272e-09</v>
+        <v>1.2178562837811263e-09</v>
       </c>
       <c r="T3" s="1">
-        <v>1.634277312334384e-09</v>
+        <v>1.6206790997093738e-09</v>
       </c>
       <c r="U3" s="1">
-        <v>9.1766039847488133e-07</v>
+        <v>9.132892687609324e-07</v>
       </c>
       <c r="V3" s="1">
-        <v>-6.5152717011151527e-08</v>
+        <v>-6.4169038791260092e-08</v>
       </c>
     </row>
     <row r="4">
@@ -549,67 +549,67 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.041294908189502808</v>
+        <v>-0.041128907743529876</v>
       </c>
       <c r="C4" s="1">
-        <v>9.0172567293530358e-06</v>
+        <v>9.028763376195629e-06</v>
       </c>
       <c r="D4" s="1">
-        <v>-1.7409428068997644e-08</v>
+        <v>-1.7533033409082453e-08</v>
       </c>
       <c r="E4" s="1">
-        <v>0.000544215307128995</v>
+        <v>0.00054424074571359784</v>
       </c>
       <c r="F4" s="1">
-        <v>0.00033319958150519876</v>
+        <v>0.00033275848633512517</v>
       </c>
       <c r="G4" s="1">
-        <v>-1.2204139413984582e-05</v>
+        <v>-1.2204539776436415e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>-7.6288888058531492e-06</v>
+        <v>-7.6206187886784339e-06</v>
       </c>
       <c r="I4" s="1">
-        <v>-2.2175897891599315e-06</v>
+        <v>-2.2164293673651512e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>-6.8193402183385812e-06</v>
+        <v>-6.8232648994416889e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>-1.1308006653404276e-05</v>
+        <v>-1.1312348782111197e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>-3.8417057068733326e-06</v>
+        <v>-3.8488221666790244e-06</v>
       </c>
       <c r="M4" s="1">
-        <v>-4.9458132332830786e-06</v>
+        <v>-4.9432377875146203e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>-5.627809411566338e-07</v>
+        <v>-5.5763979424963258e-07</v>
       </c>
       <c r="O4" s="1">
-        <v>-4.2670068545485246e-06</v>
+        <v>-4.2605520286257519e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>4.7886988730571146e-07</v>
+        <v>4.8229131232343832e-07</v>
       </c>
       <c r="Q4" s="1">
-        <v>-2.518342379120552e-06</v>
+        <v>-2.5036325589774707e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>2.4622778622312496e-08</v>
+        <v>2.4564294365875238e-08</v>
       </c>
       <c r="S4" s="1">
-        <v>9.7866890382210562e-07</v>
+        <v>9.8301343261619357e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>2.0194812079165307e-06</v>
+        <v>2.0181818010905961e-06</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.00034583742543704799</v>
+        <v>-0.00034608072263972434</v>
       </c>
       <c r="V4" s="1">
-        <v>-8.5420764099746514e-06</v>
+        <v>-8.566987502472459e-06</v>
       </c>
     </row>
     <row r="5">
@@ -617,67 +617,67 @@
         <v>27</v>
       </c>
       <c r="B5" s="1">
-        <v>0.017435209011866369</v>
+        <v>0.01159924281632343</v>
       </c>
       <c r="C5" s="1">
-        <v>5.7520151669549876e-06</v>
+        <v>6.0905256688416381e-06</v>
       </c>
       <c r="D5" s="1">
-        <v>2.147288220377858e-08</v>
+        <v>1.7564077998267628e-08</v>
       </c>
       <c r="E5" s="1">
-        <v>0.00033319958150519876</v>
+        <v>0.00033275848633512517</v>
       </c>
       <c r="F5" s="1">
-        <v>0.0026382816873429071</v>
+        <v>0.0026353888261588633</v>
       </c>
       <c r="G5" s="1">
-        <v>-7.6596972764233314e-06</v>
+        <v>-7.6544592772289036e-06</v>
       </c>
       <c r="H5" s="1">
-        <v>-5.4272261937435953e-05</v>
+        <v>-5.4228682113942461e-05</v>
       </c>
       <c r="I5" s="1">
-        <v>-3.5684821456607896e-06</v>
+        <v>-2.7188864844874607e-06</v>
       </c>
       <c r="J5" s="1">
-        <v>-2.0500662677194108e-05</v>
+        <v>-1.9156242341298512e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>-2.8369241015758091e-05</v>
+        <v>-2.6850904073026093e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-1.7153887471305845e-05</v>
+        <v>-1.5591615168566264e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-1.0608408797322664e-05</v>
+        <v>-1.0526075731655756e-05</v>
       </c>
       <c r="N5" s="1">
-        <v>-3.0484089197335197e-06</v>
+        <v>-3.0264986979324477e-06</v>
       </c>
       <c r="O5" s="1">
-        <v>-7.3288205622758489e-06</v>
+        <v>-7.3375088316040853e-06</v>
       </c>
       <c r="P5" s="1">
-        <v>1.1115588097028388e-06</v>
+        <v>1.1565056891193432e-06</v>
       </c>
       <c r="Q5" s="1">
-        <v>-4.1025626837536007e-06</v>
+        <v>-4.378204627246228e-06</v>
       </c>
       <c r="R5" s="1">
-        <v>-1.9307941966382042e-07</v>
+        <v>-1.9362334703498823e-07</v>
       </c>
       <c r="S5" s="1">
-        <v>3.6769049999317933e-06</v>
+        <v>3.5963462374070435e-06</v>
       </c>
       <c r="T5" s="1">
-        <v>3.893495457997588e-06</v>
+        <v>3.8742887382417414e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.00023444928571363967</v>
+        <v>-0.00024345962712371181</v>
       </c>
       <c r="V5" s="1">
-        <v>-3.9567854381959409e-05</v>
+        <v>-3.6195207130673895e-05</v>
       </c>
     </row>
     <row r="6">
@@ -685,67 +685,67 @@
         <v>28</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.009678801859081097</v>
+        <v>-0.0096806277354214952</v>
       </c>
       <c r="C6" s="1">
-        <v>-2.1038325735775862e-07</v>
+        <v>-2.1053151397809115e-07</v>
       </c>
       <c r="D6" s="1">
-        <v>2.997519392597074e-10</v>
+        <v>3.0132495294207875e-10</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.2204139413984582e-05</v>
+        <v>-1.2204539776436415e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>-7.6596972764233314e-06</v>
+        <v>-7.6544592772289036e-06</v>
       </c>
       <c r="G6" s="1">
-        <v>2.921385540575045e-07</v>
+        <v>2.9214532290853564e-07</v>
       </c>
       <c r="H6" s="1">
-        <v>1.879777349951724e-07</v>
+        <v>1.8788018328340001e-07</v>
       </c>
       <c r="I6" s="1">
-        <v>-1.1062600005415131e-08</v>
+        <v>-1.1093666234043094e-08</v>
       </c>
       <c r="J6" s="1">
-        <v>1.026255348100083e-07</v>
+        <v>1.0263658088267243e-07</v>
       </c>
       <c r="K6" s="1">
-        <v>2.7627120435826788e-07</v>
+        <v>2.7628861506977667e-07</v>
       </c>
       <c r="L6" s="1">
-        <v>1.6901529230731788e-07</v>
+        <v>1.6906306224689729e-07</v>
       </c>
       <c r="M6" s="1">
-        <v>9.0785319159750885e-08</v>
+        <v>9.0752817670935118e-08</v>
       </c>
       <c r="N6" s="1">
-        <v>3.0097087744728916e-08</v>
+        <v>3.0036427532905232e-08</v>
       </c>
       <c r="O6" s="1">
-        <v>9.496221407268425e-08</v>
+        <v>9.4884999134146079e-08</v>
       </c>
       <c r="P6" s="1">
-        <v>1.6068896802480572e-08</v>
+        <v>1.602880534718309e-08</v>
       </c>
       <c r="Q6" s="1">
-        <v>1.0719338819509999e-07</v>
+        <v>1.0701784013331081e-07</v>
       </c>
       <c r="R6" s="1">
-        <v>2.8366709537948588e-09</v>
+        <v>2.8370771038035591e-09</v>
       </c>
       <c r="S6" s="1">
-        <v>-4.0797229596750681e-08</v>
+        <v>-4.0839758380450006e-08</v>
       </c>
       <c r="T6" s="1">
-        <v>-7.0791792088767467e-08</v>
+        <v>-7.0765696585988268e-08</v>
       </c>
       <c r="U6" s="1">
-        <v>7.4215545530132213e-06</v>
+        <v>7.424831868113934e-06</v>
       </c>
       <c r="V6" s="1">
-        <v>1.0154755128875033e-07</v>
+        <v>1.0174066639595279e-07</v>
       </c>
     </row>
     <row r="7">
@@ -753,67 +753,67 @@
         <v>29</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.014441971420507035</v>
+        <v>-0.014330287118658771</v>
       </c>
       <c r="C7" s="1">
-        <v>-1.3192741494577839e-07</v>
+        <v>-1.3798096233381978e-07</v>
       </c>
       <c r="D7" s="1">
-        <v>-6.2279718514557152e-10</v>
+        <v>-5.5278575708977537e-10</v>
       </c>
       <c r="E7" s="1">
-        <v>-7.6288888058531492e-06</v>
+        <v>-7.6206187886784339e-06</v>
       </c>
       <c r="F7" s="1">
-        <v>-5.4272261937435953e-05</v>
+        <v>-5.4228682113942461e-05</v>
       </c>
       <c r="G7" s="1">
-        <v>1.879777349951724e-07</v>
+        <v>1.8788018328340001e-07</v>
       </c>
       <c r="H7" s="1">
-        <v>1.1980488068320602e-06</v>
+        <v>1.1974320157402654e-06</v>
       </c>
       <c r="I7" s="1">
-        <v>3.1132053673535869e-07</v>
+        <v>2.9558041678333351e-07</v>
       </c>
       <c r="J7" s="1">
-        <v>7.2764128826474765e-07</v>
+        <v>7.0261112570819056e-07</v>
       </c>
       <c r="K7" s="1">
-        <v>1.0654525598870258e-06</v>
+        <v>1.037206504602527e-06</v>
       </c>
       <c r="L7" s="1">
-        <v>8.9090832629188453e-07</v>
+        <v>8.617794977821371e-07</v>
       </c>
       <c r="M7" s="1">
-        <v>1.209816098187894e-07</v>
+        <v>1.1950946965182586e-07</v>
       </c>
       <c r="N7" s="1">
-        <v>6.9910388203098331e-08</v>
+        <v>6.9612947129353282e-08</v>
       </c>
       <c r="O7" s="1">
-        <v>5.4148529084220542e-08</v>
+        <v>5.4438002029274751e-08</v>
       </c>
       <c r="P7" s="1">
-        <v>-5.1197510418094307e-08</v>
+        <v>-5.1959851377683149e-08</v>
       </c>
       <c r="Q7" s="1">
-        <v>5.8920242813982746e-08</v>
+        <v>6.4352453029831595e-08</v>
       </c>
       <c r="R7" s="1">
-        <v>9.4525579509966195e-09</v>
+        <v>9.4607643486743451e-09</v>
       </c>
       <c r="S7" s="1">
-        <v>-1.0867347129254e-07</v>
+        <v>-1.0707289920860612e-07</v>
       </c>
       <c r="T7" s="1">
-        <v>-1.183944413746588e-07</v>
+        <v>-1.1804506730385767e-07</v>
       </c>
       <c r="U7" s="1">
-        <v>4.3230276470916549e-06</v>
+        <v>4.4856583430476527e-06</v>
       </c>
       <c r="V7" s="1">
-        <v>5.5314081060674364e-07</v>
+        <v>4.9007528536898502e-07</v>
       </c>
     </row>
     <row r="8">
@@ -821,67 +821,67 @@
         <v>30</v>
       </c>
       <c r="B8" s="1">
-        <v>0.12076688885564968</v>
+        <v>0.12060295047019046</v>
       </c>
       <c r="C8" s="1">
-        <v>3.7178418995536255e-07</v>
+        <v>3.4611761059732826e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.5333636605713003e-09</v>
+        <v>-5.2454748825419065e-09</v>
       </c>
       <c r="E8" s="1">
-        <v>-2.2175897891599315e-06</v>
+        <v>-2.2164293673651512e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>-3.5684821456607896e-06</v>
+        <v>-2.7188864844874607e-06</v>
       </c>
       <c r="G8" s="1">
-        <v>-1.1062600005415131e-08</v>
+        <v>-1.1093666234043094e-08</v>
       </c>
       <c r="H8" s="1">
-        <v>3.1132053673535869e-07</v>
+        <v>2.9558041678333351e-07</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0032679997939618565</v>
+        <v>0.0032676926543947046</v>
       </c>
       <c r="J8" s="1">
-        <v>0.0030276623820857246</v>
+        <v>0.0030273631625743194</v>
       </c>
       <c r="K8" s="1">
-        <v>0.0030281638913339836</v>
+        <v>0.0030278613362169447</v>
       </c>
       <c r="L8" s="1">
-        <v>0.0030272724129013287</v>
+        <v>0.0030269746709732058</v>
       </c>
       <c r="M8" s="1">
-        <v>7.6505132509809354e-07</v>
+        <v>7.5851667145174283e-07</v>
       </c>
       <c r="N8" s="1">
-        <v>-1.364876060161576e-06</v>
+        <v>-1.3743021188784108e-06</v>
       </c>
       <c r="O8" s="1">
-        <v>-3.691235940804715e-06</v>
+        <v>-3.7012327667282669e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>-1.3768764468251437e-06</v>
+        <v>-1.3830266835141376e-06</v>
       </c>
       <c r="Q8" s="1">
-        <v>-3.4871077512173773e-06</v>
+        <v>-3.5058957606582086e-06</v>
       </c>
       <c r="R8" s="1">
-        <v>1.055040628316656e-07</v>
+        <v>1.0561674464648459e-07</v>
       </c>
       <c r="S8" s="1">
-        <v>-2.6463265974058484e-06</v>
+        <v>-2.652105793195633e-06</v>
       </c>
       <c r="T8" s="1">
-        <v>-1.9312994038301898e-06</v>
+        <v>-1.9293417624907721e-06</v>
       </c>
       <c r="U8" s="1">
-        <v>-0.0030457851616802686</v>
+        <v>-0.0030449454475442832</v>
       </c>
       <c r="V8" s="1">
-        <v>1.5166717312154494e-05</v>
+        <v>1.5139486975151588e-05</v>
       </c>
     </row>
     <row r="9">
@@ -889,67 +889,67 @@
         <v>31</v>
       </c>
       <c r="B9" s="1">
-        <v>0.15805156649943283</v>
+        <v>0.15770081764415259</v>
       </c>
       <c r="C9" s="1">
-        <v>8.4317372271401765e-07</v>
+        <v>8.0560785472384637e-07</v>
       </c>
       <c r="D9" s="1">
-        <v>-1.1059373311137032e-08</v>
+        <v>-1.0639772280442241e-08</v>
       </c>
       <c r="E9" s="1">
-        <v>-6.8193402183385812e-06</v>
+        <v>-6.8232648994416889e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>-2.0500662677194108e-05</v>
+        <v>-1.9156242341298512e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>1.026255348100083e-07</v>
+        <v>1.0263658088267243e-07</v>
       </c>
       <c r="H9" s="1">
-        <v>7.2764128826474765e-07</v>
+        <v>7.0261112570819056e-07</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0030276623820857246</v>
+        <v>0.0030273631625743194</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0030675477761516207</v>
+        <v>0.0030672547458850214</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0030338991084162309</v>
+        <v>0.0030336023577711706</v>
       </c>
       <c r="L9" s="1">
-        <v>0.0030335148204005506</v>
+        <v>0.0030332265165150009</v>
       </c>
       <c r="M9" s="1">
-        <v>1.8675927780591668e-07</v>
+        <v>1.7757533052927437e-07</v>
       </c>
       <c r="N9" s="1">
-        <v>-8.848362644608013e-07</v>
+        <v>-8.9976470422332788e-07</v>
       </c>
       <c r="O9" s="1">
-        <v>-3.9706231753579159e-06</v>
+        <v>-3.9874731641595488e-06</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.8952102368341652e-06</v>
+        <v>-1.9047477800634337e-06</v>
       </c>
       <c r="Q9" s="1">
-        <v>-1.791760589507212e-06</v>
+        <v>-1.8264910367215102e-06</v>
       </c>
       <c r="R9" s="1">
-        <v>9.3083014878435117e-08</v>
+        <v>9.3262359498281594e-08</v>
       </c>
       <c r="S9" s="1">
-        <v>-3.3674191002731795e-06</v>
+        <v>-3.3783614631594364e-06</v>
       </c>
       <c r="T9" s="1">
-        <v>-1.9334533506246357e-06</v>
+        <v>-1.9304249892933818e-06</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.0030618229133462516</v>
+        <v>-0.0030607455248423286</v>
       </c>
       <c r="V9" s="1">
-        <v>2.4506878197730962e-05</v>
+        <v>2.4509503621104199e-05</v>
       </c>
     </row>
     <row r="10">
@@ -957,67 +957,67 @@
         <v>32</v>
       </c>
       <c r="B10" s="1">
-        <v>0.2122043430349948</v>
+        <v>0.21181221177961529</v>
       </c>
       <c r="C10" s="1">
-        <v>8.4767150119303543e-07</v>
+        <v>8.0501637712487228e-07</v>
       </c>
       <c r="D10" s="1">
-        <v>-7.2260118268646708e-09</v>
+        <v>-6.7493646964925625e-09</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.1308006653404276e-05</v>
+        <v>-1.1312348782111197e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>-2.8369241015758091e-05</v>
+        <v>-2.6850904073026093e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>2.7627120435826788e-07</v>
+        <v>2.7628861506977667e-07</v>
       </c>
       <c r="H10" s="1">
-        <v>1.0654525598870258e-06</v>
+        <v>1.037206504602527e-06</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0030281638913339836</v>
+        <v>0.0030278613362169447</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0030338991084162309</v>
+        <v>0.0030336023577711706</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0030525196397762689</v>
+        <v>0.0030522205100380474</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0030427483595873513</v>
+        <v>0.0030424581532515768</v>
       </c>
       <c r="M10" s="1">
-        <v>-2.3448166659836787e-07</v>
+        <v>-2.4492280117904825e-07</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.1096201922835455e-06</v>
+        <v>-1.1264852051520472e-06</v>
       </c>
       <c r="O10" s="1">
-        <v>-4.3379341872379113e-06</v>
+        <v>-4.3570129989064632e-06</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.3104931164993086e-06</v>
+        <v>-1.3213051304354598e-06</v>
       </c>
       <c r="Q10" s="1">
-        <v>-3.252660825229992e-07</v>
+        <v>-3.6457902849406428e-07</v>
       </c>
       <c r="R10" s="1">
-        <v>-7.6395670367471531e-09</v>
+        <v>-7.4282623424352038e-09</v>
       </c>
       <c r="S10" s="1">
-        <v>-3.4153585396998965e-06</v>
+        <v>-3.4278369457188528e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>-2.4279277772050357e-06</v>
+        <v>-2.4247438598465194e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.0030671840658051974</v>
+        <v>-0.0030659988878670164</v>
       </c>
       <c r="V10" s="1">
-        <v>2.7716188615908838e-05</v>
+        <v>2.7717217363397025e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1025,67 +1025,67 @@
         <v>33</v>
       </c>
       <c r="B11" s="1">
-        <v>0.25460219041319526</v>
+        <v>0.2541525140565703</v>
       </c>
       <c r="C11" s="1">
-        <v>2.9566368279724079e-06</v>
+        <v>2.9146711988959332e-06</v>
       </c>
       <c r="D11" s="1">
-        <v>-2.5332271651949638e-08</v>
+        <v>-2.4863785919431147e-08</v>
       </c>
       <c r="E11" s="1">
-        <v>-3.8417057068733326e-06</v>
+        <v>-3.8488221666790244e-06</v>
       </c>
       <c r="F11" s="1">
-        <v>-1.7153887471305845e-05</v>
+        <v>-1.5591615168566264e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>1.6901529230731788e-07</v>
+        <v>1.6906306224689729e-07</v>
       </c>
       <c r="H11" s="1">
-        <v>8.9090832629188453e-07</v>
+        <v>8.617794977821371e-07</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0030272724129013287</v>
+        <v>0.0030269746709732058</v>
       </c>
       <c r="J11" s="1">
-        <v>0.0030335148204005506</v>
+        <v>0.0030332265165150009</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0030427483595873513</v>
+        <v>0.0030424581532515768</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0030932566988714524</v>
+        <v>0.0030929815346114353</v>
       </c>
       <c r="M11" s="1">
-        <v>9.747898794460846e-07</v>
+        <v>9.6460752793108904e-07</v>
       </c>
       <c r="N11" s="1">
-        <v>2.5310455710252637e-07</v>
+        <v>2.3588396046897222e-07</v>
       </c>
       <c r="O11" s="1">
-        <v>-4.1935728125301529e-06</v>
+        <v>-4.2134721574228771e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>3.0977431755784001e-07</v>
+        <v>2.9898462203938961e-07</v>
       </c>
       <c r="Q11" s="1">
-        <v>-1.9566763145856507e-07</v>
+        <v>-2.3858737106029992e-07</v>
       </c>
       <c r="R11" s="1">
-        <v>-2.5491723900837718e-09</v>
+        <v>-2.335723201444544e-09</v>
       </c>
       <c r="S11" s="1">
-        <v>-3.7125465402936158e-06</v>
+        <v>-3.7262886833700517e-06</v>
       </c>
       <c r="T11" s="1">
-        <v>-3.0263695757145263e-06</v>
+        <v>-3.0232157816752382e-06</v>
       </c>
       <c r="U11" s="1">
-        <v>-0.0031283288770682224</v>
+        <v>-0.0031271720365140497</v>
       </c>
       <c r="V11" s="1">
-        <v>2.8649253181900568e-05</v>
+        <v>2.8674211662918905e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1093,67 +1093,67 @@
         <v>34</v>
       </c>
       <c r="B12" s="1">
-        <v>0.0083335579328768592</v>
+        <v>0.0083538304894634572</v>
       </c>
       <c r="C12" s="1">
-        <v>1.2068090182804621e-07</v>
+        <v>1.16862605197988e-07</v>
       </c>
       <c r="D12" s="1">
-        <v>-2.1767320020637379e-09</v>
+        <v>-2.1332918573891626e-09</v>
       </c>
       <c r="E12" s="1">
-        <v>-4.9458132332830786e-06</v>
+        <v>-4.9432377875146203e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>-1.0608408797322664e-05</v>
+        <v>-1.0526075731655756e-05</v>
       </c>
       <c r="G12" s="1">
-        <v>9.0785319159750885e-08</v>
+        <v>9.0752817670935118e-08</v>
       </c>
       <c r="H12" s="1">
-        <v>1.209816098187894e-07</v>
+        <v>1.1950946965182586e-07</v>
       </c>
       <c r="I12" s="1">
-        <v>7.6505132509809354e-07</v>
+        <v>7.5851667145174283e-07</v>
       </c>
       <c r="J12" s="1">
-        <v>1.8675927780591668e-07</v>
+        <v>1.7757533052927437e-07</v>
       </c>
       <c r="K12" s="1">
-        <v>-2.3448166659836787e-07</v>
+        <v>-2.4492280117904825e-07</v>
       </c>
       <c r="L12" s="1">
-        <v>9.747898794460846e-07</v>
+        <v>9.6460752793108904e-07</v>
       </c>
       <c r="M12" s="1">
-        <v>9.1153503188232793e-05</v>
+        <v>9.1158224134462181e-05</v>
       </c>
       <c r="N12" s="1">
-        <v>4.4046811231707851e-05</v>
+        <v>4.4048684113126495e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>4.422370120461402e-05</v>
+        <v>4.4225636421128746e-05</v>
       </c>
       <c r="P12" s="1">
-        <v>4.4098559985987563e-05</v>
+        <v>4.4100524115587222e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>2.129868386484657e-06</v>
+        <v>2.129519524453962e-06</v>
       </c>
       <c r="R12" s="1">
-        <v>-8.6919700482914961e-08</v>
+        <v>-8.6902779667313374e-08</v>
       </c>
       <c r="S12" s="1">
-        <v>-3.6611526577338309e-07</v>
+        <v>-3.6610679134181987e-07</v>
       </c>
       <c r="T12" s="1">
-        <v>-8.2632936736806816e-07</v>
+        <v>-8.2613603752621857e-07</v>
       </c>
       <c r="U12" s="1">
-        <v>-3.525280006894576e-05</v>
+        <v>-3.5163367994030161e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>1.3685012801618141e-06</v>
+        <v>1.3475424794372268e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1161,67 +1161,67 @@
         <v>35</v>
       </c>
       <c r="B13" s="1">
-        <v>0.02705584039975107</v>
+        <v>0.027126015280487432</v>
       </c>
       <c r="C13" s="1">
-        <v>3.3810341724291634e-07</v>
+        <v>3.3487589984349276e-07</v>
       </c>
       <c r="D13" s="1">
-        <v>-4.5538198974041156e-09</v>
+        <v>-4.5161858490145676e-09</v>
       </c>
       <c r="E13" s="1">
-        <v>-5.627809411566338e-07</v>
+        <v>-5.5763979424963258e-07</v>
       </c>
       <c r="F13" s="1">
-        <v>-3.0484089197335197e-06</v>
+        <v>-3.0264986979324477e-06</v>
       </c>
       <c r="G13" s="1">
-        <v>3.0097087744728916e-08</v>
+        <v>3.0036427532905232e-08</v>
       </c>
       <c r="H13" s="1">
-        <v>6.9910388203098331e-08</v>
+        <v>6.9612947129353282e-08</v>
       </c>
       <c r="I13" s="1">
-        <v>-1.364876060161576e-06</v>
+        <v>-1.3743021188784108e-06</v>
       </c>
       <c r="J13" s="1">
-        <v>-8.848362644608013e-07</v>
+        <v>-8.9976470422332788e-07</v>
       </c>
       <c r="K13" s="1">
-        <v>-1.1096201922835455e-06</v>
+        <v>-1.1264852051520472e-06</v>
       </c>
       <c r="L13" s="1">
-        <v>2.5310455710252637e-07</v>
+        <v>2.3588396046897222e-07</v>
       </c>
       <c r="M13" s="1">
-        <v>4.4046811231707851e-05</v>
+        <v>4.4048684113126495e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>0.00011879691065105111</v>
+        <v>0.00011880357645127175</v>
       </c>
       <c r="O13" s="1">
-        <v>4.401200596027503e-05</v>
+        <v>4.4015004991704252e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>4.4058319277406546e-05</v>
+        <v>4.4060659054796185e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>1.5973644248127898e-06</v>
+        <v>1.6005557527185918e-06</v>
       </c>
       <c r="R13" s="1">
-        <v>-4.6789976826757827e-08</v>
+        <v>-4.6780402892846797e-08</v>
       </c>
       <c r="S13" s="1">
-        <v>-1.4224116434211398e-06</v>
+        <v>-1.4212868543863519e-06</v>
       </c>
       <c r="T13" s="1">
-        <v>-8.9077703775039161e-07</v>
+        <v>-8.9064599156142399e-07</v>
       </c>
       <c r="U13" s="1">
-        <v>-4.4069279660249129e-05</v>
+        <v>-4.3983850360753291e-05</v>
       </c>
       <c r="V13" s="1">
-        <v>7.4703763738124884e-08</v>
+        <v>3.6572887087977368e-08</v>
       </c>
     </row>
     <row r="14">
@@ -1229,67 +1229,67 @@
         <v>36</v>
       </c>
       <c r="B14" s="1">
-        <v>0.0011885813837463218</v>
+        <v>0.0012816004907901975</v>
       </c>
       <c r="C14" s="1">
-        <v>-1.238364991441445e-07</v>
+        <v>-1.2680547077806725e-07</v>
       </c>
       <c r="D14" s="1">
-        <v>5.3624008225968987e-10</v>
+        <v>5.7129912385489015e-10</v>
       </c>
       <c r="E14" s="1">
-        <v>-4.2670068545485246e-06</v>
+        <v>-4.2605520286257519e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-7.3288205622758489e-06</v>
+        <v>-7.3375088316040853e-06</v>
       </c>
       <c r="G14" s="1">
-        <v>9.496221407268425e-08</v>
+        <v>9.4884999134146079e-08</v>
       </c>
       <c r="H14" s="1">
-        <v>5.4148529084220542e-08</v>
+        <v>5.4438002029274751e-08</v>
       </c>
       <c r="I14" s="1">
-        <v>-3.691235940804715e-06</v>
+        <v>-3.7012327667282669e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-3.9706231753579159e-06</v>
+        <v>-3.9874731641595488e-06</v>
       </c>
       <c r="K14" s="1">
-        <v>-4.3379341872379113e-06</v>
+        <v>-4.3570129989064632e-06</v>
       </c>
       <c r="L14" s="1">
-        <v>-4.1935728125301529e-06</v>
+        <v>-4.2134721574228771e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>4.422370120461402e-05</v>
+        <v>4.4225636421128746e-05</v>
       </c>
       <c r="N14" s="1">
-        <v>4.401200596027503e-05</v>
+        <v>4.4015004991704252e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>9.0645492483507368e-05</v>
+        <v>9.0651317667788189e-05</v>
       </c>
       <c r="P14" s="1">
-        <v>4.4074113009937744e-05</v>
+        <v>4.4076613437748002e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.4014500300570488e-06</v>
+        <v>1.4062459058878472e-06</v>
       </c>
       <c r="R14" s="1">
-        <v>-9.5670263213541079e-08</v>
+        <v>-9.5664137603034184e-08</v>
       </c>
       <c r="S14" s="1">
-        <v>1.2863238020437718e-07</v>
+        <v>1.3013030196270514e-07</v>
       </c>
       <c r="T14" s="1">
-        <v>4.0775898320495001e-07</v>
+        <v>4.0788627328788904e-07</v>
       </c>
       <c r="U14" s="1">
-        <v>-2.4852237938715475e-05</v>
+        <v>-2.4768954813775459e-05</v>
       </c>
       <c r="V14" s="1">
-        <v>-4.9554044099753112e-07</v>
+        <v>-5.4141406104443026e-07</v>
       </c>
     </row>
     <row r="15">
@@ -1297,67 +1297,67 @@
         <v>37</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.044991738344973393</v>
+        <v>-0.044953610390708172</v>
       </c>
       <c r="C15" s="1">
-        <v>1.0215912513359728e-07</v>
+        <v>9.9288964455779719e-08</v>
       </c>
       <c r="D15" s="1">
-        <v>-1.6669059656836359e-09</v>
+        <v>-1.6337578635212726e-09</v>
       </c>
       <c r="E15" s="1">
-        <v>4.7886988730571146e-07</v>
+        <v>4.8229131232343832e-07</v>
       </c>
       <c r="F15" s="1">
-        <v>1.1115588097028388e-06</v>
+        <v>1.1565056891193432e-06</v>
       </c>
       <c r="G15" s="1">
-        <v>1.6068896802480572e-08</v>
+        <v>1.602880534718309e-08</v>
       </c>
       <c r="H15" s="1">
-        <v>-5.1197510418094307e-08</v>
+        <v>-5.1959851377683149e-08</v>
       </c>
       <c r="I15" s="1">
-        <v>-1.3768764468251437e-06</v>
+        <v>-1.3830266835141376e-06</v>
       </c>
       <c r="J15" s="1">
-        <v>-1.8952102368341652e-06</v>
+        <v>-1.9047477800634337e-06</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.3104931164993086e-06</v>
+        <v>-1.3213051304354598e-06</v>
       </c>
       <c r="L15" s="1">
-        <v>3.0977431755784001e-07</v>
+        <v>2.9898462203938961e-07</v>
       </c>
       <c r="M15" s="1">
-        <v>4.4098559985987563e-05</v>
+        <v>4.4100524115587222e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>4.4058319277406546e-05</v>
+        <v>4.4060659054796185e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>4.4074113009937744e-05</v>
+        <v>4.4076613437748002e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>6.1915998958013036e-05</v>
+        <v>6.191931791429862e-05</v>
       </c>
       <c r="Q15" s="1">
-        <v>1.4178507909682633e-06</v>
+        <v>1.4191351020040481e-06</v>
       </c>
       <c r="R15" s="1">
-        <v>-6.1366654125358135e-08</v>
+        <v>-6.1356402266629719e-08</v>
       </c>
       <c r="S15" s="1">
-        <v>-1.0260823671818835e-06</v>
+        <v>-1.0255851506493601e-06</v>
       </c>
       <c r="T15" s="1">
-        <v>-8.0326848812981917e-07</v>
+        <v>-8.0317138349350411e-07</v>
       </c>
       <c r="U15" s="1">
-        <v>-3.806822766392523e-05</v>
+        <v>-3.7998019859809324e-05</v>
       </c>
       <c r="V15" s="1">
-        <v>5.8391775548212476e-07</v>
+        <v>5.5938735046055643e-07</v>
       </c>
     </row>
     <row r="16">
@@ -1365,67 +1365,67 @@
         <v>38</v>
       </c>
       <c r="B16" s="1">
-        <v>0.15440435516845671</v>
+        <v>0.15467095436478834</v>
       </c>
       <c r="C16" s="1">
-        <v>1.2868869503707406e-06</v>
+        <v>1.287307148851817e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.6399631699118336e-08</v>
+        <v>-1.6400371512060319e-08</v>
       </c>
       <c r="E16" s="1">
-        <v>-2.518342379120552e-06</v>
+        <v>-2.5036325589774707e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>-4.1025626837536007e-06</v>
+        <v>-4.378204627246228e-06</v>
       </c>
       <c r="G16" s="1">
-        <v>1.0719338819509999e-07</v>
+        <v>1.0701784013331081e-07</v>
       </c>
       <c r="H16" s="1">
-        <v>5.8920242813982746e-08</v>
+        <v>6.4352453029831595e-08</v>
       </c>
       <c r="I16" s="1">
-        <v>-3.4871077512173773e-06</v>
+        <v>-3.5058957606582086e-06</v>
       </c>
       <c r="J16" s="1">
-        <v>-1.791760589507212e-06</v>
+        <v>-1.8264910367215102e-06</v>
       </c>
       <c r="K16" s="1">
-        <v>-3.252660825229992e-07</v>
+        <v>-3.6457902849406428e-07</v>
       </c>
       <c r="L16" s="1">
-        <v>-1.9566763145856507e-07</v>
+        <v>-2.3858737106029992e-07</v>
       </c>
       <c r="M16" s="1">
-        <v>2.129868386484657e-06</v>
+        <v>2.129519524453962e-06</v>
       </c>
       <c r="N16" s="1">
-        <v>1.5973644248127898e-06</v>
+        <v>1.6005557527185918e-06</v>
       </c>
       <c r="O16" s="1">
-        <v>1.4014500300570488e-06</v>
+        <v>1.4062459058878472e-06</v>
       </c>
       <c r="P16" s="1">
-        <v>1.4178507909682633e-06</v>
+        <v>1.4191351020040481e-06</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.00010275622091604013</v>
+        <v>0.00010276299352784551</v>
       </c>
       <c r="R16" s="1">
-        <v>1.1882449274786724e-07</v>
+        <v>1.1878406525384075e-07</v>
       </c>
       <c r="S16" s="1">
-        <v>-1.0881082168777707e-06</v>
+        <v>-1.0825144177409712e-06</v>
       </c>
       <c r="T16" s="1">
-        <v>-1.3085758463989376e-06</v>
+        <v>-1.308703696006546e-06</v>
       </c>
       <c r="U16" s="1">
-        <v>-4.4358779436278592e-05</v>
+        <v>-4.4313632997555096e-05</v>
       </c>
       <c r="V16" s="1">
-        <v>-5.7008368325542436e-06</v>
+        <v>-5.8009204127885044e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1433,67 +1433,67 @@
         <v>39</v>
       </c>
       <c r="B17" s="1">
-        <v>0.0038295325501462849</v>
+        <v>0.0038287599376889661</v>
       </c>
       <c r="C17" s="1">
-        <v>-3.0443273059907e-09</v>
+        <v>-2.9939101071275917e-09</v>
       </c>
       <c r="D17" s="1">
-        <v>-8.6130814858915289e-11</v>
+        <v>-8.6702841544028043e-11</v>
       </c>
       <c r="E17" s="1">
-        <v>2.4622778622312496e-08</v>
+        <v>2.4564294365875238e-08</v>
       </c>
       <c r="F17" s="1">
-        <v>-1.9307941966382042e-07</v>
+        <v>-1.9362334703498823e-07</v>
       </c>
       <c r="G17" s="1">
-        <v>2.8366709537948588e-09</v>
+        <v>2.8370771038035591e-09</v>
       </c>
       <c r="H17" s="1">
-        <v>9.4525579509966195e-09</v>
+        <v>9.4607643486743451e-09</v>
       </c>
       <c r="I17" s="1">
-        <v>1.055040628316656e-07</v>
+        <v>1.0561674464648459e-07</v>
       </c>
       <c r="J17" s="1">
-        <v>9.3083014878435117e-08</v>
+        <v>9.3262359498281594e-08</v>
       </c>
       <c r="K17" s="1">
-        <v>-7.6395670367471531e-09</v>
+        <v>-7.4282623424352038e-09</v>
       </c>
       <c r="L17" s="1">
-        <v>-2.5491723900837718e-09</v>
+        <v>-2.335723201444544e-09</v>
       </c>
       <c r="M17" s="1">
-        <v>-8.6919700482914961e-08</v>
+        <v>-8.6902779667313374e-08</v>
       </c>
       <c r="N17" s="1">
-        <v>-4.6789976826757827e-08</v>
+        <v>-4.6780402892846797e-08</v>
       </c>
       <c r="O17" s="1">
-        <v>-9.5670263213541079e-08</v>
+        <v>-9.5664137603034184e-08</v>
       </c>
       <c r="P17" s="1">
-        <v>-6.1366654125358135e-08</v>
+        <v>-6.1356402266629719e-08</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.1882449274786724e-07</v>
+        <v>1.1878406525384075e-07</v>
       </c>
       <c r="R17" s="1">
-        <v>5.0845163613639966e-08</v>
+        <v>5.0841509186582848e-08</v>
       </c>
       <c r="S17" s="1">
-        <v>-7.7056542250381076e-07</v>
+        <v>-7.7052226162414961e-07</v>
       </c>
       <c r="T17" s="1">
-        <v>-9.2903032268191193e-07</v>
+        <v>-9.2896713835126301e-07</v>
       </c>
       <c r="U17" s="1">
-        <v>-5.228965281488511e-06</v>
+        <v>-5.2299163349703074e-06</v>
       </c>
       <c r="V17" s="1">
-        <v>-7.3700802080627295e-09</v>
+        <v>-6.8977964509698457e-09</v>
       </c>
     </row>
     <row r="18">
@@ -1501,67 +1501,67 @@
         <v>40</v>
       </c>
       <c r="B18" s="1">
-        <v>0.049855895566313965</v>
+        <v>0.049941938803977112</v>
       </c>
       <c r="C18" s="1">
-        <v>-2.3621210190511055e-08</v>
+        <v>-2.363891108272477e-08</v>
       </c>
       <c r="D18" s="1">
-        <v>1.2166375867943272e-09</v>
+        <v>1.2178562837811263e-09</v>
       </c>
       <c r="E18" s="1">
-        <v>9.7866890382210562e-07</v>
+        <v>9.8301343261619357e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>3.6769049999317933e-06</v>
+        <v>3.5963462374070435e-06</v>
       </c>
       <c r="G18" s="1">
-        <v>-4.0797229596750681e-08</v>
+        <v>-4.0839758380450006e-08</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.0867347129254e-07</v>
+        <v>-1.0707289920860612e-07</v>
       </c>
       <c r="I18" s="1">
-        <v>-2.6463265974058484e-06</v>
+        <v>-2.652105793195633e-06</v>
       </c>
       <c r="J18" s="1">
-        <v>-3.3674191002731795e-06</v>
+        <v>-3.3783614631594364e-06</v>
       </c>
       <c r="K18" s="1">
-        <v>-3.4153585396998965e-06</v>
+        <v>-3.4278369457188528e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>-3.7125465402936158e-06</v>
+        <v>-3.7262886833700517e-06</v>
       </c>
       <c r="M18" s="1">
-        <v>-3.6611526577338309e-07</v>
+        <v>-3.6610679134181987e-07</v>
       </c>
       <c r="N18" s="1">
-        <v>-1.4224116434211398e-06</v>
+        <v>-1.4212868543863519e-06</v>
       </c>
       <c r="O18" s="1">
-        <v>1.2863238020437718e-07</v>
+        <v>1.3013030196270514e-07</v>
       </c>
       <c r="P18" s="1">
-        <v>-1.0260823671818835e-06</v>
+        <v>-1.0255851506493601e-06</v>
       </c>
       <c r="Q18" s="1">
-        <v>-1.0881082168777707e-06</v>
+        <v>-1.0825144177409712e-06</v>
       </c>
       <c r="R18" s="1">
-        <v>-7.7056542250381076e-07</v>
+        <v>-7.7052226162414961e-07</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00013364424020636531</v>
+        <v>0.00013365077962623705</v>
       </c>
       <c r="T18" s="1">
-        <v>2.2831571976786849e-05</v>
+        <v>2.2831106331894453e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>7.8067257599261634e-05</v>
+        <v>7.8078397972998205e-05</v>
       </c>
       <c r="V18" s="1">
-        <v>-1.7272678892905792e-06</v>
+        <v>-1.7595185140241685e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1569,67 +1569,67 @@
         <v>41</v>
       </c>
       <c r="B19" s="1">
-        <v>0.027431351526688626</v>
+        <v>0.027423534661633928</v>
       </c>
       <c r="C19" s="1">
-        <v>-3.1352851083403726e-08</v>
+        <v>-3.0197262695497932e-08</v>
       </c>
       <c r="D19" s="1">
-        <v>1.634277312334384e-09</v>
+        <v>1.6206790997093738e-09</v>
       </c>
       <c r="E19" s="1">
-        <v>2.0194812079165307e-06</v>
+        <v>2.0181818010905961e-06</v>
       </c>
       <c r="F19" s="1">
-        <v>3.893495457997588e-06</v>
+        <v>3.8742887382417414e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>-7.0791792088767467e-08</v>
+        <v>-7.0765696585988268e-08</v>
       </c>
       <c r="H19" s="1">
-        <v>-1.183944413746588e-07</v>
+        <v>-1.1804506730385767e-07</v>
       </c>
       <c r="I19" s="1">
-        <v>-1.9312994038301898e-06</v>
+        <v>-1.9293417624907721e-06</v>
       </c>
       <c r="J19" s="1">
-        <v>-1.9334533506246357e-06</v>
+        <v>-1.9304249892933818e-06</v>
       </c>
       <c r="K19" s="1">
-        <v>-2.4279277772050357e-06</v>
+        <v>-2.4247438598465194e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>-3.0263695757145263e-06</v>
+        <v>-3.0232157816752382e-06</v>
       </c>
       <c r="M19" s="1">
-        <v>-8.2632936736806816e-07</v>
+        <v>-8.2613603752621857e-07</v>
       </c>
       <c r="N19" s="1">
-        <v>-8.9077703775039161e-07</v>
+        <v>-8.9064599156142399e-07</v>
       </c>
       <c r="O19" s="1">
-        <v>4.0775898320495001e-07</v>
+        <v>4.0788627328788904e-07</v>
       </c>
       <c r="P19" s="1">
-        <v>-8.0326848812981917e-07</v>
+        <v>-8.0317138349350411e-07</v>
       </c>
       <c r="Q19" s="1">
-        <v>-1.3085758463989376e-06</v>
+        <v>-1.308703696006546e-06</v>
       </c>
       <c r="R19" s="1">
-        <v>-9.2903032268191193e-07</v>
+        <v>-9.2896713835126301e-07</v>
       </c>
       <c r="S19" s="1">
-        <v>2.2831571976786849e-05</v>
+        <v>2.2831106331894453e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.00014814108933439225</v>
+        <v>0.00014814843884011666</v>
       </c>
       <c r="U19" s="1">
-        <v>9.3305142780873173e-05</v>
+        <v>9.3269947993041615e-05</v>
       </c>
       <c r="V19" s="1">
-        <v>-3.9560632178029668e-07</v>
+        <v>-3.8862359062560318e-07</v>
       </c>
     </row>
     <row r="20">
@@ -1637,67 +1637,67 @@
         <v>42</v>
       </c>
       <c r="B20" s="1">
-        <v>0.11967648653930617</v>
+        <v>0.11838292204124685</v>
       </c>
       <c r="C20" s="1">
-        <v>-8.5567216401620963e-05</v>
+        <v>-8.5183728788814278e-05</v>
       </c>
       <c r="D20" s="1">
-        <v>9.1766039847488133e-07</v>
+        <v>9.132892687609324e-07</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.00034583742543704799</v>
+        <v>-0.00034608072263972434</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.00023444928571363967</v>
+        <v>-0.00024345962712371181</v>
       </c>
       <c r="G20" s="1">
-        <v>7.4215545530132213e-06</v>
+        <v>7.424831868113934e-06</v>
       </c>
       <c r="H20" s="1">
-        <v>4.3230276470916549e-06</v>
+        <v>4.4856583430476527e-06</v>
       </c>
       <c r="I20" s="1">
-        <v>-0.0030457851616802686</v>
+        <v>-0.0030449454475442832</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.0030618229133462516</v>
+        <v>-0.0030607455248423286</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.0030671840658051974</v>
+        <v>-0.0030659988878670164</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.0031283288770682224</v>
+        <v>-0.0031271720365140497</v>
       </c>
       <c r="M20" s="1">
-        <v>-3.525280006894576e-05</v>
+        <v>-3.5163367994030161e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-4.4069279660249129e-05</v>
+        <v>-4.3983850360753291e-05</v>
       </c>
       <c r="O20" s="1">
-        <v>-2.4852237938715475e-05</v>
+        <v>-2.4768954813775459e-05</v>
       </c>
       <c r="P20" s="1">
-        <v>-3.806822766392523e-05</v>
+        <v>-3.7998019859809324e-05</v>
       </c>
       <c r="Q20" s="1">
-        <v>-4.4358779436278592e-05</v>
+        <v>-4.4313632997555096e-05</v>
       </c>
       <c r="R20" s="1">
-        <v>-5.228965281488511e-06</v>
+        <v>-5.2299163349703074e-06</v>
       </c>
       <c r="S20" s="1">
-        <v>7.8067257599261634e-05</v>
+        <v>7.8078397972998205e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>9.3305142780873173e-05</v>
+        <v>9.3269947993041615e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0055952521152258308</v>
+        <v>0.0055858556410524063</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.00015218188966993043</v>
+        <v>-0.00015036054919221632</v>
       </c>
     </row>
     <row r="21">
@@ -1705,67 +1705,67 @@
         <v>43</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.11901755009190702</v>
+        <v>-0.12013895015729667</v>
       </c>
       <c r="C21" s="1">
-        <v>5.6012429124135965e-06</v>
+        <v>5.5128227794583851e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>-6.5152717011151527e-08</v>
+        <v>-6.4169038791260092e-08</v>
       </c>
       <c r="E21" s="1">
-        <v>-8.5420764099746514e-06</v>
+        <v>-8.566987502472459e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-3.9567854381959409e-05</v>
+        <v>-3.6195207130673895e-05</v>
       </c>
       <c r="G21" s="1">
-        <v>1.0154755128875033e-07</v>
+        <v>1.0174066639595279e-07</v>
       </c>
       <c r="H21" s="1">
-        <v>5.5314081060674364e-07</v>
+        <v>4.9007528536898502e-07</v>
       </c>
       <c r="I21" s="1">
-        <v>1.5166717312154494e-05</v>
+        <v>1.5139486975151588e-05</v>
       </c>
       <c r="J21" s="1">
-        <v>2.4506878197730962e-05</v>
+        <v>2.4509503621104199e-05</v>
       </c>
       <c r="K21" s="1">
-        <v>2.7716188615908838e-05</v>
+        <v>2.7717217363397025e-05</v>
       </c>
       <c r="L21" s="1">
-        <v>2.8649253181900568e-05</v>
+        <v>2.8674211662918905e-05</v>
       </c>
       <c r="M21" s="1">
-        <v>1.3685012801618141e-06</v>
+        <v>1.3475424794372268e-06</v>
       </c>
       <c r="N21" s="1">
-        <v>7.4703763738124884e-08</v>
+        <v>3.6572887087977368e-08</v>
       </c>
       <c r="O21" s="1">
-        <v>-4.9554044099753112e-07</v>
+        <v>-5.4141406104443026e-07</v>
       </c>
       <c r="P21" s="1">
-        <v>5.8391775548212476e-07</v>
+        <v>5.5938735046055643e-07</v>
       </c>
       <c r="Q21" s="1">
-        <v>-5.7008368325542436e-06</v>
+        <v>-5.8009204127885044e-06</v>
       </c>
       <c r="R21" s="1">
-        <v>-7.3700802080627295e-09</v>
+        <v>-6.8977964509698457e-09</v>
       </c>
       <c r="S21" s="1">
-        <v>-1.7272678892905792e-06</v>
+        <v>-1.7595185140241685e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>-3.9560632178029668e-07</v>
+        <v>-3.8862359062560318e-07</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.00015218188966993043</v>
+        <v>-0.00015036054919221632</v>
       </c>
       <c r="V21" s="1">
-        <v>6.3531170575090591e-05</v>
+        <v>6.3645773438076176e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1850,67 +1850,67 @@
         <v>24</v>
       </c>
       <c r="B2" s="1">
-        <v>0.043592901124043369</v>
+        <v>0.043633801884624804</v>
       </c>
       <c r="C2" s="1">
-        <v>3.2206018856665638e-06</v>
+        <v>3.2042315725113419e-06</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.3770939767060129e-08</v>
+        <v>-3.3584026301938334e-08</v>
       </c>
       <c r="E2" s="1">
-        <v>1.4917070440772305e-05</v>
+        <v>1.490228742152874e-05</v>
       </c>
       <c r="F2" s="1">
-        <v>1.4658271238352207e-05</v>
+        <v>1.4949199267456436e-05</v>
       </c>
       <c r="G2" s="1">
-        <v>-3.4061773709745298e-07</v>
+        <v>-3.4040753794298746e-07</v>
       </c>
       <c r="H2" s="1">
-        <v>-3.2716951269188252e-07</v>
+        <v>-3.3253286602651488e-07</v>
       </c>
       <c r="I2" s="1">
-        <v>9.2480046709029532e-07</v>
+        <v>9.1135007744960681e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>1.7908031423996577e-06</v>
+        <v>1.7503540737004424e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>1.4188452339631969e-06</v>
+        <v>1.3715508390223655e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>3.2013446179104678e-06</v>
+        <v>3.1566827392836311e-06</v>
       </c>
       <c r="M2" s="1">
-        <v>1.3295745918648144e-07</v>
+        <v>1.2518169036073267e-07</v>
       </c>
       <c r="N2" s="1">
-        <v>-7.8782222113765361e-08</v>
+        <v>-8.301742021195137e-08</v>
       </c>
       <c r="O2" s="1">
-        <v>-1.8770160486494024e-07</v>
+        <v>-1.9284313821271901e-07</v>
       </c>
       <c r="P2" s="1">
-        <v>-3.5714799957775621e-08</v>
+        <v>-3.9233213741386746e-08</v>
       </c>
       <c r="Q2" s="1">
-        <v>2.5507678301275693e-06</v>
+        <v>2.5309332504622639e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>3.314239666872741e-09</v>
+        <v>3.3496444263259769e-09</v>
       </c>
       <c r="S2" s="1">
-        <v>-1.1123191806743202e-07</v>
+        <v>-1.1212055725750406e-07</v>
       </c>
       <c r="T2" s="1">
-        <v>-4.6588364297259917e-08</v>
+        <v>-4.3383420282702772e-08</v>
       </c>
       <c r="U2" s="1">
-        <v>-7.4613092364366954e-05</v>
+        <v>-7.420896334968692e-05</v>
       </c>
       <c r="V2" s="1">
-        <v>6.0239027218038284e-06</v>
+        <v>5.9059197217351462e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1918,67 +1918,67 @@
         <v>25</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.00038645118715319486</v>
+        <v>-0.00038659585512739933</v>
       </c>
       <c r="C3" s="1">
-        <v>-3.3770939767060129e-08</v>
+        <v>-3.3584026301938334e-08</v>
       </c>
       <c r="D3" s="1">
-        <v>3.866829744841141e-10</v>
+        <v>3.8456297420256788e-10</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.832941320992192e-08</v>
+        <v>-4.8129363776674123e-08</v>
       </c>
       <c r="F3" s="1">
-        <v>-4.2885068910992562e-08</v>
+        <v>-4.6298244336823982e-08</v>
       </c>
       <c r="G3" s="1">
-        <v>9.2694092479948541e-10</v>
+        <v>9.2385199811314817e-10</v>
       </c>
       <c r="H3" s="1">
-        <v>7.370277783136539e-10</v>
+        <v>7.999973585082339e-10</v>
       </c>
       <c r="I3" s="1">
-        <v>-1.0983083483309323e-08</v>
+        <v>-1.0855251847191668e-08</v>
       </c>
       <c r="J3" s="1">
-        <v>-2.1604064327458507e-08</v>
+        <v>-2.1192832995669312e-08</v>
       </c>
       <c r="K3" s="1">
-        <v>-1.3428558171883629e-08</v>
+        <v>-1.294768230587386e-08</v>
       </c>
       <c r="L3" s="1">
-        <v>-2.8161047602666538e-08</v>
+        <v>-2.7710325229700028e-08</v>
       </c>
       <c r="M3" s="1">
-        <v>-2.384763821274194e-09</v>
+        <v>-2.2949386506853203e-09</v>
       </c>
       <c r="N3" s="1">
-        <v>-2.7560553429402627e-10</v>
+        <v>-2.2320097786528645e-10</v>
       </c>
       <c r="O3" s="1">
-        <v>1.350144840732081e-09</v>
+        <v>1.4132086029811441e-09</v>
       </c>
       <c r="P3" s="1">
-        <v>2.2462124056915422e-10</v>
+        <v>2.6712929934848926e-10</v>
       </c>
       <c r="Q3" s="1">
-        <v>-3.2588011086063637e-08</v>
+        <v>-3.2324504200035493e-08</v>
       </c>
       <c r="R3" s="1">
-        <v>-1.2929205771067281e-10</v>
+        <v>-1.2978966376503602e-10</v>
       </c>
       <c r="S3" s="1">
-        <v>2.7654401231375974e-09</v>
+        <v>2.7805036276645605e-09</v>
       </c>
       <c r="T3" s="1">
-        <v>1.8246189847060525e-09</v>
+        <v>1.7869368223315584e-09</v>
       </c>
       <c r="U3" s="1">
-        <v>7.3423983532499709e-07</v>
+        <v>7.2968350130993608e-07</v>
       </c>
       <c r="V3" s="1">
-        <v>-7.2516605912914439e-08</v>
+        <v>-7.1289576428991611e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1986,67 +1986,67 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.090530954676465408</v>
+        <v>-0.090101277775636937</v>
       </c>
       <c r="C4" s="1">
-        <v>1.4917070440772305e-05</v>
+        <v>1.490228742152874e-05</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.832941320992192e-08</v>
+        <v>-4.8129363776674123e-08</v>
       </c>
       <c r="E4" s="1">
-        <v>0.00061492839486870787</v>
+        <v>0.00061504449977703814</v>
       </c>
       <c r="F4" s="1">
-        <v>0.00048246816428757785</v>
+        <v>0.0004827006995066519</v>
       </c>
       <c r="G4" s="1">
-        <v>-1.3754885548264782e-05</v>
+        <v>-1.3757128124930262e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>-1.0871304591192617e-05</v>
+        <v>-1.0875506000596402e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>1.2912881379908431e-06</v>
+        <v>1.2472609842455153e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>-2.6452284565903375e-06</v>
+        <v>-2.7455563674408398e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>-8.1666654488190945e-06</v>
+        <v>-8.2845147005175181e-06</v>
       </c>
       <c r="L4" s="1">
-        <v>-2.6287765468338179e-06</v>
+        <v>-2.7436377126154134e-06</v>
       </c>
       <c r="M4" s="1">
-        <v>-2.0650137708531209e-06</v>
+        <v>-2.0720617891480734e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.1762409589631016e-06</v>
+        <v>-2.1752688267601599e-06</v>
       </c>
       <c r="O4" s="1">
-        <v>-2.2079654469453422e-06</v>
+        <v>-2.2088021276361257e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>4.7825852857397362e-07</v>
+        <v>4.7711716894758409e-07</v>
       </c>
       <c r="Q4" s="1">
-        <v>-2.3707761787512191e-06</v>
+        <v>-2.3437277245262187e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>6.297365344799205e-08</v>
+        <v>6.2885073030450104e-08</v>
       </c>
       <c r="S4" s="1">
-        <v>2.7686593490405425e-06</v>
+        <v>2.774102748389747e-06</v>
       </c>
       <c r="T4" s="1">
-        <v>1.5283742408599028e-06</v>
+        <v>1.5315978668998704e-06</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.0005590087981275397</v>
+        <v>-0.00055861273138013462</v>
       </c>
       <c r="V4" s="1">
-        <v>1.3285894679176042e-06</v>
+        <v>1.070555011483761e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2054,67 +2054,67 @@
         <v>27</v>
       </c>
       <c r="B5" s="1">
-        <v>0.014443388803588952</v>
+        <v>0.0087588430388607381</v>
       </c>
       <c r="C5" s="1">
-        <v>1.4658271238352207e-05</v>
+        <v>1.4949199267456436e-05</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.2885068910992562e-08</v>
+        <v>-4.6298244336823982e-08</v>
       </c>
       <c r="E5" s="1">
-        <v>0.00048246816428757785</v>
+        <v>0.0004827006995066519</v>
       </c>
       <c r="F5" s="1">
-        <v>0.001546394931913725</v>
+        <v>0.0015440577177182645</v>
       </c>
       <c r="G5" s="1">
-        <v>-1.0937817760013365e-05</v>
+        <v>-1.0939333259146292e-05</v>
       </c>
       <c r="H5" s="1">
-        <v>-3.3076335651950156e-05</v>
+        <v>-3.3033800149598618e-05</v>
       </c>
       <c r="I5" s="1">
-        <v>-7.0014296356878522e-06</v>
+        <v>-6.3887438923532397e-06</v>
       </c>
       <c r="J5" s="1">
-        <v>-2.225225440791077e-05</v>
+        <v>-2.0831224319295941e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>-3.0614486621214361e-05</v>
+        <v>-2.8940468982937735e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-2.3756307200096674e-05</v>
+        <v>-2.2069757870037453e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-9.4867826717167846e-06</v>
+        <v>-9.3750701213419342e-06</v>
       </c>
       <c r="N5" s="1">
-        <v>-3.5514857081890773e-06</v>
+        <v>-3.5367276559611283e-06</v>
       </c>
       <c r="O5" s="1">
-        <v>-8.3969087295227919e-06</v>
+        <v>-8.3789181545726755e-06</v>
       </c>
       <c r="P5" s="1">
-        <v>2.3244275395470005e-06</v>
+        <v>2.3585476112795166e-06</v>
       </c>
       <c r="Q5" s="1">
-        <v>-8.3083306728247162e-06</v>
+        <v>-8.5751258739436824e-06</v>
       </c>
       <c r="R5" s="1">
-        <v>-1.3791127130437086e-07</v>
+        <v>-1.3652786989575658e-07</v>
       </c>
       <c r="S5" s="1">
-        <v>5.7755206930441918e-06</v>
+        <v>5.7070067063925211e-06</v>
       </c>
       <c r="T5" s="1">
-        <v>3.9326859065655088e-06</v>
+        <v>3.8940621158944732e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.00050506134452029186</v>
+        <v>-0.00051342405449762935</v>
       </c>
       <c r="V5" s="1">
-        <v>-3.9276490770532653e-05</v>
+        <v>-3.5504845831435116e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2122,67 +2122,67 @@
         <v>28</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.0074380518368222176</v>
+        <v>-0.0074497724869997404</v>
       </c>
       <c r="C6" s="1">
-        <v>-3.4061773709745298e-07</v>
+        <v>-3.4040753794298746e-07</v>
       </c>
       <c r="D6" s="1">
-        <v>9.2694092479948541e-10</v>
+        <v>9.2385199811314817e-10</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.3754885548264782e-05</v>
+        <v>-1.3757128124930262e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>-1.0937817760013365e-05</v>
+        <v>-1.0939333259146292e-05</v>
       </c>
       <c r="G6" s="1">
-        <v>3.3159692265053129e-07</v>
+        <v>3.3164319028547043e-07</v>
       </c>
       <c r="H6" s="1">
-        <v>2.6513957932334023e-07</v>
+        <v>2.6516732751893831e-07</v>
       </c>
       <c r="I6" s="1">
-        <v>-3.7427363328476533e-08</v>
+        <v>-3.6370896564176309e-08</v>
       </c>
       <c r="J6" s="1">
-        <v>7.540555320201622e-08</v>
+        <v>7.7671436229093508e-08</v>
       </c>
       <c r="K6" s="1">
-        <v>2.7117897793638351e-07</v>
+        <v>2.7385819875733927e-07</v>
       </c>
       <c r="L6" s="1">
-        <v>2.1009024307438583e-07</v>
+        <v>2.1275986900296261e-07</v>
       </c>
       <c r="M6" s="1">
-        <v>-5.114399103632702e-09</v>
+        <v>-5.0333516229933859e-09</v>
       </c>
       <c r="N6" s="1">
-        <v>4.5372530691248786e-08</v>
+        <v>4.5289195765508391e-08</v>
       </c>
       <c r="O6" s="1">
-        <v>1.6788789472576808e-08</v>
+        <v>1.6729153108649336e-08</v>
       </c>
       <c r="P6" s="1">
-        <v>-1.5848106904668379e-08</v>
+        <v>-1.5858799506389954e-08</v>
       </c>
       <c r="Q6" s="1">
-        <v>1.4238444213742215e-07</v>
+        <v>1.4132287867045681e-07</v>
       </c>
       <c r="R6" s="1">
-        <v>1.1605848139819005e-09</v>
+        <v>1.1631405370733722e-09</v>
       </c>
       <c r="S6" s="1">
-        <v>-8.1834175959856852e-08</v>
+        <v>-8.1984717385865682e-08</v>
       </c>
       <c r="T6" s="1">
-        <v>-6.2063398193029576e-08</v>
+        <v>-6.2087982132580119e-08</v>
       </c>
       <c r="U6" s="1">
-        <v>1.1952993746486194e-05</v>
+        <v>1.1946390546768123e-05</v>
       </c>
       <c r="V6" s="1">
-        <v>4.6580279363849994e-08</v>
+        <v>5.2168375881600214e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2190,67 +2190,67 @@
         <v>29</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.015095793384027103</v>
+        <v>-0.014989878213214694</v>
       </c>
       <c r="C7" s="1">
-        <v>-3.2716951269188252e-07</v>
+        <v>-3.3253286602651488e-07</v>
       </c>
       <c r="D7" s="1">
-        <v>7.370277783136539e-10</v>
+        <v>7.999973585082339e-10</v>
       </c>
       <c r="E7" s="1">
-        <v>-1.0871304591192617e-05</v>
+        <v>-1.0875506000596402e-05</v>
       </c>
       <c r="F7" s="1">
-        <v>-3.3076335651950156e-05</v>
+        <v>-3.3033800149598618e-05</v>
       </c>
       <c r="G7" s="1">
-        <v>2.6513957932334023e-07</v>
+        <v>2.6516732751893831e-07</v>
       </c>
       <c r="H7" s="1">
-        <v>7.7471986012717756e-07</v>
+        <v>7.7394950913456499e-07</v>
       </c>
       <c r="I7" s="1">
-        <v>7.5845612653072009e-08</v>
+        <v>6.4487637809508747e-08</v>
       </c>
       <c r="J7" s="1">
-        <v>4.0845824661898323e-07</v>
+        <v>3.8218382550819182e-07</v>
       </c>
       <c r="K7" s="1">
-        <v>6.915957620135601e-07</v>
+        <v>6.6066017521574791e-07</v>
       </c>
       <c r="L7" s="1">
-        <v>6.2290106383673911e-07</v>
+        <v>5.917300714679261e-07</v>
       </c>
       <c r="M7" s="1">
-        <v>1.1239029328960749e-07</v>
+        <v>1.1033035206826611e-07</v>
       </c>
       <c r="N7" s="1">
-        <v>7.0192990960282088e-08</v>
+        <v>6.9931427248112844e-08</v>
       </c>
       <c r="O7" s="1">
-        <v>7.9907754360265199e-08</v>
+        <v>7.9581011464590746e-08</v>
       </c>
       <c r="P7" s="1">
-        <v>-1.2595538874421535e-07</v>
+        <v>-1.2658087169194375e-07</v>
       </c>
       <c r="Q7" s="1">
-        <v>1.5073577212503051e-07</v>
+        <v>1.5584666661329271e-07</v>
       </c>
       <c r="R7" s="1">
-        <v>7.1141937707025024e-09</v>
+        <v>7.0870483391255368e-09</v>
       </c>
       <c r="S7" s="1">
-        <v>-1.4830511965655155e-07</v>
+        <v>-1.4699283544996591e-07</v>
       </c>
       <c r="T7" s="1">
-        <v>-1.2142515716290895e-07</v>
+        <v>-1.206928666367319e-07</v>
       </c>
       <c r="U7" s="1">
-        <v>1.0575391970139978e-05</v>
+        <v>1.0729735047307729e-05</v>
       </c>
       <c r="V7" s="1">
-        <v>7.0096581331090176e-07</v>
+        <v>6.309760351518194e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2258,67 +2258,67 @@
         <v>30</v>
       </c>
       <c r="B8" s="1">
-        <v>0.0050465070705230956</v>
+        <v>0.0042549741528379263</v>
       </c>
       <c r="C8" s="1">
-        <v>9.2480046709029532e-07</v>
+        <v>9.1135007744960681e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>-1.0983083483309323e-08</v>
+        <v>-1.0855251847191668e-08</v>
       </c>
       <c r="E8" s="1">
-        <v>1.2912881379908431e-06</v>
+        <v>1.2472609842455153e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>-7.0014296356878522e-06</v>
+        <v>-6.3887438923532397e-06</v>
       </c>
       <c r="G8" s="1">
-        <v>-3.7427363328476533e-08</v>
+        <v>-3.6370896564176309e-08</v>
       </c>
       <c r="H8" s="1">
-        <v>7.5845612653072009e-08</v>
+        <v>6.4487637809508747e-08</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0025751937749982877</v>
+        <v>0.0025742538963861457</v>
       </c>
       <c r="J8" s="1">
-        <v>0.0023446632275184467</v>
+        <v>0.0023438011384055877</v>
       </c>
       <c r="K8" s="1">
-        <v>0.002345287976521779</v>
+        <v>0.0023444419925009357</v>
       </c>
       <c r="L8" s="1">
-        <v>0.0023452517073691307</v>
+        <v>0.0023444138713426491</v>
       </c>
       <c r="M8" s="1">
-        <v>1.4357264027440315e-06</v>
+        <v>1.4242122838789695e-06</v>
       </c>
       <c r="N8" s="1">
-        <v>2.5849836471894524e-06</v>
+        <v>2.5706532076311886e-06</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.6530312622256748e-06</v>
+        <v>-1.6681332060152099e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>-1.3133147042815781e-06</v>
+        <v>-1.321575435754979e-06</v>
       </c>
       <c r="Q8" s="1">
-        <v>-1.2244200596531235e-06</v>
+        <v>-1.3364422972406766e-06</v>
       </c>
       <c r="R8" s="1">
-        <v>1.6149758475543714e-07</v>
+        <v>1.6178511504534661e-07</v>
       </c>
       <c r="S8" s="1">
-        <v>-4.7677060641691729e-06</v>
+        <v>-4.7806001371317606e-06</v>
       </c>
       <c r="T8" s="1">
-        <v>-1.1807720107913419e-06</v>
+        <v>-1.1735576735821121e-06</v>
       </c>
       <c r="U8" s="1">
-        <v>-0.0023826807687701941</v>
+        <v>-0.002381568505142585</v>
       </c>
       <c r="V8" s="1">
-        <v>1.585376199073887e-05</v>
+        <v>1.6043334903633863e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2326,67 +2326,67 @@
         <v>31</v>
       </c>
       <c r="B9" s="1">
-        <v>0.063223095197705442</v>
+        <v>0.061750264284701165</v>
       </c>
       <c r="C9" s="1">
-        <v>1.7908031423996577e-06</v>
+        <v>1.7503540737004424e-06</v>
       </c>
       <c r="D9" s="1">
-        <v>-2.1604064327458507e-08</v>
+        <v>-2.1192832995669312e-08</v>
       </c>
       <c r="E9" s="1">
-        <v>-2.6452284565903375e-06</v>
+        <v>-2.7455563674408398e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>-2.225225440791077e-05</v>
+        <v>-2.0831224319295941e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>7.540555320201622e-08</v>
+        <v>7.7671436229093508e-08</v>
       </c>
       <c r="H9" s="1">
-        <v>4.0845824661898323e-07</v>
+        <v>3.8218382550819182e-07</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0023446632275184467</v>
+        <v>0.0023438011384055877</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0023908646990428912</v>
+        <v>0.0023900467989215629</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0023558863104720701</v>
+        <v>0.0023550897369945221</v>
       </c>
       <c r="L9" s="1">
-        <v>0.0023563344505149178</v>
+        <v>0.0023555554812336697</v>
       </c>
       <c r="M9" s="1">
-        <v>1.0593997915102223e-06</v>
+        <v>1.0316789600331098e-06</v>
       </c>
       <c r="N9" s="1">
-        <v>2.3071502244104323e-06</v>
+        <v>2.2758934235155484e-06</v>
       </c>
       <c r="O9" s="1">
-        <v>-2.940147023990013e-06</v>
+        <v>-2.9746368927936312e-06</v>
       </c>
       <c r="P9" s="1">
-        <v>-2.6166485946111423e-06</v>
+        <v>-2.6355272818311297e-06</v>
       </c>
       <c r="Q9" s="1">
-        <v>4.2528447057868123e-06</v>
+        <v>4.0199724411629725e-06</v>
       </c>
       <c r="R9" s="1">
-        <v>1.1612560477693651e-07</v>
+        <v>1.1675627223105897e-07</v>
       </c>
       <c r="S9" s="1">
-        <v>-3.8675946223561115e-06</v>
+        <v>-3.8950289324103048e-06</v>
       </c>
       <c r="T9" s="1">
-        <v>-1.8209521309865158e-06</v>
+        <v>-1.8067447104716438e-06</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.0024078753384392118</v>
+        <v>-0.002406251074976357</v>
       </c>
       <c r="V9" s="1">
-        <v>3.5718355408363803e-05</v>
+        <v>3.5974753312202959e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2394,67 +2394,67 @@
         <v>32</v>
       </c>
       <c r="B10" s="1">
-        <v>0.12135464673295573</v>
+        <v>0.11960922049872849</v>
       </c>
       <c r="C10" s="1">
-        <v>1.4188452339631969e-06</v>
+        <v>1.3715508390223655e-06</v>
       </c>
       <c r="D10" s="1">
-        <v>-1.3428558171883629e-08</v>
+        <v>-1.294768230587386e-08</v>
       </c>
       <c r="E10" s="1">
-        <v>-8.1666654488190945e-06</v>
+        <v>-8.2845147005175181e-06</v>
       </c>
       <c r="F10" s="1">
-        <v>-3.0614486621214361e-05</v>
+        <v>-2.8940468982937735e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>2.7117897793638351e-07</v>
+        <v>2.7385819875733927e-07</v>
       </c>
       <c r="H10" s="1">
-        <v>6.915957620135601e-07</v>
+        <v>6.6066017521574791e-07</v>
       </c>
       <c r="I10" s="1">
-        <v>0.002345287976521779</v>
+        <v>0.0023444419925009357</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0023558863104720701</v>
+        <v>0.0023550897369945221</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0023774838056500802</v>
+        <v>0.0023767218898189308</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0023687210151800888</v>
+        <v>0.0023679772170254439</v>
       </c>
       <c r="M10" s="1">
-        <v>1.1075170489982664e-06</v>
+        <v>1.075270478127223e-06</v>
       </c>
       <c r="N10" s="1">
-        <v>3.1722168502777445e-06</v>
+        <v>3.135459573954926e-06</v>
       </c>
       <c r="O10" s="1">
-        <v>-2.2148197319180237e-06</v>
+        <v>-2.2556899616543873e-06</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.3296068673446323e-06</v>
+        <v>-1.3517683972636356e-06</v>
       </c>
       <c r="Q10" s="1">
-        <v>7.0383962998611255e-06</v>
+        <v>6.7620251185427792e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>1.9055666881261894e-08</v>
+        <v>1.982648669738187e-08</v>
       </c>
       <c r="S10" s="1">
-        <v>-3.7663774123584896e-06</v>
+        <v>-3.8000589294699485e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>-2.0527026931768768e-06</v>
+        <v>-2.0374395102248641e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.0024102204991367955</v>
+        <v>-0.0024084935177050028</v>
       </c>
       <c r="V10" s="1">
-        <v>4.2139696390400475e-05</v>
+        <v>4.2448934506224104e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2462,67 +2462,67 @@
         <v>33</v>
       </c>
       <c r="B11" s="1">
-        <v>0.15768187436719946</v>
+        <v>0.15584346782716701</v>
       </c>
       <c r="C11" s="1">
-        <v>3.2013446179104678e-06</v>
+        <v>3.1566827392836311e-06</v>
       </c>
       <c r="D11" s="1">
-        <v>-2.8161047602666538e-08</v>
+        <v>-2.7710325229700028e-08</v>
       </c>
       <c r="E11" s="1">
-        <v>-2.6287765468338179e-06</v>
+        <v>-2.7436377126154134e-06</v>
       </c>
       <c r="F11" s="1">
-        <v>-2.3756307200096674e-05</v>
+        <v>-2.2069757870037453e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>2.1009024307438583e-07</v>
+        <v>2.1275986900296261e-07</v>
       </c>
       <c r="H11" s="1">
-        <v>6.2290106383673911e-07</v>
+        <v>5.917300714679261e-07</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0023452517073691307</v>
+        <v>0.0023444138713426491</v>
       </c>
       <c r="J11" s="1">
-        <v>0.0023563344505149178</v>
+        <v>0.0023555554812336697</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0023687210151800888</v>
+        <v>0.0023679772170254439</v>
       </c>
       <c r="L11" s="1">
-        <v>0.002412683927032604</v>
+        <v>0.0024119768623693302</v>
       </c>
       <c r="M11" s="1">
-        <v>1.3321011196153058e-06</v>
+        <v>1.3005910054723038e-06</v>
       </c>
       <c r="N11" s="1">
-        <v>3.6807213634627577e-06</v>
+        <v>3.6436799121646932e-06</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.5452334385892967e-06</v>
+        <v>-2.5865892344896101e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>-8.7636665600980096e-07</v>
+        <v>-8.9826527139387864e-07</v>
       </c>
       <c r="Q11" s="1">
-        <v>6.8748781054710965e-06</v>
+        <v>6.5900677423163675e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>2.7143007085636777e-08</v>
+        <v>2.7941462201957259e-08</v>
       </c>
       <c r="S11" s="1">
-        <v>-3.9148515209379949e-06</v>
+        <v>-3.9496734135669586e-06</v>
       </c>
       <c r="T11" s="1">
-        <v>-1.7908129116657194e-06</v>
+        <v>-1.7755154115200012e-06</v>
       </c>
       <c r="U11" s="1">
-        <v>-0.0024648129618741279</v>
+        <v>-0.0024631745947980084</v>
       </c>
       <c r="V11" s="1">
-        <v>4.258344212992153e-05</v>
+        <v>4.2938646943580766e-05</v>
       </c>
     </row>
     <row r="12">
@@ -2530,67 +2530,67 @@
         <v>34</v>
       </c>
       <c r="B12" s="1">
-        <v>-0.01883137436931244</v>
+        <v>-0.018755787887789876</v>
       </c>
       <c r="C12" s="1">
-        <v>1.3295745918648144e-07</v>
+        <v>1.2518169036073267e-07</v>
       </c>
       <c r="D12" s="1">
-        <v>-2.384763821274194e-09</v>
+        <v>-2.2949386506853203e-09</v>
       </c>
       <c r="E12" s="1">
-        <v>-2.0650137708531209e-06</v>
+        <v>-2.0720617891480734e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>-9.4867826717167846e-06</v>
+        <v>-9.3750701213419342e-06</v>
       </c>
       <c r="G12" s="1">
-        <v>-5.114399103632702e-09</v>
+        <v>-5.0333516229933859e-09</v>
       </c>
       <c r="H12" s="1">
-        <v>1.1239029328960749e-07</v>
+        <v>1.1033035206826611e-07</v>
       </c>
       <c r="I12" s="1">
-        <v>1.4357264027440315e-06</v>
+        <v>1.4242122838789695e-06</v>
       </c>
       <c r="J12" s="1">
-        <v>1.0593997915102223e-06</v>
+        <v>1.0316789600331098e-06</v>
       </c>
       <c r="K12" s="1">
-        <v>1.1075170489982664e-06</v>
+        <v>1.075270478127223e-06</v>
       </c>
       <c r="L12" s="1">
-        <v>1.3321011196153058e-06</v>
+        <v>1.3005910054723038e-06</v>
       </c>
       <c r="M12" s="1">
-        <v>8.9078365797503958e-05</v>
+        <v>8.9097519237223914e-05</v>
       </c>
       <c r="N12" s="1">
-        <v>4.3242642002571517e-05</v>
+        <v>4.325226483198017e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>4.3368815975347805e-05</v>
+        <v>4.3378147070464263e-05</v>
       </c>
       <c r="P12" s="1">
-        <v>4.3222419268780515e-05</v>
+        <v>4.3232052230034983e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>2.3848257158140883e-06</v>
+        <v>2.3803196683838153e-06</v>
       </c>
       <c r="R12" s="1">
-        <v>-8.0400286180602205e-08</v>
+        <v>-8.0394571745348156e-08</v>
       </c>
       <c r="S12" s="1">
-        <v>-7.3524197521278799e-07</v>
+        <v>-7.3521875261736548e-07</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.11659332541522e-07</v>
+        <v>-6.1072792003730766e-07</v>
       </c>
       <c r="U12" s="1">
-        <v>-3.5050335164451543e-05</v>
+        <v>-3.4856391606654568e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>2.1229177514151522e-06</v>
+        <v>2.0462537672929323e-06</v>
       </c>
     </row>
     <row r="13">
@@ -2598,67 +2598,67 @@
         <v>35</v>
       </c>
       <c r="B13" s="1">
-        <v>0.070948013712757108</v>
+        <v>0.071101387316733211</v>
       </c>
       <c r="C13" s="1">
-        <v>-7.8782222113765361e-08</v>
+        <v>-8.301742021195137e-08</v>
       </c>
       <c r="D13" s="1">
-        <v>-2.7560553429402627e-10</v>
+        <v>-2.2320097786528645e-10</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.1762409589631016e-06</v>
+        <v>-2.1752688267601599e-06</v>
       </c>
       <c r="F13" s="1">
-        <v>-3.5514857081890773e-06</v>
+        <v>-3.5367276559611283e-06</v>
       </c>
       <c r="G13" s="1">
-        <v>4.5372530691248786e-08</v>
+        <v>4.5289195765508391e-08</v>
       </c>
       <c r="H13" s="1">
-        <v>7.0192990960282088e-08</v>
+        <v>6.9931427248112844e-08</v>
       </c>
       <c r="I13" s="1">
-        <v>2.5849836471894524e-06</v>
+        <v>2.5706532076311886e-06</v>
       </c>
       <c r="J13" s="1">
-        <v>2.3071502244104323e-06</v>
+        <v>2.2758934235155484e-06</v>
       </c>
       <c r="K13" s="1">
-        <v>3.1722168502777445e-06</v>
+        <v>3.135459573954926e-06</v>
       </c>
       <c r="L13" s="1">
-        <v>3.6807213634627577e-06</v>
+        <v>3.6436799121646932e-06</v>
       </c>
       <c r="M13" s="1">
-        <v>4.3242642002571517e-05</v>
+        <v>4.325226483198017e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>0.00011626413352695539</v>
+        <v>0.00011629273205886832</v>
       </c>
       <c r="O13" s="1">
-        <v>4.3231771653138556e-05</v>
+        <v>4.3243443007501227e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>4.3189846423304963e-05</v>
+        <v>4.3200860684166318e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>2.9172347827134761e-06</v>
+        <v>2.927320973023216e-06</v>
       </c>
       <c r="R13" s="1">
-        <v>-6.5281067389424343e-08</v>
+        <v>-6.5312731051997726e-08</v>
       </c>
       <c r="S13" s="1">
-        <v>-1.5478352479915231e-06</v>
+        <v>-1.5459528768192217e-06</v>
       </c>
       <c r="T13" s="1">
-        <v>-1.033302400926882e-06</v>
+        <v>-1.0334898509007329e-06</v>
       </c>
       <c r="U13" s="1">
-        <v>-3.4862884281745334e-05</v>
+        <v>-3.47396139401508e-05</v>
       </c>
       <c r="V13" s="1">
-        <v>-3.2359137468795345e-07</v>
+        <v>-4.0457243312727222e-07</v>
       </c>
     </row>
     <row r="14">
@@ -2666,67 +2666,67 @@
         <v>36</v>
       </c>
       <c r="B14" s="1">
-        <v>-0.014457202728520621</v>
+        <v>-0.014281735110075093</v>
       </c>
       <c r="C14" s="1">
-        <v>-1.8770160486494024e-07</v>
+        <v>-1.9284313821271901e-07</v>
       </c>
       <c r="D14" s="1">
-        <v>1.350144840732081e-09</v>
+        <v>1.4132086029811441e-09</v>
       </c>
       <c r="E14" s="1">
-        <v>-2.2079654469453422e-06</v>
+        <v>-2.2088021276361257e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-8.3969087295227919e-06</v>
+        <v>-8.3789181545726755e-06</v>
       </c>
       <c r="G14" s="1">
-        <v>1.6788789472576808e-08</v>
+        <v>1.6729153108649336e-08</v>
       </c>
       <c r="H14" s="1">
-        <v>7.9907754360265199e-08</v>
+        <v>7.9581011464590746e-08</v>
       </c>
       <c r="I14" s="1">
-        <v>-1.6530312622256748e-06</v>
+        <v>-1.6681332060152099e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-2.940147023990013e-06</v>
+        <v>-2.9746368927936312e-06</v>
       </c>
       <c r="K14" s="1">
-        <v>-2.2148197319180237e-06</v>
+        <v>-2.2556899616543873e-06</v>
       </c>
       <c r="L14" s="1">
-        <v>-2.5452334385892967e-06</v>
+        <v>-2.5865892344896101e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>4.3368815975347805e-05</v>
+        <v>4.3378147070464263e-05</v>
       </c>
       <c r="N14" s="1">
-        <v>4.3231771653138556e-05</v>
+        <v>4.3243443007501227e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>8.7678717895281358e-05</v>
+        <v>8.7701020575262501e-05</v>
       </c>
       <c r="P14" s="1">
-        <v>4.3251566322441582e-05</v>
+        <v>4.3262518912864467e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>3.2070390636034681e-06</v>
+        <v>3.2185945542564912e-06</v>
       </c>
       <c r="R14" s="1">
-        <v>-9.3537860843192442e-08</v>
+        <v>-9.3570588375412095e-08</v>
       </c>
       <c r="S14" s="1">
-        <v>3.4039304797858591e-08</v>
+        <v>3.5898452664410837e-08</v>
       </c>
       <c r="T14" s="1">
-        <v>5.2069180858575609e-07</v>
+        <v>5.208744419642893e-07</v>
       </c>
       <c r="U14" s="1">
-        <v>-2.3907359542745653e-05</v>
+        <v>-2.3759122444400401e-05</v>
       </c>
       <c r="V14" s="1">
-        <v>-2.7225517226161014e-07</v>
+        <v>-3.6643204804072815e-07</v>
       </c>
     </row>
     <row r="15">
@@ -2734,67 +2734,67 @@
         <v>37</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.093985384974738698</v>
+        <v>-0.093898760856356692</v>
       </c>
       <c r="C15" s="1">
-        <v>-3.5714799957775621e-08</v>
+        <v>-3.9233213741386746e-08</v>
       </c>
       <c r="D15" s="1">
-        <v>2.2462124056915422e-10</v>
+        <v>2.6712929934848926e-10</v>
       </c>
       <c r="E15" s="1">
-        <v>4.7825852857397362e-07</v>
+        <v>4.7711716894758409e-07</v>
       </c>
       <c r="F15" s="1">
-        <v>2.3244275395470005e-06</v>
+        <v>2.3585476112795166e-06</v>
       </c>
       <c r="G15" s="1">
-        <v>-1.5848106904668379e-08</v>
+        <v>-1.5858799506389954e-08</v>
       </c>
       <c r="H15" s="1">
-        <v>-1.2595538874421535e-07</v>
+        <v>-1.2658087169194375e-07</v>
       </c>
       <c r="I15" s="1">
-        <v>-1.3133147042815781e-06</v>
+        <v>-1.321575435754979e-06</v>
       </c>
       <c r="J15" s="1">
-        <v>-2.6166485946111423e-06</v>
+        <v>-2.6355272818311297e-06</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.3296068673446323e-06</v>
+        <v>-1.3517683972636356e-06</v>
       </c>
       <c r="L15" s="1">
-        <v>-8.7636665600980096e-07</v>
+        <v>-8.9826527139387864e-07</v>
       </c>
       <c r="M15" s="1">
-        <v>4.3222419268780515e-05</v>
+        <v>4.3232052230034983e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>4.3189846423304963e-05</v>
+        <v>4.3200860684166318e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>4.3251566322441582e-05</v>
+        <v>4.3262518912864467e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>6.1015307063454786e-05</v>
+        <v>6.1030483683761863e-05</v>
       </c>
       <c r="Q15" s="1">
-        <v>1.2964639162865686e-06</v>
+        <v>1.3005334950633938e-06</v>
       </c>
       <c r="R15" s="1">
-        <v>-6.7162498856225911e-08</v>
+        <v>-6.7173712309237281e-08</v>
       </c>
       <c r="S15" s="1">
-        <v>-8.5780432772668374e-07</v>
+        <v>-8.5706729040026187e-07</v>
       </c>
       <c r="T15" s="1">
-        <v>-9.7475367182159543e-07</v>
+        <v>-9.7496809407210587e-07</v>
       </c>
       <c r="U15" s="1">
-        <v>-3.2890408328685417e-05</v>
+        <v>-3.2800488574843036e-05</v>
       </c>
       <c r="V15" s="1">
-        <v>2.9748637335805763e-07</v>
+        <v>2.4439287927868035e-07</v>
       </c>
     </row>
     <row r="16">
@@ -2802,67 +2802,67 @@
         <v>38</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.0085684740167149762</v>
+        <v>-0.0072584953480051917</v>
       </c>
       <c r="C16" s="1">
-        <v>2.5507678301275693e-06</v>
+        <v>2.5309332504622639e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>-3.2588011086063637e-08</v>
+        <v>-3.2324504200035493e-08</v>
       </c>
       <c r="E16" s="1">
-        <v>-2.3707761787512191e-06</v>
+        <v>-2.3437277245262187e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>-8.3083306728247162e-06</v>
+        <v>-8.5751258739436824e-06</v>
       </c>
       <c r="G16" s="1">
-        <v>1.4238444213742215e-07</v>
+        <v>1.4132287867045681e-07</v>
       </c>
       <c r="H16" s="1">
-        <v>1.5073577212503051e-07</v>
+        <v>1.5584666661329271e-07</v>
       </c>
       <c r="I16" s="1">
-        <v>-1.2244200596531235e-06</v>
+        <v>-1.3364422972406766e-06</v>
       </c>
       <c r="J16" s="1">
-        <v>4.2528447057868123e-06</v>
+        <v>4.0199724411629725e-06</v>
       </c>
       <c r="K16" s="1">
-        <v>7.0383962998611255e-06</v>
+        <v>6.7620251185427792e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>6.8748781054710965e-06</v>
+        <v>6.5900677423163675e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>2.3848257158140883e-06</v>
+        <v>2.3803196683838153e-06</v>
       </c>
       <c r="N16" s="1">
-        <v>2.9172347827134761e-06</v>
+        <v>2.927320973023216e-06</v>
       </c>
       <c r="O16" s="1">
-        <v>3.2070390636034681e-06</v>
+        <v>3.2185945542564912e-06</v>
       </c>
       <c r="P16" s="1">
-        <v>1.2964639162865686e-06</v>
+        <v>1.3005334950633938e-06</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0002882969017654703</v>
+        <v>0.00028827161529422859</v>
       </c>
       <c r="R16" s="1">
-        <v>1.1608439504657209e-07</v>
+        <v>1.1560717435372507e-07</v>
       </c>
       <c r="S16" s="1">
-        <v>-1.2220548841542171e-06</v>
+        <v>-1.1999202109115233e-06</v>
       </c>
       <c r="T16" s="1">
-        <v>-9.1994884872467018e-07</v>
+        <v>-9.1893681315332813e-07</v>
       </c>
       <c r="U16" s="1">
-        <v>-7.3114358578189349e-05</v>
+        <v>-7.2343188248347325e-05</v>
       </c>
       <c r="V16" s="1">
-        <v>-1.0038749781514762e-05</v>
+        <v>-1.0620128356295156e-05</v>
       </c>
     </row>
     <row r="17">
@@ -2870,67 +2870,67 @@
         <v>39</v>
       </c>
       <c r="B17" s="1">
-        <v>0.0050996772116353329</v>
+        <v>0.0050955274814060147</v>
       </c>
       <c r="C17" s="1">
-        <v>3.314239666872741e-09</v>
+        <v>3.3496444263259769e-09</v>
       </c>
       <c r="D17" s="1">
-        <v>-1.2929205771067281e-10</v>
+        <v>-1.2978966376503602e-10</v>
       </c>
       <c r="E17" s="1">
-        <v>6.297365344799205e-08</v>
+        <v>6.2885073030450104e-08</v>
       </c>
       <c r="F17" s="1">
-        <v>-1.3791127130437086e-07</v>
+        <v>-1.3652786989575658e-07</v>
       </c>
       <c r="G17" s="1">
-        <v>1.1605848139819005e-09</v>
+        <v>1.1631405370733722e-09</v>
       </c>
       <c r="H17" s="1">
-        <v>7.1141937707025024e-09</v>
+        <v>7.0870483391255368e-09</v>
       </c>
       <c r="I17" s="1">
-        <v>1.6149758475543714e-07</v>
+        <v>1.6178511504534661e-07</v>
       </c>
       <c r="J17" s="1">
-        <v>1.1612560477693651e-07</v>
+        <v>1.1675627223105897e-07</v>
       </c>
       <c r="K17" s="1">
-        <v>1.9055666881261894e-08</v>
+        <v>1.982648669738187e-08</v>
       </c>
       <c r="L17" s="1">
-        <v>2.7143007085636777e-08</v>
+        <v>2.7941462201957259e-08</v>
       </c>
       <c r="M17" s="1">
-        <v>-8.0400286180602205e-08</v>
+        <v>-8.0394571745348156e-08</v>
       </c>
       <c r="N17" s="1">
-        <v>-6.5281067389424343e-08</v>
+        <v>-6.5312731051997726e-08</v>
       </c>
       <c r="O17" s="1">
-        <v>-9.3537860843192442e-08</v>
+        <v>-9.3570588375412095e-08</v>
       </c>
       <c r="P17" s="1">
-        <v>-6.7162498856225911e-08</v>
+        <v>-6.7173712309237281e-08</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.1608439504657209e-07</v>
+        <v>1.1560717435372507e-07</v>
       </c>
       <c r="R17" s="1">
-        <v>4.9368276636717e-08</v>
+        <v>4.9361502634792301e-08</v>
       </c>
       <c r="S17" s="1">
-        <v>-7.6464913768009493e-07</v>
+        <v>-7.6459043214152382e-07</v>
       </c>
       <c r="T17" s="1">
-        <v>-9.1886560979852282e-07</v>
+        <v>-9.1870749892931487e-07</v>
       </c>
       <c r="U17" s="1">
-        <v>-5.2683618810882036e-06</v>
+        <v>-5.2692320917089123e-06</v>
       </c>
       <c r="V17" s="1">
-        <v>4.2722717494677886e-08</v>
+        <v>4.4423864674554577e-08</v>
       </c>
     </row>
     <row r="18">
@@ -2938,67 +2938,67 @@
         <v>40</v>
       </c>
       <c r="B18" s="1">
-        <v>0.048950442676558924</v>
+        <v>0.049146284034265179</v>
       </c>
       <c r="C18" s="1">
-        <v>-1.1123191806743202e-07</v>
+        <v>-1.1212055725750406e-07</v>
       </c>
       <c r="D18" s="1">
-        <v>2.7654401231375974e-09</v>
+        <v>2.7805036276645605e-09</v>
       </c>
       <c r="E18" s="1">
-        <v>2.7686593490405425e-06</v>
+        <v>2.774102748389747e-06</v>
       </c>
       <c r="F18" s="1">
-        <v>5.7755206930441918e-06</v>
+        <v>5.7070067063925211e-06</v>
       </c>
       <c r="G18" s="1">
-        <v>-8.1834175959856852e-08</v>
+        <v>-8.1984717385865682e-08</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.4830511965655155e-07</v>
+        <v>-1.4699283544996591e-07</v>
       </c>
       <c r="I18" s="1">
-        <v>-4.7677060641691729e-06</v>
+        <v>-4.7806001371317606e-06</v>
       </c>
       <c r="J18" s="1">
-        <v>-3.8675946223561115e-06</v>
+        <v>-3.8950289324103048e-06</v>
       </c>
       <c r="K18" s="1">
-        <v>-3.7663774123584896e-06</v>
+        <v>-3.8000589294699485e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>-3.9148515209379949e-06</v>
+        <v>-3.9496734135669586e-06</v>
       </c>
       <c r="M18" s="1">
-        <v>-7.3524197521278799e-07</v>
+        <v>-7.3521875261736548e-07</v>
       </c>
       <c r="N18" s="1">
-        <v>-1.5478352479915231e-06</v>
+        <v>-1.5459528768192217e-06</v>
       </c>
       <c r="O18" s="1">
-        <v>3.4039304797858591e-08</v>
+        <v>3.5898452664410837e-08</v>
       </c>
       <c r="P18" s="1">
-        <v>-8.5780432772668374e-07</v>
+        <v>-8.5706729040026187e-07</v>
       </c>
       <c r="Q18" s="1">
-        <v>-1.2220548841542171e-06</v>
+        <v>-1.1999202109115233e-06</v>
       </c>
       <c r="R18" s="1">
-        <v>-7.6464913768009493e-07</v>
+        <v>-7.6459043214152382e-07</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00013432519009756437</v>
+        <v>0.00013435312681389508</v>
       </c>
       <c r="T18" s="1">
-        <v>2.2724423733835991e-05</v>
+        <v>2.2724007635878334e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>7.8539971376796221e-05</v>
+        <v>7.8586273822234793e-05</v>
       </c>
       <c r="V18" s="1">
-        <v>-2.1759133442782147e-06</v>
+        <v>-2.2497959030841101e-06</v>
       </c>
     </row>
     <row r="19">
@@ -3006,67 +3006,67 @@
         <v>41</v>
       </c>
       <c r="B19" s="1">
-        <v>0.02171249411169408</v>
+        <v>0.021678967343984418</v>
       </c>
       <c r="C19" s="1">
-        <v>-4.6588364297259917e-08</v>
+        <v>-4.3383420282702772e-08</v>
       </c>
       <c r="D19" s="1">
-        <v>1.8246189847060525e-09</v>
+        <v>1.7869368223315584e-09</v>
       </c>
       <c r="E19" s="1">
-        <v>1.5283742408599028e-06</v>
+        <v>1.5315978668998704e-06</v>
       </c>
       <c r="F19" s="1">
-        <v>3.9326859065655088e-06</v>
+        <v>3.8940621158944732e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>-6.2063398193029576e-08</v>
+        <v>-6.2087982132580119e-08</v>
       </c>
       <c r="H19" s="1">
-        <v>-1.2142515716290895e-07</v>
+        <v>-1.206928666367319e-07</v>
       </c>
       <c r="I19" s="1">
-        <v>-1.1807720107913419e-06</v>
+        <v>-1.1735576735821121e-06</v>
       </c>
       <c r="J19" s="1">
-        <v>-1.8209521309865158e-06</v>
+        <v>-1.8067447104716438e-06</v>
       </c>
       <c r="K19" s="1">
-        <v>-2.0527026931768768e-06</v>
+        <v>-2.0374395102248641e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>-1.7908129116657194e-06</v>
+        <v>-1.7755154115200012e-06</v>
       </c>
       <c r="M19" s="1">
-        <v>-6.11659332541522e-07</v>
+        <v>-6.1072792003730766e-07</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.033302400926882e-06</v>
+        <v>-1.0334898509007329e-06</v>
       </c>
       <c r="O19" s="1">
-        <v>5.2069180858575609e-07</v>
+        <v>5.208744419642893e-07</v>
       </c>
       <c r="P19" s="1">
-        <v>-9.7475367182159543e-07</v>
+        <v>-9.7496809407210587e-07</v>
       </c>
       <c r="Q19" s="1">
-        <v>-9.1994884872467018e-07</v>
+        <v>-9.1893681315332813e-07</v>
       </c>
       <c r="R19" s="1">
-        <v>-9.1886560979852282e-07</v>
+        <v>-9.1870749892931487e-07</v>
       </c>
       <c r="S19" s="1">
-        <v>2.2724423733835991e-05</v>
+        <v>2.2724007635878334e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.00014598545357753272</v>
+        <v>0.00014601652044787737</v>
       </c>
       <c r="U19" s="1">
-        <v>9.2184140891157787e-05</v>
+        <v>9.2079393729839609e-05</v>
       </c>
       <c r="V19" s="1">
-        <v>-8.3090774197963953e-07</v>
+        <v>-7.9972625649890685e-07</v>
       </c>
     </row>
     <row r="20">
@@ -3074,67 +3074,67 @@
         <v>42</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.013485659611445679</v>
+        <v>-0.012165956366075051</v>
       </c>
       <c r="C20" s="1">
-        <v>-7.4613092364366954e-05</v>
+        <v>-7.420896334968692e-05</v>
       </c>
       <c r="D20" s="1">
-        <v>7.3423983532499709e-07</v>
+        <v>7.2968350130993608e-07</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.0005590087981275397</v>
+        <v>-0.00055861273138013462</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.00050506134452029186</v>
+        <v>-0.00051342405449762935</v>
       </c>
       <c r="G20" s="1">
-        <v>1.1952993746486194e-05</v>
+        <v>1.1946390546768123e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>1.0575391970139978e-05</v>
+        <v>1.0729735047307729e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>-0.0023826807687701941</v>
+        <v>-0.002381568505142585</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.0024078753384392118</v>
+        <v>-0.002406251074976357</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.0024102204991367955</v>
+        <v>-0.0024084935177050028</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.0024648129618741279</v>
+        <v>-0.0024631745947980084</v>
       </c>
       <c r="M20" s="1">
-        <v>-3.5050335164451543e-05</v>
+        <v>-3.4856391606654568e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-3.4862884281745334e-05</v>
+        <v>-3.47396139401508e-05</v>
       </c>
       <c r="O20" s="1">
-        <v>-2.3907359542745653e-05</v>
+        <v>-2.3759122444400401e-05</v>
       </c>
       <c r="P20" s="1">
-        <v>-3.2890408328685417e-05</v>
+        <v>-3.2800488574843036e-05</v>
       </c>
       <c r="Q20" s="1">
-        <v>-7.3114358578189349e-05</v>
+        <v>-7.2343188248347325e-05</v>
       </c>
       <c r="R20" s="1">
-        <v>-5.2683618810882036e-06</v>
+        <v>-5.2692320917089123e-06</v>
       </c>
       <c r="S20" s="1">
-        <v>7.8539971376796221e-05</v>
+        <v>7.8586273822234793e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>9.2184140891157787e-05</v>
+        <v>9.2079393729839609e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0048242551243464164</v>
+        <v>0.0048137640523362663</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.00018070319736963292</v>
+        <v>-0.00017858662094370287</v>
       </c>
     </row>
     <row r="21">
@@ -3142,67 +3142,67 @@
         <v>43</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.16586138492645466</v>
+        <v>-0.16950523502889306</v>
       </c>
       <c r="C21" s="1">
-        <v>6.0239027218038284e-06</v>
+        <v>5.9059197217351462e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>-7.2516605912914439e-08</v>
+        <v>-7.1289576428991611e-08</v>
       </c>
       <c r="E21" s="1">
-        <v>1.3285894679176042e-06</v>
+        <v>1.070555011483761e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-3.9276490770532653e-05</v>
+        <v>-3.5504845831435116e-05</v>
       </c>
       <c r="G21" s="1">
-        <v>4.6580279363849994e-08</v>
+        <v>5.2168375881600214e-08</v>
       </c>
       <c r="H21" s="1">
-        <v>7.0096581331090176e-07</v>
+        <v>6.309760351518194e-07</v>
       </c>
       <c r="I21" s="1">
-        <v>1.585376199073887e-05</v>
+        <v>1.6043334903633863e-05</v>
       </c>
       <c r="J21" s="1">
-        <v>3.5718355408363803e-05</v>
+        <v>3.5974753312202959e-05</v>
       </c>
       <c r="K21" s="1">
-        <v>4.2139696390400475e-05</v>
+        <v>4.2448934506224104e-05</v>
       </c>
       <c r="L21" s="1">
-        <v>4.258344212992153e-05</v>
+        <v>4.2938646943580766e-05</v>
       </c>
       <c r="M21" s="1">
-        <v>2.1229177514151522e-06</v>
+        <v>2.0462537672929323e-06</v>
       </c>
       <c r="N21" s="1">
-        <v>-3.2359137468795345e-07</v>
+        <v>-4.0457243312727222e-07</v>
       </c>
       <c r="O21" s="1">
-        <v>-2.7225517226161014e-07</v>
+        <v>-3.6643204804072815e-07</v>
       </c>
       <c r="P21" s="1">
-        <v>2.9748637335805763e-07</v>
+        <v>2.4439287927868035e-07</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.0038749781514762e-05</v>
+        <v>-1.0620128356295156e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>4.2722717494677886e-08</v>
+        <v>4.4423864674554577e-08</v>
       </c>
       <c r="S21" s="1">
-        <v>-2.1759133442782147e-06</v>
+        <v>-2.2497959030841101e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>-8.3090774197963953e-07</v>
+        <v>-7.9972625649890685e-07</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.00018070319736963292</v>
+        <v>-0.00017858662094370287</v>
       </c>
       <c r="V21" s="1">
-        <v>9.4055708629224263e-05</v>
+        <v>9.455395488049534e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3290,70 +3290,70 @@
         <v>45</v>
       </c>
       <c r="B2" s="1">
-        <v>0.75914800937421323</v>
+        <v>0.75911852047262818</v>
       </c>
       <c r="C2" s="1">
-        <v>9.1402781963909765e-06</v>
+        <v>9.1246842593135824e-06</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.6955652157707165e-07</v>
+        <v>-3.8761589969549513e-07</v>
       </c>
       <c r="E2" s="1">
-        <v>2.7207357190041678e-09</v>
+        <v>2.932520261146419e-09</v>
       </c>
       <c r="F2" s="1">
-        <v>8.9292156050020496e-07</v>
+        <v>9.0045670746943008e-07</v>
       </c>
       <c r="G2" s="1">
-        <v>2.9632582600010372e-07</v>
+        <v>3.2133936312615747e-07</v>
       </c>
       <c r="H2" s="1">
-        <v>7.9195540824657052e-08</v>
+        <v>7.9054665100929526e-08</v>
       </c>
       <c r="I2" s="1">
-        <v>1.2936363874674917e-07</v>
+        <v>1.2912745000777879e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>-1.329576166668261e-06</v>
+        <v>-1.3972706667857241e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>-2.1154160469521786e-06</v>
+        <v>-2.2200563413788758e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.575516174145509e-06</v>
+        <v>-2.6907319500682823e-06</v>
       </c>
       <c r="M2" s="1">
-        <v>-3.0398976712361011e-06</v>
+        <v>-3.1597600781694574e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>-6.8894745889296805e-08</v>
+        <v>-7.3779791649479002e-08</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.0461586583745925e-07</v>
+        <v>-2.0249720190202802e-07</v>
       </c>
       <c r="P2" s="1">
-        <v>-1.612995692623056e-08</v>
+        <v>-1.3117577463417174e-08</v>
       </c>
       <c r="Q2" s="1">
-        <v>4.1253785063112049e-07</v>
+        <v>4.122174321803317e-07</v>
       </c>
       <c r="R2" s="1">
-        <v>-5.3985273628379837e-07</v>
+        <v>-5.3120779209500691e-07</v>
       </c>
       <c r="S2" s="1">
-        <v>-3.1725445782703972e-08</v>
+        <v>-3.1817927415252808e-08</v>
       </c>
       <c r="T2" s="1">
-        <v>-5.7451745290199412e-07</v>
+        <v>-5.5640088738611438e-07</v>
       </c>
       <c r="U2" s="1">
-        <v>-3.3993745147163856e-07</v>
+        <v>-3.3266569904529709e-07</v>
       </c>
       <c r="V2" s="1">
-        <v>1.7306224963702015e-06</v>
+        <v>2.2812835583347253e-06</v>
       </c>
       <c r="W2" s="1">
-        <v>-8.6087834123038204e-07</v>
+        <v>-1.2052295381251564e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3361,70 +3361,70 @@
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>0.015570992678284885</v>
+        <v>0.018247304342652936</v>
       </c>
       <c r="C3" s="1">
-        <v>-3.6955652157707165e-07</v>
+        <v>-3.8761589969549513e-07</v>
       </c>
       <c r="D3" s="1">
-        <v>1.335129241555279e-05</v>
+        <v>1.3880652452017836e-05</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.5322823428338972e-07</v>
+        <v>-1.5932046889636831e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>-1.0827915443886774e-06</v>
+        <v>-1.3320288115875471e-06</v>
       </c>
       <c r="G3" s="1">
-        <v>-2.1509982390282668e-05</v>
+        <v>-2.2019075587858062e-05</v>
       </c>
       <c r="H3" s="1">
-        <v>-1.2309732383803699e-07</v>
+        <v>-1.2396387066827486e-07</v>
       </c>
       <c r="I3" s="1">
-        <v>1.1650385410440496e-07</v>
+        <v>1.1278652609729893e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>4.3092976382750868e-05</v>
+        <v>4.5048207451597167e-05</v>
       </c>
       <c r="K3" s="1">
-        <v>6.6000108741650563e-05</v>
+        <v>6.8926678720369048e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>7.3267008214151325e-05</v>
+        <v>7.6498422981173075e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>7.7565540860454331e-05</v>
+        <v>8.0982697251160622e-05</v>
       </c>
       <c r="N3" s="1">
-        <v>3.2895653087975842e-06</v>
+        <v>3.4384966998311995e-06</v>
       </c>
       <c r="O3" s="1">
-        <v>-9.9589338257899275e-07</v>
+        <v>-1.0461771274237672e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>-1.7693611483057637e-06</v>
+        <v>-1.8316142196929856e-06</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.2966564623322738e-07</v>
+        <v>-1.3243498528409269e-07</v>
       </c>
       <c r="R3" s="1">
-        <v>-7.6007482328904806e-07</v>
+        <v>-7.0880600833410249e-07</v>
       </c>
       <c r="S3" s="1">
-        <v>-3.2161260280618683e-09</v>
+        <v>-4.812061892745527e-09</v>
       </c>
       <c r="T3" s="1">
-        <v>-9.6370431985031101e-06</v>
+        <v>-1.006105568865197e-05</v>
       </c>
       <c r="U3" s="1">
-        <v>-2.8203116859035689e-06</v>
+        <v>-2.9095754039691796e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>-0.00037010256147277699</v>
+        <v>-0.00038495425942503095</v>
       </c>
       <c r="W3" s="1">
-        <v>0.00021486155085840661</v>
+        <v>0.00022375527358854146</v>
       </c>
     </row>
     <row r="4">
@@ -3432,70 +3432,70 @@
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.00014573624308038605</v>
+        <v>-0.0001766540024118361</v>
       </c>
       <c r="C4" s="1">
-        <v>2.7207357190041678e-09</v>
+        <v>2.932520261146419e-09</v>
       </c>
       <c r="D4" s="1">
-        <v>-1.5322823428338972e-07</v>
+        <v>-1.5932046889636831e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>1.770975645315036e-09</v>
+        <v>1.8412931105001022e-09</v>
       </c>
       <c r="F4" s="1">
-        <v>5.3668339660879405e-08</v>
+        <v>5.7252741674794346e-08</v>
       </c>
       <c r="G4" s="1">
-        <v>2.9028587513921156e-07</v>
+        <v>2.9687740438204209e-07</v>
       </c>
       <c r="H4" s="1">
-        <v>4.0756633435764367e-10</v>
+        <v>4.0074520573018963e-10</v>
       </c>
       <c r="I4" s="1">
-        <v>-2.3745246364985281e-09</v>
+        <v>-2.3483078130803554e-09</v>
       </c>
       <c r="J4" s="1">
-        <v>-4.9835048261834688e-07</v>
+        <v>-5.2094380171543953e-07</v>
       </c>
       <c r="K4" s="1">
-        <v>-7.6301520504357469e-07</v>
+        <v>-7.9682944650752459e-07</v>
       </c>
       <c r="L4" s="1">
-        <v>-8.4514173320042382e-07</v>
+        <v>-8.8244724898383903e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>-8.9166175463450808e-07</v>
+        <v>-9.3105495540308926e-07</v>
       </c>
       <c r="N4" s="1">
-        <v>-3.8328008832915859e-08</v>
+        <v>-4.0056952880177933e-08</v>
       </c>
       <c r="O4" s="1">
-        <v>1.1294875937742779e-08</v>
+        <v>1.1872323243293416e-08</v>
       </c>
       <c r="P4" s="1">
-        <v>2.0046074731730839e-08</v>
+        <v>2.0757870873618325e-08</v>
       </c>
       <c r="Q4" s="1">
-        <v>1.2296963214623994e-09</v>
+        <v>1.2577286622741999e-09</v>
       </c>
       <c r="R4" s="1">
-        <v>8.0716558805951755e-09</v>
+        <v>7.4781631812165795e-09</v>
       </c>
       <c r="S4" s="1">
-        <v>-1.0452519450567112e-11</v>
+        <v>7.9792517690732846e-12</v>
       </c>
       <c r="T4" s="1">
-        <v>1.1182305324956598e-07</v>
+        <v>1.1671263077679052e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>3.3163610931909897e-08</v>
+        <v>3.4181509813252506e-08</v>
       </c>
       <c r="V4" s="1">
-        <v>4.2390165884613272e-06</v>
+        <v>4.4097184882505079e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>-2.4830711083232331e-06</v>
+        <v>-2.5858404374380383e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3503,70 +3503,70 @@
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.017488784563135275</v>
+        <v>-0.018743565673470582</v>
       </c>
       <c r="C5" s="1">
-        <v>8.9292156050020496e-07</v>
+        <v>9.0045670746943008e-07</v>
       </c>
       <c r="D5" s="1">
-        <v>-1.0827915443886774e-06</v>
+        <v>-1.3320288115875471e-06</v>
       </c>
       <c r="E5" s="1">
-        <v>5.3668339660879405e-08</v>
+        <v>5.7252741674794346e-08</v>
       </c>
       <c r="F5" s="1">
-        <v>0.00027209543309126037</v>
+        <v>0.00027663143217428193</v>
       </c>
       <c r="G5" s="1">
-        <v>0.00016680955575011083</v>
+        <v>0.00016997975435260678</v>
       </c>
       <c r="H5" s="1">
-        <v>-5.9684630632905688e-06</v>
+        <v>-6.0635774259102881e-06</v>
       </c>
       <c r="I5" s="1">
-        <v>-3.6456973088532176e-06</v>
+        <v>-3.7068319219996309e-06</v>
       </c>
       <c r="J5" s="1">
-        <v>-1.9132389603419844e-05</v>
+        <v>-2.0445660743214189e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>-3.0578168031125734e-05</v>
+        <v>-3.2559083094358025e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-3.5678410029623528e-05</v>
+        <v>-3.7895811975724425e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-3.3240721594389195e-05</v>
+        <v>-3.5469765605325294e-05</v>
       </c>
       <c r="N5" s="1">
-        <v>-3.7267833670423571e-06</v>
+        <v>-3.8617499870034406e-06</v>
       </c>
       <c r="O5" s="1">
-        <v>5.9469346436467045e-07</v>
+        <v>6.3163497138528684e-07</v>
       </c>
       <c r="P5" s="1">
-        <v>-9.5376204999818191e-07</v>
+        <v>-9.3578995897833999e-07</v>
       </c>
       <c r="Q5" s="1">
-        <v>5.8032549033180113e-07</v>
+        <v>5.9619424435986299e-07</v>
       </c>
       <c r="R5" s="1">
-        <v>-4.317819622510065e-07</v>
+        <v>-4.3061894784281215e-07</v>
       </c>
       <c r="S5" s="1">
-        <v>2.1952956958122924e-08</v>
+        <v>2.2706880811575285e-08</v>
       </c>
       <c r="T5" s="1">
-        <v>4.5778864452402758e-06</v>
+        <v>4.8902001554019333e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>1.9203702156151008e-06</v>
+        <v>1.9966505362269138e-06</v>
       </c>
       <c r="V5" s="1">
-        <v>-1.9586883579712538e-05</v>
+        <v>-1.3201395034272676e-05</v>
       </c>
       <c r="W5" s="1">
-        <v>-9.0971539066747112e-05</v>
+        <v>-9.6926265795555799e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3574,70 +3574,70 @@
         <v>27</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.029542980806915257</v>
+        <v>-0.034797757945001832</v>
       </c>
       <c r="C6" s="1">
-        <v>2.9632582600010372e-07</v>
+        <v>3.2133936312615747e-07</v>
       </c>
       <c r="D6" s="1">
-        <v>-2.1509982390282668e-05</v>
+        <v>-2.2019075587858062e-05</v>
       </c>
       <c r="E6" s="1">
-        <v>2.9028587513921156e-07</v>
+        <v>2.9687740438204209e-07</v>
       </c>
       <c r="F6" s="1">
-        <v>0.00016680955575011083</v>
+        <v>0.00016997975435260678</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0015609250696051269</v>
+        <v>0.0015788922628312259</v>
       </c>
       <c r="H6" s="1">
-        <v>-3.5244721617312359e-06</v>
+        <v>-3.5885757487146539e-06</v>
       </c>
       <c r="I6" s="1">
-        <v>-3.1016660379413048e-05</v>
+        <v>-3.135549731889753e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>-9.5364083711132553e-05</v>
+        <v>-9.7914751099368721e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.00014993637099250777</v>
+        <v>-0.00015365044342325273</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.00016807049662611023</v>
+        <v>-0.00017216004712578898</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00016874759136849466</v>
+        <v>-0.00017289734220915436</v>
       </c>
       <c r="N6" s="1">
-        <v>-1.2436775996840554e-05</v>
+        <v>-1.2710544251730326e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>2.1729303597008068e-06</v>
+        <v>2.2034719169481572e-06</v>
       </c>
       <c r="P6" s="1">
-        <v>3.2033161342278219e-07</v>
+        <v>3.1276723267921283e-07</v>
       </c>
       <c r="Q6" s="1">
-        <v>6.6541912203274463e-07</v>
+        <v>6.6166005837784012e-07</v>
       </c>
       <c r="R6" s="1">
-        <v>1.2161327350658538e-06</v>
+        <v>1.1248371528271407e-06</v>
       </c>
       <c r="S6" s="1">
-        <v>-4.8656950552330201e-08</v>
+        <v>-4.5759619500911649e-08</v>
       </c>
       <c r="T6" s="1">
-        <v>2.1901944642785299e-05</v>
+        <v>2.2434641589753834e-05</v>
       </c>
       <c r="U6" s="1">
-        <v>7.4920713239843193e-06</v>
+        <v>7.5800637986360115e-06</v>
       </c>
       <c r="V6" s="1">
-        <v>0.00057619989151922401</v>
+        <v>0.00058992425507764555</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.00045083496442177139</v>
+        <v>-0.00046052258815063404</v>
       </c>
     </row>
     <row r="7">
@@ -3645,70 +3645,70 @@
         <v>28</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.0022295291575184705</v>
+        <v>-0.0022350176431894866</v>
       </c>
       <c r="C7" s="1">
-        <v>7.9195540824657052e-08</v>
+        <v>7.9054665100929526e-08</v>
       </c>
       <c r="D7" s="1">
-        <v>-1.2309732383803699e-07</v>
+        <v>-1.2396387066827486e-07</v>
       </c>
       <c r="E7" s="1">
-        <v>4.0756633435764367e-10</v>
+        <v>4.0074520573018963e-10</v>
       </c>
       <c r="F7" s="1">
-        <v>-5.9684630632905688e-06</v>
+        <v>-6.0635774259102881e-06</v>
       </c>
       <c r="G7" s="1">
-        <v>-3.5244721617312359e-06</v>
+        <v>-3.5885757487146539e-06</v>
       </c>
       <c r="H7" s="1">
-        <v>1.4199542999075008e-07</v>
+        <v>1.442162128470839e-07</v>
       </c>
       <c r="I7" s="1">
-        <v>8.8364460262127657e-08</v>
+        <v>8.9875606946676107e-08</v>
       </c>
       <c r="J7" s="1">
-        <v>-1.3748010260539537e-07</v>
+        <v>-1.327080541016194e-07</v>
       </c>
       <c r="K7" s="1">
-        <v>-1.6510774277011591e-07</v>
+        <v>-1.5772037727458169e-07</v>
       </c>
       <c r="L7" s="1">
-        <v>-1.1158687875166143e-07</v>
+        <v>-1.020018926818695e-07</v>
       </c>
       <c r="M7" s="1">
-        <v>-1.8278824204078499e-07</v>
+        <v>-1.7443886643927566e-07</v>
       </c>
       <c r="N7" s="1">
-        <v>3.3872337772345809e-08</v>
+        <v>3.4902476430315551e-08</v>
       </c>
       <c r="O7" s="1">
-        <v>7.791044759993477e-09</v>
+        <v>7.774391470309872e-09</v>
       </c>
       <c r="P7" s="1">
-        <v>4.2999941333615043e-08</v>
+        <v>4.3387178244285851e-08</v>
       </c>
       <c r="Q7" s="1">
-        <v>5.6554498368977109e-09</v>
+        <v>5.6496102849054088e-09</v>
       </c>
       <c r="R7" s="1">
-        <v>4.8590897553381585e-08</v>
+        <v>4.799246667066341e-08</v>
       </c>
       <c r="S7" s="1">
-        <v>7.8233311342890696e-10</v>
+        <v>7.8430222879115957e-10</v>
       </c>
       <c r="T7" s="1">
-        <v>1.9831679152756437e-09</v>
+        <v>6.699330294915257e-10</v>
       </c>
       <c r="U7" s="1">
-        <v>-2.3385631224593459e-08</v>
+        <v>-2.3504201417437925e-08</v>
       </c>
       <c r="V7" s="1">
-        <v>4.3046056610613416e-06</v>
+        <v>4.3415054949100146e-06</v>
       </c>
       <c r="W7" s="1">
-        <v>-6.2593705201969432e-07</v>
+        <v>-6.0641429970997933e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3716,70 +3716,70 @@
         <v>29</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.0029109909695478734</v>
+        <v>-0.0028785598561041604</v>
       </c>
       <c r="C8" s="1">
-        <v>1.2936363874674917e-07</v>
+        <v>1.2912745000777879e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>1.1650385410440496e-07</v>
+        <v>1.1278652609729893e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>-2.3745246364985281e-09</v>
+        <v>-2.3483078130803554e-09</v>
       </c>
       <c r="F8" s="1">
-        <v>-3.6456973088532176e-06</v>
+        <v>-3.7068319219996309e-06</v>
       </c>
       <c r="G8" s="1">
-        <v>-3.1016660379413048e-05</v>
+        <v>-3.135549731889753e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>8.8364460262127657e-08</v>
+        <v>8.9875606946676107e-08</v>
       </c>
       <c r="I8" s="1">
-        <v>6.6460323246245916e-07</v>
+        <v>6.7192403352123752e-07</v>
       </c>
       <c r="J8" s="1">
-        <v>8.7398182392588053e-07</v>
+        <v>8.7319279706797162e-07</v>
       </c>
       <c r="K8" s="1">
-        <v>1.3862941608613992e-06</v>
+        <v>1.3833143178310243e-06</v>
       </c>
       <c r="L8" s="1">
-        <v>1.6298791007933199e-06</v>
+        <v>1.6276665286640732e-06</v>
       </c>
       <c r="M8" s="1">
-        <v>1.5731303552137411e-06</v>
+        <v>1.5680797094347141e-06</v>
       </c>
       <c r="N8" s="1">
-        <v>1.2103201358942965e-07</v>
+        <v>1.2191461200576373e-07</v>
       </c>
       <c r="O8" s="1">
-        <v>-8.9432753666023755e-09</v>
+        <v>-8.0535514662785164e-09</v>
       </c>
       <c r="P8" s="1">
-        <v>-3.8198448461443356e-09</v>
+        <v>-2.6217315098711026e-09</v>
       </c>
       <c r="Q8" s="1">
-        <v>-1.8568379817788069e-08</v>
+        <v>-1.8554948982549573e-08</v>
       </c>
       <c r="R8" s="1">
-        <v>-2.5867490190967711e-09</v>
+        <v>-1.9851057494567019e-09</v>
       </c>
       <c r="S8" s="1">
-        <v>3.213952037914748e-09</v>
+        <v>3.200017680918172e-09</v>
       </c>
       <c r="T8" s="1">
-        <v>-2.0481410218698427e-07</v>
+        <v>-2.0317451691756227e-07</v>
       </c>
       <c r="U8" s="1">
-        <v>-9.9171176587116558e-08</v>
+        <v>-9.793461896110662e-08</v>
       </c>
       <c r="V8" s="1">
-        <v>-3.0328899356351068e-06</v>
+        <v>-2.9164427903718044e-06</v>
       </c>
       <c r="W8" s="1">
-        <v>3.2178544056340832e-06</v>
+        <v>3.1660146231611015e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3787,70 +3787,70 @@
         <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>0.081658378311899149</v>
+        <v>0.091741974215740402</v>
       </c>
       <c r="C9" s="1">
-        <v>-1.329576166668261e-06</v>
+        <v>-1.3972706667857241e-06</v>
       </c>
       <c r="D9" s="1">
-        <v>4.3092976382750868e-05</v>
+        <v>4.5048207451597167e-05</v>
       </c>
       <c r="E9" s="1">
-        <v>-4.9835048261834688e-07</v>
+        <v>-5.2094380171543953e-07</v>
       </c>
       <c r="F9" s="1">
-        <v>-1.9132389603419844e-05</v>
+        <v>-2.0445660743214189e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>-9.5364083711132553e-05</v>
+        <v>-9.7914751099368721e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.3748010260539537e-07</v>
+        <v>-1.327080541016194e-07</v>
       </c>
       <c r="I9" s="1">
-        <v>8.7398182392588053e-07</v>
+        <v>8.7319279706797162e-07</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0017649681968123822</v>
+        <v>0.0017777694077319999</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0017398867260378693</v>
+        <v>0.0017551138232069024</v>
       </c>
       <c r="L9" s="1">
-        <v>0.0017676966891428296</v>
+        <v>0.00178412683524224</v>
       </c>
       <c r="M9" s="1">
-        <v>0.0017799388650569818</v>
+        <v>0.0017970276809974833</v>
       </c>
       <c r="N9" s="1">
-        <v>1.3085676329167249e-05</v>
+        <v>1.3667908659676639e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-4.7702376759018377e-06</v>
+        <v>-4.9935047066335464e-06</v>
       </c>
       <c r="P9" s="1">
-        <v>-7.4258954531917537e-06</v>
+        <v>-7.6472155390320534e-06</v>
       </c>
       <c r="Q9" s="1">
-        <v>-1.0416980495073182e-06</v>
+        <v>-1.0523833446747026e-06</v>
       </c>
       <c r="R9" s="1">
-        <v>-7.4398302362316664e-06</v>
+        <v>-7.2542098178925646e-06</v>
       </c>
       <c r="S9" s="1">
-        <v>3.3351608332601688e-08</v>
+        <v>2.7106947337217338e-08</v>
       </c>
       <c r="T9" s="1">
-        <v>-3.7046789586502962e-05</v>
+        <v>-3.8731173374994197e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>-1.0798167308472676e-05</v>
+        <v>-1.1145670070488481e-05</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.002734350313124188</v>
+        <v>-0.0027936946267983279</v>
       </c>
       <c r="W9" s="1">
-        <v>0.00080916455466740784</v>
+        <v>0.00084368829196800142</v>
       </c>
     </row>
     <row r="10">
@@ -3858,70 +3858,70 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>0.10016148903490146</v>
+        <v>0.1155620082277935</v>
       </c>
       <c r="C10" s="1">
-        <v>-2.1154160469521786e-06</v>
+        <v>-2.2200563413788758e-06</v>
       </c>
       <c r="D10" s="1">
-        <v>6.6000108741650563e-05</v>
+        <v>6.8926678720369048e-05</v>
       </c>
       <c r="E10" s="1">
-        <v>-7.6301520504357469e-07</v>
+        <v>-7.9682944650752459e-07</v>
       </c>
       <c r="F10" s="1">
-        <v>-3.0578168031125734e-05</v>
+        <v>-3.2559083094358025e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>-0.00014993637099250777</v>
+        <v>-0.00015365044342325273</v>
       </c>
       <c r="H10" s="1">
-        <v>-1.6510774277011591e-07</v>
+        <v>-1.5772037727458169e-07</v>
       </c>
       <c r="I10" s="1">
-        <v>1.3862941608613992e-06</v>
+        <v>1.3833143178310243e-06</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0017398867260378693</v>
+        <v>0.0017551138232069024</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0018894881663133491</v>
+        <v>0.0019106838144149719</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0019161407314848091</v>
+        <v>0.0019388595181738728</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0019352073314146006</v>
+        <v>0.0019589165794916402</v>
       </c>
       <c r="N10" s="1">
-        <v>1.9103643974971957e-05</v>
+        <v>1.996524635219969e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.8723915113014682e-06</v>
+        <v>-7.200197597994142e-06</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.1164938581212497e-05</v>
+        <v>-1.151111656487998e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>-1.6325261441058533e-06</v>
+        <v>-1.6613454551413515e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>-9.7709852338133018e-06</v>
+        <v>-9.4809366100742888e-06</v>
       </c>
       <c r="S10" s="1">
-        <v>2.4784033747815766e-08</v>
+        <v>1.527305799890861e-08</v>
       </c>
       <c r="T10" s="1">
-        <v>-5.6518460944069701e-05</v>
+        <v>-5.9026176248002833e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>-1.6261231449329902e-05</v>
+        <v>-1.677870260350876e-05</v>
       </c>
       <c r="V10" s="1">
-        <v>-0.0033943542645061744</v>
+        <v>-0.0034812837409477927</v>
       </c>
       <c r="W10" s="1">
-        <v>0.0012381814975155345</v>
+        <v>0.0012898515589065231</v>
       </c>
     </row>
     <row r="11">
@@ -3929,70 +3929,70 @@
         <v>32</v>
       </c>
       <c r="B11" s="1">
-        <v>0.12738668955320487</v>
+        <v>0.1444938700610659</v>
       </c>
       <c r="C11" s="1">
-        <v>-2.575516174145509e-06</v>
+        <v>-2.6907319500682823e-06</v>
       </c>
       <c r="D11" s="1">
-        <v>7.3267008214151325e-05</v>
+        <v>7.6498422981173075e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.4514173320042382e-07</v>
+        <v>-8.8244724898383903e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>-3.5678410029623528e-05</v>
+        <v>-3.7895811975724425e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>-0.00016807049662611023</v>
+        <v>-0.00017216004712578898</v>
       </c>
       <c r="H11" s="1">
-        <v>-1.1158687875166143e-07</v>
+        <v>-1.020018926818695e-07</v>
       </c>
       <c r="I11" s="1">
-        <v>1.6298791007933199e-06</v>
+        <v>1.6276665286640732e-06</v>
       </c>
       <c r="J11" s="1">
-        <v>0.0017676966891428296</v>
+        <v>0.00178412683524224</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0019161407314848091</v>
+        <v>0.0019388595181738728</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0019713825061641469</v>
+        <v>0.0019962406932466422</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0019881943966581516</v>
+        <v>0.0020140630482094564</v>
       </c>
       <c r="N11" s="1">
-        <v>2.1012423241989099e-05</v>
+        <v>2.19587489257242e-05</v>
       </c>
       <c r="O11" s="1">
-        <v>-7.7545791232043145e-06</v>
+        <v>-8.1168875919417191e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>-1.2394052503442905e-05</v>
+        <v>-1.2784982977085096e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-1.450817826021366e-06</v>
+        <v>-1.4783318445354936e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>-9.9706012863855343e-06</v>
+        <v>-9.6492699322379069e-06</v>
       </c>
       <c r="S11" s="1">
-        <v>-2.0592259074543647e-08</v>
+        <v>-3.1142534280910278e-08</v>
       </c>
       <c r="T11" s="1">
-        <v>-6.2674586907900511e-05</v>
+        <v>-6.5446790092592598e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>-1.8266920407099411e-05</v>
+        <v>-1.885771155895277e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.0036057398658764631</v>
+        <v>-0.0037014583154260849</v>
       </c>
       <c r="W11" s="1">
-        <v>0.0013752390306774496</v>
+        <v>0.001432276353527076</v>
       </c>
     </row>
     <row r="12">
@@ -4000,70 +4000,70 @@
         <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>0.13568340750628557</v>
+        <v>0.1535842044820962</v>
       </c>
       <c r="C12" s="1">
-        <v>-3.0398976712361011e-06</v>
+        <v>-3.1597600781694574e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>7.7565540860454331e-05</v>
+        <v>8.0982697251160622e-05</v>
       </c>
       <c r="E12" s="1">
-        <v>-8.9166175463450808e-07</v>
+        <v>-9.3105495540308926e-07</v>
       </c>
       <c r="F12" s="1">
-        <v>-3.3240721594389195e-05</v>
+        <v>-3.5469765605325294e-05</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00016874759136849466</v>
+        <v>-0.00017289734220915436</v>
       </c>
       <c r="H12" s="1">
-        <v>-1.8278824204078499e-07</v>
+        <v>-1.7443886643927566e-07</v>
       </c>
       <c r="I12" s="1">
-        <v>1.5731303552137411e-06</v>
+        <v>1.5680797094347141e-06</v>
       </c>
       <c r="J12" s="1">
-        <v>0.0017799388650569818</v>
+        <v>0.0017970276809974833</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0019352073314146006</v>
+        <v>0.0019589165794916402</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0019881943966581516</v>
+        <v>0.0020140630482094564</v>
       </c>
       <c r="M12" s="1">
-        <v>0.002034832135261371</v>
+        <v>0.002062327837121015</v>
       </c>
       <c r="N12" s="1">
-        <v>2.252956150373692e-05</v>
+        <v>2.3535975541046403e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>-7.494042535654579e-06</v>
+        <v>-7.8588501354715122e-06</v>
       </c>
       <c r="P12" s="1">
-        <v>-1.283377104702631e-05</v>
+        <v>-1.3243074828271006e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.3097590648177341e-07</v>
+        <v>-7.4311072125706228e-07</v>
       </c>
       <c r="R12" s="1">
-        <v>-1.0347697175664487e-05</v>
+        <v>-1.0014694399691196e-05</v>
       </c>
       <c r="S12" s="1">
-        <v>-1.6807999975370109e-08</v>
+        <v>-2.7804431966281866e-08</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.5524841696822122e-05</v>
+        <v>-6.8443219027559783e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>-1.9389344808155573e-05</v>
+        <v>-2.0018047222958153e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>-0.0037298557534467874</v>
+        <v>-0.0038309000206610284</v>
       </c>
       <c r="W12" s="1">
-        <v>0.0014371053802197072</v>
+        <v>0.0014971364135565866</v>
       </c>
     </row>
     <row r="13">
@@ -4071,70 +4071,70 @@
         <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>0.0083275064454137338</v>
+        <v>0.0090903320273378989</v>
       </c>
       <c r="C13" s="1">
-        <v>-6.8894745889296805e-08</v>
+        <v>-7.3779791649479002e-08</v>
       </c>
       <c r="D13" s="1">
-        <v>3.2895653087975842e-06</v>
+        <v>3.4384966998311995e-06</v>
       </c>
       <c r="E13" s="1">
-        <v>-3.8328008832915859e-08</v>
+        <v>-4.0056952880177933e-08</v>
       </c>
       <c r="F13" s="1">
-        <v>-3.7267833670423571e-06</v>
+        <v>-3.8617499870034406e-06</v>
       </c>
       <c r="G13" s="1">
-        <v>-1.2436775996840554e-05</v>
+        <v>-1.2710544251730326e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>3.3872337772345809e-08</v>
+        <v>3.4902476430315551e-08</v>
       </c>
       <c r="I13" s="1">
-        <v>1.2103201358942965e-07</v>
+        <v>1.2191461200576373e-07</v>
       </c>
       <c r="J13" s="1">
-        <v>1.3085676329167249e-05</v>
+        <v>1.3667908659676639e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>1.9103643974971957e-05</v>
+        <v>1.996524635219969e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>2.1012423241989099e-05</v>
+        <v>2.19587489257242e-05</v>
       </c>
       <c r="M13" s="1">
-        <v>2.252956150373692e-05</v>
+        <v>2.3535975541046403e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>4.3219172689579556e-05</v>
+        <v>4.4064880882709952e-05</v>
       </c>
       <c r="O13" s="1">
-        <v>2.0207203682273221e-05</v>
+        <v>2.0576778578122086e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>2.0136029019227039e-05</v>
+        <v>2.0503423921499843e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>2.0520898774811205e-05</v>
+        <v>2.0905073785468238e-05</v>
       </c>
       <c r="R13" s="1">
-        <v>4.541419541128636e-07</v>
+        <v>4.6430944542570781e-07</v>
       </c>
       <c r="S13" s="1">
-        <v>-4.5029417916795682e-08</v>
+        <v>-4.5487519262124602e-08</v>
       </c>
       <c r="T13" s="1">
-        <v>-2.8688454173198001e-06</v>
+        <v>-3.0062652132856663e-06</v>
       </c>
       <c r="U13" s="1">
-        <v>-1.0926995436509485e-06</v>
+        <v>-1.1420396895516485e-06</v>
       </c>
       <c r="V13" s="1">
-        <v>-0.00010941811371019872</v>
+        <v>-0.00011399856905883001</v>
       </c>
       <c r="W13" s="1">
-        <v>6.0647631655173374e-05</v>
+        <v>6.3264387465876423e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4142,70 +4142,70 @@
         <v>35</v>
       </c>
       <c r="B14" s="1">
-        <v>0.01690474514223907</v>
+        <v>0.016630261293378655</v>
       </c>
       <c r="C14" s="1">
-        <v>-2.0461586583745925e-07</v>
+        <v>-2.0249720190202802e-07</v>
       </c>
       <c r="D14" s="1">
-        <v>-9.9589338257899275e-07</v>
+        <v>-1.0461771274237672e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>1.1294875937742779e-08</v>
+        <v>1.1872323243293416e-08</v>
       </c>
       <c r="F14" s="1">
-        <v>5.9469346436467045e-07</v>
+        <v>6.3163497138528684e-07</v>
       </c>
       <c r="G14" s="1">
-        <v>2.1729303597008068e-06</v>
+        <v>2.2034719169481572e-06</v>
       </c>
       <c r="H14" s="1">
-        <v>7.791044759993477e-09</v>
+        <v>7.774391470309872e-09</v>
       </c>
       <c r="I14" s="1">
-        <v>-8.9432753666023755e-09</v>
+        <v>-8.0535514662785164e-09</v>
       </c>
       <c r="J14" s="1">
-        <v>-4.7702376759018377e-06</v>
+        <v>-4.9935047066335464e-06</v>
       </c>
       <c r="K14" s="1">
-        <v>-6.8723915113014682e-06</v>
+        <v>-7.200197597994142e-06</v>
       </c>
       <c r="L14" s="1">
-        <v>-7.7545791232043145e-06</v>
+        <v>-8.1168875919417191e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>-7.494042535654579e-06</v>
+        <v>-7.8588501354715122e-06</v>
       </c>
       <c r="N14" s="1">
-        <v>2.0207203682273221e-05</v>
+        <v>2.0576778578122086e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>5.5796807152798889e-05</v>
+        <v>5.6831659995632628e-05</v>
       </c>
       <c r="P14" s="1">
-        <v>2.0700155084168806e-05</v>
+        <v>2.1091371938670426e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>2.0552862375483086e-05</v>
+        <v>2.0938741913513245e-05</v>
       </c>
       <c r="R14" s="1">
-        <v>9.6528946751566446e-07</v>
+        <v>9.5693363860997717e-07</v>
       </c>
       <c r="S14" s="1">
-        <v>-2.4385040334742639e-08</v>
+        <v>-2.420189774067559e-08</v>
       </c>
       <c r="T14" s="1">
-        <v>3.6326456823938441e-07</v>
+        <v>3.9796302408819562e-07</v>
       </c>
       <c r="U14" s="1">
-        <v>-5.2667935480088515e-08</v>
+        <v>-5.7561172810141682e-08</v>
       </c>
       <c r="V14" s="1">
-        <v>1.3004444993021177e-05</v>
+        <v>1.4088960095926685e-05</v>
       </c>
       <c r="W14" s="1">
-        <v>-2.1866447286830713e-05</v>
+        <v>-2.278965241539738e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4213,70 +4213,70 @@
         <v>36</v>
       </c>
       <c r="B15" s="1">
-        <v>0.0027427981650576042</v>
+        <v>0.0023527172655760445</v>
       </c>
       <c r="C15" s="1">
-        <v>-1.612995692623056e-08</v>
+        <v>-1.3117577463417174e-08</v>
       </c>
       <c r="D15" s="1">
-        <v>-1.7693611483057637e-06</v>
+        <v>-1.8316142196929856e-06</v>
       </c>
       <c r="E15" s="1">
-        <v>2.0046074731730839e-08</v>
+        <v>2.0757870873618325e-08</v>
       </c>
       <c r="F15" s="1">
-        <v>-9.5376204999818191e-07</v>
+        <v>-9.3578995897833999e-07</v>
       </c>
       <c r="G15" s="1">
-        <v>3.2033161342278219e-07</v>
+        <v>3.1276723267921283e-07</v>
       </c>
       <c r="H15" s="1">
-        <v>4.2999941333615043e-08</v>
+        <v>4.3387178244285851e-08</v>
       </c>
       <c r="I15" s="1">
-        <v>-3.8198448461443356e-09</v>
+        <v>-2.6217315098711026e-09</v>
       </c>
       <c r="J15" s="1">
-        <v>-7.4258954531917537e-06</v>
+        <v>-7.6472155390320534e-06</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.1164938581212497e-05</v>
+        <v>-1.151111656487998e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-1.2394052503442905e-05</v>
+        <v>-1.2784982977085096e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>-1.283377104702631e-05</v>
+        <v>-1.3243074828271006e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>2.0136029019227039e-05</v>
+        <v>2.0503423921499843e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>2.0700155084168806e-05</v>
+        <v>2.1091371938670426e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>4.2640892286841506e-05</v>
+        <v>4.3433619936622594e-05</v>
       </c>
       <c r="Q15" s="1">
-        <v>2.0580744139549283e-05</v>
+        <v>2.0966408926165189e-05</v>
       </c>
       <c r="R15" s="1">
-        <v>9.3990740851705736e-07</v>
+        <v>9.2800359936065708e-07</v>
       </c>
       <c r="S15" s="1">
-        <v>-4.3773067598317071e-08</v>
+        <v>-4.3558706726802231e-08</v>
       </c>
       <c r="T15" s="1">
-        <v>1.4759897660591757e-06</v>
+        <v>1.5207190673978293e-06</v>
       </c>
       <c r="U15" s="1">
-        <v>6.6479604857148543e-07</v>
+        <v>6.6055989477521426e-07</v>
       </c>
       <c r="V15" s="1">
-        <v>3.698660854811083e-05</v>
+        <v>3.8370889758454049e-05</v>
       </c>
       <c r="W15" s="1">
-        <v>-3.2050082411115895e-05</v>
+        <v>-3.3135166541783741e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4284,70 +4284,70 @@
         <v>37</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.0083720675469531932</v>
+        <v>-0.0084009748352482077</v>
       </c>
       <c r="C16" s="1">
-        <v>4.1253785063112049e-07</v>
+        <v>4.122174321803317e-07</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.2966564623322738e-07</v>
+        <v>-1.3243498528409269e-07</v>
       </c>
       <c r="E16" s="1">
-        <v>1.2296963214623994e-09</v>
+        <v>1.2577286622741999e-09</v>
       </c>
       <c r="F16" s="1">
-        <v>5.8032549033180113e-07</v>
+        <v>5.9619424435986299e-07</v>
       </c>
       <c r="G16" s="1">
-        <v>6.6541912203274463e-07</v>
+        <v>6.6166005837784012e-07</v>
       </c>
       <c r="H16" s="1">
-        <v>5.6554498368977109e-09</v>
+        <v>5.6496102849054088e-09</v>
       </c>
       <c r="I16" s="1">
-        <v>-1.8568379817788069e-08</v>
+        <v>-1.8554948982549573e-08</v>
       </c>
       <c r="J16" s="1">
-        <v>-1.0416980495073182e-06</v>
+        <v>-1.0523833446747026e-06</v>
       </c>
       <c r="K16" s="1">
-        <v>-1.6325261441058533e-06</v>
+        <v>-1.6613454551413515e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>-1.450817826021366e-06</v>
+        <v>-1.4783318445354936e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>-7.3097590648177341e-07</v>
+        <v>-7.4311072125706228e-07</v>
       </c>
       <c r="N16" s="1">
-        <v>2.0520898774811205e-05</v>
+        <v>2.0905073785468238e-05</v>
       </c>
       <c r="O16" s="1">
-        <v>2.0552862375483086e-05</v>
+        <v>2.0938741913513245e-05</v>
       </c>
       <c r="P16" s="1">
-        <v>2.0580744139549283e-05</v>
+        <v>2.0966408926165189e-05</v>
       </c>
       <c r="Q16" s="1">
-        <v>2.8867910339995396e-05</v>
+        <v>2.9408535764335505e-05</v>
       </c>
       <c r="R16" s="1">
-        <v>5.7142391192028093e-07</v>
+        <v>5.6838357213727826e-07</v>
       </c>
       <c r="S16" s="1">
-        <v>-3.2863717814502556e-08</v>
+        <v>-3.2861344140855136e-08</v>
       </c>
       <c r="T16" s="1">
-        <v>-2.9347501904206645e-07</v>
+        <v>-3.0112984475801763e-07</v>
       </c>
       <c r="U16" s="1">
-        <v>-2.5397048588196829e-07</v>
+        <v>-2.7524521651289152e-07</v>
       </c>
       <c r="V16" s="1">
-        <v>-1.30862587691766e-05</v>
+        <v>-1.3379456552318593e-05</v>
       </c>
       <c r="W16" s="1">
-        <v>-2.4009545364350054e-06</v>
+        <v>-2.4646151360120109e-06</v>
       </c>
     </row>
     <row r="17">
@@ -4355,70 +4355,70 @@
         <v>38</v>
       </c>
       <c r="B17" s="1">
-        <v>0.088491077453089359</v>
+        <v>0.088244935698452875</v>
       </c>
       <c r="C17" s="1">
-        <v>-5.3985273628379837e-07</v>
+        <v>-5.3120779209500691e-07</v>
       </c>
       <c r="D17" s="1">
-        <v>-7.6007482328904806e-07</v>
+        <v>-7.0880600833410249e-07</v>
       </c>
       <c r="E17" s="1">
-        <v>8.0716558805951755e-09</v>
+        <v>7.4781631812165795e-09</v>
       </c>
       <c r="F17" s="1">
-        <v>-4.317819622510065e-07</v>
+        <v>-4.3061894784281215e-07</v>
       </c>
       <c r="G17" s="1">
-        <v>1.2161327350658538e-06</v>
+        <v>1.1248371528271407e-06</v>
       </c>
       <c r="H17" s="1">
-        <v>4.8590897553381585e-08</v>
+        <v>4.799246667066341e-08</v>
       </c>
       <c r="I17" s="1">
-        <v>-2.5867490190967711e-09</v>
+        <v>-1.9851057494567019e-09</v>
       </c>
       <c r="J17" s="1">
-        <v>-7.4398302362316664e-06</v>
+        <v>-7.2542098178925646e-06</v>
       </c>
       <c r="K17" s="1">
-        <v>-9.7709852338133018e-06</v>
+        <v>-9.4809366100742888e-06</v>
       </c>
       <c r="L17" s="1">
-        <v>-9.9706012863855343e-06</v>
+        <v>-9.6492699322379069e-06</v>
       </c>
       <c r="M17" s="1">
-        <v>-1.0347697175664487e-05</v>
+        <v>-1.0014694399691196e-05</v>
       </c>
       <c r="N17" s="1">
-        <v>4.541419541128636e-07</v>
+        <v>4.6430944542570781e-07</v>
       </c>
       <c r="O17" s="1">
-        <v>9.6528946751566446e-07</v>
+        <v>9.5693363860997717e-07</v>
       </c>
       <c r="P17" s="1">
-        <v>9.3990740851705736e-07</v>
+        <v>9.2800359936065708e-07</v>
       </c>
       <c r="Q17" s="1">
-        <v>5.7142391192028093e-07</v>
+        <v>5.6838357213727826e-07</v>
       </c>
       <c r="R17" s="1">
-        <v>5.0746274296874837e-05</v>
+        <v>5.0588476877753321e-05</v>
       </c>
       <c r="S17" s="1">
-        <v>6.4367834339691808e-08</v>
+        <v>6.4583150096076781e-08</v>
       </c>
       <c r="T17" s="1">
-        <v>8.5890325664010015e-07</v>
+        <v>8.1561683969106884e-07</v>
       </c>
       <c r="U17" s="1">
-        <v>-2.1424418401483144e-07</v>
+        <v>-2.3364794148743779e-07</v>
       </c>
       <c r="V17" s="1">
-        <v>1.9585805021687986e-05</v>
+        <v>1.808964332571101e-05</v>
       </c>
       <c r="W17" s="1">
-        <v>-3.0787142987034561e-05</v>
+        <v>-2.9786757022585778e-05</v>
       </c>
     </row>
     <row r="18">
@@ -4426,70 +4426,70 @@
         <v>39</v>
       </c>
       <c r="B18" s="1">
-        <v>0.00087279153630380186</v>
+        <v>0.00087066270570612789</v>
       </c>
       <c r="C18" s="1">
-        <v>-3.1725445782703972e-08</v>
+        <v>-3.1817927415252808e-08</v>
       </c>
       <c r="D18" s="1">
-        <v>-3.2161260280618683e-09</v>
+        <v>-4.812061892745527e-09</v>
       </c>
       <c r="E18" s="1">
-        <v>-1.0452519450567112e-11</v>
+        <v>7.9792517690732846e-12</v>
       </c>
       <c r="F18" s="1">
-        <v>2.1952956958122924e-08</v>
+        <v>2.2706880811575285e-08</v>
       </c>
       <c r="G18" s="1">
-        <v>-4.8656950552330201e-08</v>
+        <v>-4.5759619500911649e-08</v>
       </c>
       <c r="H18" s="1">
-        <v>7.8233311342890696e-10</v>
+        <v>7.8430222879115957e-10</v>
       </c>
       <c r="I18" s="1">
-        <v>3.213952037914748e-09</v>
+        <v>3.200017680918172e-09</v>
       </c>
       <c r="J18" s="1">
-        <v>3.3351608332601688e-08</v>
+        <v>2.7106947337217338e-08</v>
       </c>
       <c r="K18" s="1">
-        <v>2.4784033747815766e-08</v>
+        <v>1.527305799890861e-08</v>
       </c>
       <c r="L18" s="1">
-        <v>-2.0592259074543647e-08</v>
+        <v>-3.1142534280910278e-08</v>
       </c>
       <c r="M18" s="1">
-        <v>-1.6807999975370109e-08</v>
+        <v>-2.7804431966281866e-08</v>
       </c>
       <c r="N18" s="1">
-        <v>-4.5029417916795682e-08</v>
+        <v>-4.5487519262124602e-08</v>
       </c>
       <c r="O18" s="1">
-        <v>-2.4385040334742639e-08</v>
+        <v>-2.420189774067559e-08</v>
       </c>
       <c r="P18" s="1">
-        <v>-4.3773067598317071e-08</v>
+        <v>-4.3558706726802231e-08</v>
       </c>
       <c r="Q18" s="1">
-        <v>-3.2863717814502556e-08</v>
+        <v>-3.2861344140855136e-08</v>
       </c>
       <c r="R18" s="1">
-        <v>6.4367834339691808e-08</v>
+        <v>6.4583150096076781e-08</v>
       </c>
       <c r="S18" s="1">
-        <v>2.3181811158833826e-08</v>
+        <v>2.3199429254771555e-08</v>
       </c>
       <c r="T18" s="1">
-        <v>-3.4039787616806396e-07</v>
+        <v>-3.3930439190045883e-07</v>
       </c>
       <c r="U18" s="1">
-        <v>-4.1610085424614751e-07</v>
+        <v>-4.1604290541653148e-07</v>
       </c>
       <c r="V18" s="1">
-        <v>-2.2848720968288204e-06</v>
+        <v>-2.2402439624244361e-06</v>
       </c>
       <c r="W18" s="1">
-        <v>-7.0182028266619682e-08</v>
+        <v>-1.0019446202911351e-07</v>
       </c>
     </row>
     <row r="19">
@@ -4497,70 +4497,70 @@
         <v>40</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.017934762296264645</v>
+        <v>-0.020188627084187703</v>
       </c>
       <c r="C19" s="1">
-        <v>-5.7451745290199412e-07</v>
+        <v>-5.5640088738611438e-07</v>
       </c>
       <c r="D19" s="1">
-        <v>-9.6370431985031101e-06</v>
+        <v>-1.006105568865197e-05</v>
       </c>
       <c r="E19" s="1">
-        <v>1.1182305324956598e-07</v>
+        <v>1.1671263077679052e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>4.5778864452402758e-06</v>
+        <v>4.8902001554019333e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>2.1901944642785299e-05</v>
+        <v>2.2434641589753834e-05</v>
       </c>
       <c r="H19" s="1">
-        <v>1.9831679152756437e-09</v>
+        <v>6.699330294915257e-10</v>
       </c>
       <c r="I19" s="1">
-        <v>-2.0481410218698427e-07</v>
+        <v>-2.0317451691756227e-07</v>
       </c>
       <c r="J19" s="1">
-        <v>-3.7046789586502962e-05</v>
+        <v>-3.8731173374994197e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>-5.6518460944069701e-05</v>
+        <v>-5.9026176248002833e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>-6.2674586907900511e-05</v>
+        <v>-6.5446790092592598e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>-6.5524841696822122e-05</v>
+        <v>-6.8443219027559783e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>-2.8688454173198001e-06</v>
+        <v>-3.0062652132856663e-06</v>
       </c>
       <c r="O19" s="1">
-        <v>3.6326456823938441e-07</v>
+        <v>3.9796302408819562e-07</v>
       </c>
       <c r="P19" s="1">
-        <v>1.4759897660591757e-06</v>
+        <v>1.5207190673978293e-06</v>
       </c>
       <c r="Q19" s="1">
-        <v>-2.9347501904206645e-07</v>
+        <v>-3.0112984475801763e-07</v>
       </c>
       <c r="R19" s="1">
-        <v>8.5890325664010015e-07</v>
+        <v>8.1561683969106884e-07</v>
       </c>
       <c r="S19" s="1">
-        <v>-3.4039787616806396e-07</v>
+        <v>-3.3930439190045883e-07</v>
       </c>
       <c r="T19" s="1">
-        <v>7.0561656827931106e-05</v>
+        <v>7.1902964832822188e-05</v>
       </c>
       <c r="U19" s="1">
-        <v>1.2706348389601879e-05</v>
+        <v>1.2864580287976232e-05</v>
       </c>
       <c r="V19" s="1">
-        <v>0.00031200419238927969</v>
+        <v>0.00032405205716232714</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.00018050982201790717</v>
+        <v>-0.00018801837626443441</v>
       </c>
     </row>
     <row r="20">
@@ -4568,70 +4568,70 @@
         <v>41</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.010519011808655646</v>
+        <v>-0.011136636389208096</v>
       </c>
       <c r="C20" s="1">
-        <v>-3.3993745147163856e-07</v>
+        <v>-3.3266569904529709e-07</v>
       </c>
       <c r="D20" s="1">
-        <v>-2.8203116859035689e-06</v>
+        <v>-2.9095754039691796e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>3.3163610931909897e-08</v>
+        <v>3.4181509813252506e-08</v>
       </c>
       <c r="F20" s="1">
-        <v>1.9203702156151008e-06</v>
+        <v>1.9966505362269138e-06</v>
       </c>
       <c r="G20" s="1">
-        <v>7.4920713239843193e-06</v>
+        <v>7.5800637986360115e-06</v>
       </c>
       <c r="H20" s="1">
-        <v>-2.3385631224593459e-08</v>
+        <v>-2.3504201417437925e-08</v>
       </c>
       <c r="I20" s="1">
-        <v>-9.9171176587116558e-08</v>
+        <v>-9.793461896110662e-08</v>
       </c>
       <c r="J20" s="1">
-        <v>-1.0798167308472676e-05</v>
+        <v>-1.1145670070488481e-05</v>
       </c>
       <c r="K20" s="1">
-        <v>-1.6261231449329902e-05</v>
+        <v>-1.677870260350876e-05</v>
       </c>
       <c r="L20" s="1">
-        <v>-1.8266920407099411e-05</v>
+        <v>-1.885771155895277e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>-1.9389344808155573e-05</v>
+        <v>-2.0018047222958153e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-1.0926995436509485e-06</v>
+        <v>-1.1420396895516485e-06</v>
       </c>
       <c r="O20" s="1">
-        <v>-5.2667935480088515e-08</v>
+        <v>-5.7561172810141682e-08</v>
       </c>
       <c r="P20" s="1">
-        <v>6.6479604857148543e-07</v>
+        <v>6.6055989477521426e-07</v>
       </c>
       <c r="Q20" s="1">
-        <v>-2.5397048588196829e-07</v>
+        <v>-2.7524521651289152e-07</v>
       </c>
       <c r="R20" s="1">
-        <v>-2.1424418401483144e-07</v>
+        <v>-2.3364794148743779e-07</v>
       </c>
       <c r="S20" s="1">
-        <v>-4.1610085424614751e-07</v>
+        <v>-4.1604290541653148e-07</v>
       </c>
       <c r="T20" s="1">
-        <v>1.2706348389601879e-05</v>
+        <v>1.2864580287976232e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>6.9552957763724789e-05</v>
+        <v>7.0709405765912979e-05</v>
       </c>
       <c r="V20" s="1">
-        <v>0.00012216265549412376</v>
+        <v>0.00012468089152445192</v>
       </c>
       <c r="W20" s="1">
-        <v>-5.197353396347335e-05</v>
+        <v>-5.3517844622019205e-05</v>
       </c>
     </row>
     <row r="21">
@@ -4639,70 +4639,70 @@
         <v>42</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.2175846901168523</v>
+        <v>-0.29441185564495992</v>
       </c>
       <c r="C21" s="1">
-        <v>1.7306224963702015e-06</v>
+        <v>2.2812835583347253e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>-0.00037010256147277699</v>
+        <v>-0.00038495425942503095</v>
       </c>
       <c r="E21" s="1">
-        <v>4.2390165884613272e-06</v>
+        <v>4.4097184882505079e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.9586883579712538e-05</v>
+        <v>-1.3201395034272676e-05</v>
       </c>
       <c r="G21" s="1">
-        <v>0.00057619989151922401</v>
+        <v>0.00058992425507764555</v>
       </c>
       <c r="H21" s="1">
-        <v>4.3046056610613416e-06</v>
+        <v>4.3415054949100146e-06</v>
       </c>
       <c r="I21" s="1">
-        <v>-3.0328899356351068e-06</v>
+        <v>-2.9164427903718044e-06</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.002734350313124188</v>
+        <v>-0.0027936946267983279</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.0033943542645061744</v>
+        <v>-0.0034812837409477927</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.0036057398658764631</v>
+        <v>-0.0037014583154260849</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.0037298557534467874</v>
+        <v>-0.0038309000206610284</v>
       </c>
       <c r="N21" s="1">
-        <v>-0.00010941811371019872</v>
+        <v>-0.00011399856905883001</v>
       </c>
       <c r="O21" s="1">
-        <v>1.3004444993021177e-05</v>
+        <v>1.4088960095926685e-05</v>
       </c>
       <c r="P21" s="1">
-        <v>3.698660854811083e-05</v>
+        <v>3.8370889758454049e-05</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.30862587691766e-05</v>
+        <v>-1.3379456552318593e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>1.9585805021687986e-05</v>
+        <v>1.808964332571101e-05</v>
       </c>
       <c r="S21" s="1">
-        <v>-2.2848720968288204e-06</v>
+        <v>-2.2402439624244361e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>0.00031200419238927969</v>
+        <v>0.00032405205716232714</v>
       </c>
       <c r="U21" s="1">
-        <v>0.00012216265549412376</v>
+        <v>0.00012468089152445192</v>
       </c>
       <c r="V21" s="1">
-        <v>0.012166687571188863</v>
+        <v>0.012589519329481481</v>
       </c>
       <c r="W21" s="1">
-        <v>-0.0061807080262202604</v>
+        <v>-0.0064325585535254335</v>
       </c>
     </row>
     <row r="22">
@@ -4710,70 +4710,70 @@
         <v>43</v>
       </c>
       <c r="B22" s="1">
-        <v>0.15642191618843199</v>
+        <v>0.2061661915894199</v>
       </c>
       <c r="C22" s="1">
-        <v>-8.6087834123038204e-07</v>
+        <v>-1.2052295381251564e-06</v>
       </c>
       <c r="D22" s="1">
-        <v>0.00021486155085840661</v>
+        <v>0.00022375527358854146</v>
       </c>
       <c r="E22" s="1">
-        <v>-2.4830711083232331e-06</v>
+        <v>-2.5858404374380383e-06</v>
       </c>
       <c r="F22" s="1">
-        <v>-9.0971539066747112e-05</v>
+        <v>-9.6926265795555799e-05</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.00045083496442177139</v>
+        <v>-0.00046052258815063404</v>
       </c>
       <c r="H22" s="1">
-        <v>-6.2593705201969432e-07</v>
+        <v>-6.0641429970997933e-07</v>
       </c>
       <c r="I22" s="1">
-        <v>3.2178544056340832e-06</v>
+        <v>3.1660146231611015e-06</v>
       </c>
       <c r="J22" s="1">
-        <v>0.00080916455466740784</v>
+        <v>0.00084368829196800142</v>
       </c>
       <c r="K22" s="1">
-        <v>0.0012381814975155345</v>
+        <v>0.0012898515589065231</v>
       </c>
       <c r="L22" s="1">
-        <v>0.0013752390306774496</v>
+        <v>0.001432276353527076</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0014371053802197072</v>
+        <v>0.0014971364135565866</v>
       </c>
       <c r="N22" s="1">
-        <v>6.0647631655173374e-05</v>
+        <v>6.3264387465876423e-05</v>
       </c>
       <c r="O22" s="1">
-        <v>-2.1866447286830713e-05</v>
+        <v>-2.278965241539738e-05</v>
       </c>
       <c r="P22" s="1">
-        <v>-3.2050082411115895e-05</v>
+        <v>-3.3135166541783741e-05</v>
       </c>
       <c r="Q22" s="1">
-        <v>-2.4009545364350054e-06</v>
+        <v>-2.4646151360120109e-06</v>
       </c>
       <c r="R22" s="1">
-        <v>-3.0787142987034561e-05</v>
+        <v>-2.9786757022585778e-05</v>
       </c>
       <c r="S22" s="1">
-        <v>-7.0182028266619682e-08</v>
+        <v>-1.0019446202911351e-07</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.00018050982201790717</v>
+        <v>-0.00018801837626443441</v>
       </c>
       <c r="U22" s="1">
-        <v>-5.197353396347335e-05</v>
+        <v>-5.3517844622019205e-05</v>
       </c>
       <c r="V22" s="1">
-        <v>-0.0061807080262202604</v>
+        <v>-0.0064325585535254335</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0040004999967319845</v>
+        <v>0.004156444243217255</v>
       </c>
     </row>
   </sheetData>
@@ -4861,70 +4861,70 @@
         <v>45</v>
       </c>
       <c r="B2" s="1">
-        <v>0.81754152829622773</v>
+        <v>0.81749189394946231</v>
       </c>
       <c r="C2" s="1">
-        <v>8.5719799380112936e-06</v>
+        <v>9.0159897616134926e-06</v>
       </c>
       <c r="D2" s="1">
-        <v>-9.6357485484354118e-08</v>
+        <v>-8.695998833459178e-08</v>
       </c>
       <c r="E2" s="1">
-        <v>-2.2830238276407115e-11</v>
+        <v>-1.9805062199341824e-10</v>
       </c>
       <c r="F2" s="1">
-        <v>1.0016690684354763e-06</v>
+        <v>1.0614073214424152e-06</v>
       </c>
       <c r="G2" s="1">
-        <v>-3.360436818405722e-07</v>
+        <v>-3.7282481810847547e-07</v>
       </c>
       <c r="H2" s="1">
-        <v>5.72596780673939e-08</v>
+        <v>6.0041350144554233e-08</v>
       </c>
       <c r="I2" s="1">
-        <v>1.2885582860948503e-07</v>
+        <v>1.3567198132440606e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>5.45439141752782e-07</v>
+        <v>6.4352786716528285e-07</v>
       </c>
       <c r="K2" s="1">
-        <v>1.4482514845650772e-06</v>
+        <v>1.6644151539856337e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>1.2815801798531074e-06</v>
+        <v>1.5067087229564433e-06</v>
       </c>
       <c r="M2" s="1">
-        <v>1.0122393671551963e-06</v>
+        <v>1.2269285345081865e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>2.5149956979487623e-07</v>
+        <v>2.6975660811602586e-07</v>
       </c>
       <c r="O2" s="1">
-        <v>-7.2497937398557479e-07</v>
+        <v>-7.6810461532286462e-07</v>
       </c>
       <c r="P2" s="1">
-        <v>1.1035047931850824e-08</v>
+        <v>6.4127094210992326e-09</v>
       </c>
       <c r="Q2" s="1">
-        <v>7.5953216481798214e-07</v>
+        <v>7.9739640972672343e-07</v>
       </c>
       <c r="R2" s="1">
-        <v>1.271963702109067e-06</v>
+        <v>1.3088954429141434e-06</v>
       </c>
       <c r="S2" s="1">
-        <v>-4.6056211331114222e-08</v>
+        <v>-4.8411034740049847e-08</v>
       </c>
       <c r="T2" s="1">
-        <v>-7.6555364133873366e-07</v>
+        <v>-8.1918500223259498e-07</v>
       </c>
       <c r="U2" s="1">
-        <v>-1.4418322794137973e-07</v>
+        <v>-1.4994208914397028e-07</v>
       </c>
       <c r="V2" s="1">
-        <v>-7.7439097670995628e-06</v>
+        <v>-8.6213184368799659e-06</v>
       </c>
       <c r="W2" s="1">
-        <v>9.5290420813499604e-06</v>
+        <v>1.0462758516736962e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4932,70 +4932,70 @@
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0083017969195921214</v>
+        <v>-0.0087447282689506779</v>
       </c>
       <c r="C3" s="1">
-        <v>-9.6357485484354118e-08</v>
+        <v>-8.695998833459178e-08</v>
       </c>
       <c r="D3" s="1">
-        <v>8.9388123718401584e-06</v>
+        <v>9.5099362308019027e-06</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.0437997512938109e-07</v>
+        <v>-1.1108795470496592e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>1.3995870290245832e-05</v>
+        <v>1.4795176151124426e-05</v>
       </c>
       <c r="G3" s="1">
-        <v>-4.5035087354437294e-06</v>
+        <v>-5.0668090315422262e-06</v>
       </c>
       <c r="H3" s="1">
-        <v>-3.2349271651709307e-07</v>
+        <v>-3.4179128722730129e-07</v>
       </c>
       <c r="I3" s="1">
-        <v>-6.787524881522505e-08</v>
+        <v>-6.6510065937175413e-08</v>
       </c>
       <c r="J3" s="1">
-        <v>3.2709055480318718e-05</v>
+        <v>3.4903648353731611e-05</v>
       </c>
       <c r="K3" s="1">
-        <v>6.7662252681921655e-05</v>
+        <v>7.217356742454286e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>7.54016541980888e-05</v>
+        <v>8.0439817156148296e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>7.804515926095962e-05</v>
+        <v>8.3235382071258934e-05</v>
       </c>
       <c r="N3" s="1">
-        <v>1.7596591154108668e-06</v>
+        <v>1.8857376836457368e-06</v>
       </c>
       <c r="O3" s="1">
-        <v>-2.1433693691763144e-06</v>
+        <v>-2.2981269626910055e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>-2.1303960959452357e-06</v>
+        <v>-2.286300209330839e-06</v>
       </c>
       <c r="Q3" s="1">
-        <v>-6.7038047163706636e-07</v>
+        <v>-7.1901973696885623e-07</v>
       </c>
       <c r="R3" s="1">
-        <v>-1.4164345413678755e-06</v>
+        <v>-1.6346024049031838e-06</v>
       </c>
       <c r="S3" s="1">
-        <v>-1.7519818906491076e-08</v>
+        <v>-1.7989996463168776e-08</v>
       </c>
       <c r="T3" s="1">
-        <v>-6.1920262790011074e-06</v>
+        <v>-6.6158182870882466e-06</v>
       </c>
       <c r="U3" s="1">
-        <v>1.5354376099694776e-06</v>
+        <v>1.6242005607187921e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>-0.00027068070388926749</v>
+        <v>-0.00028826253877510684</v>
       </c>
       <c r="W3" s="1">
-        <v>0.000211687281128268</v>
+        <v>0.00022580335629701525</v>
       </c>
     </row>
     <row r="4">
@@ -5003,70 +5003,70 @@
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>0.00011471489932512702</v>
+        <v>0.00012006176894871503</v>
       </c>
       <c r="C4" s="1">
-        <v>-2.2830238276407115e-11</v>
+        <v>-1.9805062199341824e-10</v>
       </c>
       <c r="D4" s="1">
-        <v>-1.0437997512938109e-07</v>
+        <v>-1.1108795470496592e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>1.2429712343061825e-09</v>
+        <v>1.3230132331683425e-09</v>
       </c>
       <c r="F4" s="1">
-        <v>-8.7328849216225061e-08</v>
+        <v>-9.2762874575903988e-08</v>
       </c>
       <c r="G4" s="1">
-        <v>1.3717856467672172e-07</v>
+        <v>1.4823884054330889e-07</v>
       </c>
       <c r="H4" s="1">
-        <v>1.9431635005202673e-09</v>
+        <v>2.0627533072503737e-09</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.1590458210061321e-09</v>
+        <v>-1.2774618245573641e-09</v>
       </c>
       <c r="J4" s="1">
-        <v>-3.9488572922500512e-07</v>
+        <v>-4.2136085650465624e-07</v>
       </c>
       <c r="K4" s="1">
-        <v>-8.1697856204955601e-07</v>
+        <v>-8.7140675479674764e-07</v>
       </c>
       <c r="L4" s="1">
-        <v>-9.0812400888249725e-07</v>
+        <v>-9.6878949101364278e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>-9.356514221247226e-07</v>
+        <v>-9.9792581574346703e-07</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.1759824142311797e-08</v>
+        <v>-2.3308084781546249e-08</v>
       </c>
       <c r="O4" s="1">
-        <v>2.528213581687567e-08</v>
+        <v>2.7119100347439834e-08</v>
       </c>
       <c r="P4" s="1">
-        <v>2.5148081304804029e-08</v>
+        <v>2.6999929739189855e-08</v>
       </c>
       <c r="Q4" s="1">
-        <v>7.8880233373053858e-09</v>
+        <v>8.4642200431817127e-09</v>
       </c>
       <c r="R4" s="1">
-        <v>1.5472056656198025e-08</v>
+        <v>1.8033162584495335e-08</v>
       </c>
       <c r="S4" s="1">
-        <v>1.7314233839552872e-10</v>
+        <v>1.7680560582008252e-10</v>
       </c>
       <c r="T4" s="1">
-        <v>7.5454734888846687e-08</v>
+        <v>8.0604143339492566e-08</v>
       </c>
       <c r="U4" s="1">
-        <v>-1.8035694006008437e-08</v>
+        <v>-1.9079819094584789e-08</v>
       </c>
       <c r="V4" s="1">
-        <v>3.1562671385628023e-06</v>
+        <v>3.3626274142740523e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>-2.5550678443893168e-06</v>
+        <v>-2.7253284330028936e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5074,70 +5074,70 @@
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.033800948836971205</v>
+        <v>-0.034086044980466385</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0016690684354763e-06</v>
+        <v>1.0614073214424152e-06</v>
       </c>
       <c r="D5" s="1">
-        <v>1.3995870290245832e-05</v>
+        <v>1.4795176151124426e-05</v>
       </c>
       <c r="E5" s="1">
-        <v>-8.7328849216225061e-08</v>
+        <v>-9.2762874575903988e-08</v>
       </c>
       <c r="F5" s="1">
-        <v>0.00039116895927665139</v>
+        <v>0.00041140354114838708</v>
       </c>
       <c r="G5" s="1">
-        <v>0.00028974671161578335</v>
+        <v>0.00030446231301477483</v>
       </c>
       <c r="H5" s="1">
-        <v>-8.6544952991215635e-06</v>
+        <v>-9.1021127815735888e-06</v>
       </c>
       <c r="I5" s="1">
-        <v>-6.5799288765850334e-06</v>
+        <v>-6.9160059172312177e-06</v>
       </c>
       <c r="J5" s="1">
-        <v>2.2852958638569301e-05</v>
+        <v>2.4385107891430085e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>4.4878858244122343e-05</v>
+        <v>4.7906713973056971e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>4.7167701996976456e-05</v>
+        <v>5.0403189065242552e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>5.1549719409393884e-05</v>
+        <v>5.5021814293801401e-05</v>
       </c>
       <c r="N5" s="1">
-        <v>-1.663898711954644e-07</v>
+        <v>-1.5096416711540308e-07</v>
       </c>
       <c r="O5" s="1">
-        <v>-2.2942380001830508e-06</v>
+        <v>-2.4426349661668029e-06</v>
       </c>
       <c r="P5" s="1">
-        <v>-2.5514086210217328e-06</v>
+        <v>-2.7146725282417185e-06</v>
       </c>
       <c r="Q5" s="1">
-        <v>2.0714775073959332e-07</v>
+        <v>2.0778705016431939e-07</v>
       </c>
       <c r="R5" s="1">
-        <v>-4.3740824761927539e-06</v>
+        <v>-4.683070013901158e-06</v>
       </c>
       <c r="S5" s="1">
-        <v>2.563808435029714e-08</v>
+        <v>2.7271364351666146e-08</v>
       </c>
       <c r="T5" s="1">
-        <v>-2.7753638319107293e-06</v>
+        <v>-2.9907426094821285e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>1.4323137028340943e-06</v>
+        <v>1.5133561768445948e-06</v>
       </c>
       <c r="V5" s="1">
-        <v>-0.00050643826020385001</v>
+        <v>-0.00053510090305155047</v>
       </c>
       <c r="W5" s="1">
-        <v>0.00015054492978484828</v>
+        <v>0.00016054715518794461</v>
       </c>
     </row>
     <row r="6">
@@ -5145,70 +5145,70 @@
         <v>27</v>
       </c>
       <c r="B6" s="1">
-        <v>0.027336816364298924</v>
+        <v>0.028469172731133818</v>
       </c>
       <c r="C6" s="1">
-        <v>-3.360436818405722e-07</v>
+        <v>-3.7282481810847547e-07</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.5035087354437294e-06</v>
+        <v>-5.0668090315422262e-06</v>
       </c>
       <c r="E6" s="1">
-        <v>1.3717856467672172e-07</v>
+        <v>1.4823884054330889e-07</v>
       </c>
       <c r="F6" s="1">
-        <v>0.00028974671161578335</v>
+        <v>0.00030446231301477483</v>
       </c>
       <c r="G6" s="1">
-        <v>0.001080811256420974</v>
+        <v>0.0011374461109619179</v>
       </c>
       <c r="H6" s="1">
-        <v>-6.4864023356591805e-06</v>
+        <v>-6.8159742957801682e-06</v>
       </c>
       <c r="I6" s="1">
-        <v>-2.2421869511660834e-05</v>
+        <v>-2.3589994702019843e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>-6.7416349533931346e-05</v>
+        <v>-7.2417158161974804e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.00014490814886148576</v>
+        <v>-0.00015549052256014589</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.00016478541560917853</v>
+        <v>-0.00017677741851829229</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00016330872044930625</v>
+        <v>-0.0001752811167296952</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.4373476933446708e-06</v>
+        <v>-1.0017276819240149e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>2.1034788979253253e-06</v>
+        <v>2.3296081589620497e-06</v>
       </c>
       <c r="P6" s="1">
-        <v>-1.5483297437031937e-06</v>
+        <v>-1.5090293436640138e-06</v>
       </c>
       <c r="Q6" s="1">
-        <v>2.314120354258204e-06</v>
+        <v>2.4722971044480844e-06</v>
       </c>
       <c r="R6" s="1">
-        <v>2.1150473544687655e-06</v>
+        <v>2.415933402049232e-06</v>
       </c>
       <c r="S6" s="1">
-        <v>-1.715397334683928e-08</v>
+        <v>-1.8558293265011728e-08</v>
       </c>
       <c r="T6" s="1">
-        <v>1.5606146623387442e-05</v>
+        <v>1.6714141832612749e-05</v>
       </c>
       <c r="U6" s="1">
-        <v>-8.8262432999707306e-07</v>
+        <v>-9.7524885560773394e-07</v>
       </c>
       <c r="V6" s="1">
-        <v>0.00011809779953667602</v>
+        <v>0.00013500232608632421</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.0004303779294505138</v>
+        <v>-0.00046228871919541968</v>
       </c>
     </row>
     <row r="7">
@@ -5216,70 +5216,70 @@
         <v>28</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.00081720134106618466</v>
+        <v>-0.00081109475648196273</v>
       </c>
       <c r="C7" s="1">
-        <v>5.72596780673939e-08</v>
+        <v>6.0041350144554233e-08</v>
       </c>
       <c r="D7" s="1">
-        <v>-3.2349271651709307e-07</v>
+        <v>-3.4179128722730129e-07</v>
       </c>
       <c r="E7" s="1">
-        <v>1.9431635005202673e-09</v>
+        <v>2.0627533072503737e-09</v>
       </c>
       <c r="F7" s="1">
-        <v>-8.6544952991215635e-06</v>
+        <v>-9.1021127815735888e-06</v>
       </c>
       <c r="G7" s="1">
-        <v>-6.4864023356591805e-06</v>
+        <v>-6.8159742957801682e-06</v>
       </c>
       <c r="H7" s="1">
-        <v>2.0648134157550635e-07</v>
+        <v>2.1715720213060315e-07</v>
       </c>
       <c r="I7" s="1">
-        <v>1.5972469268649885e-07</v>
+        <v>1.6788988793175622e-07</v>
       </c>
       <c r="J7" s="1">
-        <v>-5.2541192679914334e-07</v>
+        <v>-5.5984545968499657e-07</v>
       </c>
       <c r="K7" s="1">
-        <v>-1.0162192002197664e-06</v>
+        <v>-1.0834165372343429e-06</v>
       </c>
       <c r="L7" s="1">
-        <v>-1.0327568482186059e-06</v>
+        <v>-1.1026667193954332e-06</v>
       </c>
       <c r="M7" s="1">
-        <v>-1.0949702594944283e-06</v>
+        <v>-1.168297484470983e-06</v>
       </c>
       <c r="N7" s="1">
-        <v>-2.6986928807212213e-08</v>
+        <v>-2.887593850160006e-08</v>
       </c>
       <c r="O7" s="1">
-        <v>4.4127182160795488e-08</v>
+        <v>4.7034697960784195e-08</v>
       </c>
       <c r="P7" s="1">
-        <v>3.8305648314895476e-08</v>
+        <v>4.0955358163867021e-08</v>
       </c>
       <c r="Q7" s="1">
-        <v>-8.9451320988791462e-11</v>
+        <v>1.2196807209398252e-10</v>
       </c>
       <c r="R7" s="1">
-        <v>1.6288223690267113e-07</v>
+        <v>1.7297255238901501e-07</v>
       </c>
       <c r="S7" s="1">
-        <v>3.3239530248624334e-10</v>
+        <v>3.4230708707882334e-10</v>
       </c>
       <c r="T7" s="1">
-        <v>5.0381889612308155e-08</v>
+        <v>5.4489139276327301e-08</v>
       </c>
       <c r="U7" s="1">
-        <v>-4.7653173744185951e-08</v>
+        <v>-5.0248347489915991e-08</v>
       </c>
       <c r="V7" s="1">
-        <v>1.1074650930368207e-05</v>
+        <v>1.1698815107867874e-05</v>
       </c>
       <c r="W7" s="1">
-        <v>-3.3633505240804736e-06</v>
+        <v>-3.5832206219967769e-06</v>
       </c>
     </row>
     <row r="8">
@@ -5287,70 +5287,70 @@
         <v>29</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.0028640926986650086</v>
+        <v>-0.0028799709822632307</v>
       </c>
       <c r="C8" s="1">
-        <v>1.2885582860948503e-07</v>
+        <v>1.3567198132440606e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>-6.787524881522505e-08</v>
+        <v>-6.6510065937175413e-08</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.1590458210061321e-09</v>
+        <v>-1.2774618245573641e-09</v>
       </c>
       <c r="F8" s="1">
-        <v>-6.5799288765850334e-06</v>
+        <v>-6.9160059172312177e-06</v>
       </c>
       <c r="G8" s="1">
-        <v>-2.2421869511660834e-05</v>
+        <v>-2.3589994702019843e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>1.5972469268649885e-07</v>
+        <v>1.6788988793175622e-07</v>
       </c>
       <c r="I8" s="1">
-        <v>5.1080297085191474e-07</v>
+        <v>5.3728838915360079e-07</v>
       </c>
       <c r="J8" s="1">
-        <v>6.8121666884890313e-07</v>
+        <v>7.3884206446446971e-07</v>
       </c>
       <c r="K8" s="1">
-        <v>1.5755446475584516e-06</v>
+        <v>1.7029551069214249e-06</v>
       </c>
       <c r="L8" s="1">
-        <v>1.8823616874370457e-06</v>
+        <v>2.031266864033922e-06</v>
       </c>
       <c r="M8" s="1">
-        <v>1.8633373988000331e-06</v>
+        <v>2.0121900541915829e-06</v>
       </c>
       <c r="N8" s="1">
-        <v>1.1228733379932175e-07</v>
+        <v>1.193913745958328e-07</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.2590502197977029e-08</v>
+        <v>-1.4872453095041211e-08</v>
       </c>
       <c r="P8" s="1">
-        <v>1.9481302101165153e-08</v>
+        <v>1.8875739900102231e-08</v>
       </c>
       <c r="Q8" s="1">
-        <v>-7.2141003498394036e-08</v>
+        <v>-7.6386857023494251e-08</v>
       </c>
       <c r="R8" s="1">
-        <v>2.6881361916250879e-08</v>
+        <v>2.6540834408444402e-08</v>
       </c>
       <c r="S8" s="1">
-        <v>2.3750169529830964e-09</v>
+        <v>2.4984688184266099e-09</v>
       </c>
       <c r="T8" s="1">
-        <v>-2.1674460423205684e-07</v>
+        <v>-2.3232083254866523e-07</v>
       </c>
       <c r="U8" s="1">
-        <v>-3.3126276989111385e-08</v>
+        <v>-3.401247329500109e-08</v>
       </c>
       <c r="V8" s="1">
-        <v>2.2420853471717389e-06</v>
+        <v>2.1991471417415414e-06</v>
       </c>
       <c r="W8" s="1">
-        <v>4.5450041182570334e-06</v>
+        <v>4.9233797541817269e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5358,70 +5358,70 @@
         <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>-0.12682867431996114</v>
+        <v>-0.12890127867057147</v>
       </c>
       <c r="C9" s="1">
-        <v>5.45439141752782e-07</v>
+        <v>6.4352786716528285e-07</v>
       </c>
       <c r="D9" s="1">
-        <v>3.2709055480318718e-05</v>
+        <v>3.4903648353731611e-05</v>
       </c>
       <c r="E9" s="1">
-        <v>-3.9488572922500512e-07</v>
+        <v>-4.2136085650465624e-07</v>
       </c>
       <c r="F9" s="1">
-        <v>2.2852958638569301e-05</v>
+        <v>2.4385107891430085e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>-6.7416349533931346e-05</v>
+        <v>-7.2417158161974804e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-5.2541192679914334e-07</v>
+        <v>-5.5984545968499657e-07</v>
       </c>
       <c r="I9" s="1">
-        <v>6.8121666884890313e-07</v>
+        <v>7.3884206446446971e-07</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0015370985970945392</v>
+        <v>0.0016187372596603708</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0015662776354217784</v>
+        <v>0.0016517904604997405</v>
       </c>
       <c r="L9" s="1">
-        <v>0.0016042794076839635</v>
+        <v>0.0016923420743294513</v>
       </c>
       <c r="M9" s="1">
-        <v>0.0016111986078070164</v>
+        <v>0.0016996913345669379</v>
       </c>
       <c r="N9" s="1">
-        <v>9.2986042328685394e-06</v>
+        <v>9.9439735528284158e-06</v>
       </c>
       <c r="O9" s="1">
-        <v>-8.4997406297836351e-06</v>
+        <v>-9.1443056263636462e-06</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.0044284433739983e-05</v>
+        <v>-1.0776850246333151e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>-3.632798489226808e-06</v>
+        <v>-3.8852626957270861e-06</v>
       </c>
       <c r="R9" s="1">
-        <v>-1.2131121602420204e-05</v>
+        <v>-1.3472275346962693e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>-3.1125058306251189e-09</v>
+        <v>-1.2048825684587302e-09</v>
       </c>
       <c r="T9" s="1">
-        <v>-3.0729180899911556e-05</v>
+        <v>-3.2798552953957071e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>7.4441621883989011e-06</v>
+        <v>7.870326971384273e-06</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.0023200130782038619</v>
+        <v>-0.0024563983393637179</v>
       </c>
       <c r="W9" s="1">
-        <v>0.00098395537889925215</v>
+        <v>0.0010494758674410294</v>
       </c>
     </row>
     <row r="10">
@@ -5429,70 +5429,70 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.18597625216344818</v>
+        <v>-0.19019398257806397</v>
       </c>
       <c r="C10" s="1">
-        <v>1.4482514845650772e-06</v>
+        <v>1.6644151539856337e-06</v>
       </c>
       <c r="D10" s="1">
-        <v>6.7662252681921655e-05</v>
+        <v>7.217356742454286e-05</v>
       </c>
       <c r="E10" s="1">
-        <v>-8.1697856204955601e-07</v>
+        <v>-8.7140675479674764e-07</v>
       </c>
       <c r="F10" s="1">
-        <v>4.4878858244122343e-05</v>
+        <v>4.7906713973056971e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>-0.00014490814886148576</v>
+        <v>-0.00015549052256014589</v>
       </c>
       <c r="H10" s="1">
-        <v>-1.0162192002197664e-06</v>
+        <v>-1.0834165372343429e-06</v>
       </c>
       <c r="I10" s="1">
-        <v>1.5755446475584516e-06</v>
+        <v>1.7029551069214249e-06</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0015662776354217784</v>
+        <v>0.0016517904604997405</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0019289438172209873</v>
+        <v>0.0020379241596743623</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0019856627981936509</v>
+        <v>0.0020987547230034605</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0020003199190514027</v>
+        <v>0.0021143124975412982</v>
       </c>
       <c r="N10" s="1">
-        <v>1.7421114537083598e-05</v>
+        <v>1.865397172100909e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-1.9380769725766443e-05</v>
+        <v>-2.0797519565117991e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-2.1100969449017541e-05</v>
+        <v>-2.2624347616005322e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>-7.4343586068787462e-06</v>
+        <v>-7.9499442319760225e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>-2.3546433459851598e-05</v>
+        <v>-2.6210698082882097e-05</v>
       </c>
       <c r="S10" s="1">
-        <v>-1.3170913625806322e-07</v>
+        <v>-1.3409813101910066e-07</v>
       </c>
       <c r="T10" s="1">
-        <v>-6.0635308691845765e-05</v>
+        <v>-6.4739378989936457e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>1.4928499224466714e-05</v>
+        <v>1.5779193002745031e-05</v>
       </c>
       <c r="V10" s="1">
-        <v>-0.0034533272165144999</v>
+        <v>-0.003665101142725162</v>
       </c>
       <c r="W10" s="1">
-        <v>0.0020395056304370841</v>
+        <v>0.0021743840649156559</v>
       </c>
     </row>
     <row r="11">
@@ -5500,70 +5500,70 @@
         <v>32</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.19232358361157023</v>
+        <v>-0.19707306040009301</v>
       </c>
       <c r="C11" s="1">
-        <v>1.2815801798531074e-06</v>
+        <v>1.5067087229564433e-06</v>
       </c>
       <c r="D11" s="1">
-        <v>7.54016541980888e-05</v>
+        <v>8.0439817156148296e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>-9.0812400888249725e-07</v>
+        <v>-9.6878949101364278e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>4.7167701996976456e-05</v>
+        <v>5.0403189065242552e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>-0.00016478541560917853</v>
+        <v>-0.00017677741851829229</v>
       </c>
       <c r="H11" s="1">
-        <v>-1.0327568482186059e-06</v>
+        <v>-1.1026667193954332e-06</v>
       </c>
       <c r="I11" s="1">
-        <v>1.8823616874370457e-06</v>
+        <v>2.031266864033922e-06</v>
       </c>
       <c r="J11" s="1">
-        <v>0.0016042794076839635</v>
+        <v>0.0016923420743294513</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0019856627981936509</v>
+        <v>0.0020987547230034605</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0020858760186119626</v>
+        <v>0.0022054712678748773</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0020965943724471263</v>
+        <v>0.0022169054003842092</v>
       </c>
       <c r="N11" s="1">
-        <v>1.938655486933362e-05</v>
+        <v>2.0761938113873943e-05</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.1257406307672501e-05</v>
+        <v>-2.282253271565392e-05</v>
       </c>
       <c r="P11" s="1">
-        <v>-2.2987766814459635e-05</v>
+        <v>-2.4662120277920296e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-7.4080580122130805e-06</v>
+        <v>-7.938563931667325e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>-2.5533167378453458e-05</v>
+        <v>-2.8475284571296805e-05</v>
       </c>
       <c r="S11" s="1">
-        <v>-2.0578065663118315e-07</v>
+        <v>-2.1148388838450431e-07</v>
       </c>
       <c r="T11" s="1">
-        <v>-6.7838067575316406e-05</v>
+        <v>-7.2435166932444464e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>1.6476605513574525e-05</v>
+        <v>1.7418047478311005e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.003714004004424125</v>
+        <v>-0.003943425325609845</v>
       </c>
       <c r="W11" s="1">
-        <v>0.0022851689451956186</v>
+        <v>0.0024364298419346812</v>
       </c>
     </row>
     <row r="12">
@@ -5571,70 +5571,70 @@
         <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>-0.19348663814856684</v>
+        <v>-0.19831327640379004</v>
       </c>
       <c r="C12" s="1">
-        <v>1.0122393671551963e-06</v>
+        <v>1.2269285345081865e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>7.804515926095962e-05</v>
+        <v>8.3235382071258934e-05</v>
       </c>
       <c r="E12" s="1">
-        <v>-9.356514221247226e-07</v>
+        <v>-9.9792581574346703e-07</v>
       </c>
       <c r="F12" s="1">
-        <v>5.1549719409393884e-05</v>
+        <v>5.5021814293801401e-05</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00016330872044930625</v>
+        <v>-0.0001752811167296952</v>
       </c>
       <c r="H12" s="1">
-        <v>-1.0949702594944283e-06</v>
+        <v>-1.168297484470983e-06</v>
       </c>
       <c r="I12" s="1">
-        <v>1.8633373988000331e-06</v>
+        <v>2.0121900541915829e-06</v>
       </c>
       <c r="J12" s="1">
-        <v>0.0016111986078070164</v>
+        <v>0.0016996913345669379</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0020003199190514027</v>
+        <v>0.0021143124975412982</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0020965943724471263</v>
+        <v>0.0022169054003842092</v>
       </c>
       <c r="M12" s="1">
-        <v>0.002140985465172517</v>
+        <v>0.0022637512754060799</v>
       </c>
       <c r="N12" s="1">
-        <v>1.9854748068220714e-05</v>
+        <v>2.1260341403668627e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>-2.1458495492841612e-05</v>
+        <v>-2.3041492570524996e-05</v>
       </c>
       <c r="P12" s="1">
-        <v>-2.3613286354808168e-05</v>
+        <v>-2.5327789563786683e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.2447414872821684e-06</v>
+        <v>-7.7690675595431341e-06</v>
       </c>
       <c r="R12" s="1">
-        <v>-2.6494759600030859e-05</v>
+        <v>-2.9525704251752482e-05</v>
       </c>
       <c r="S12" s="1">
-        <v>-2.0345329743264723e-07</v>
+        <v>-2.0891396038138437e-07</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.9119289664842202e-05</v>
+        <v>-7.3798377201361631e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>1.6922054704051905e-05</v>
+        <v>1.7886488277938537e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>-0.0037972162758293281</v>
+        <v>-0.0040314533905587285</v>
       </c>
       <c r="W12" s="1">
-        <v>0.0023300807872463905</v>
+        <v>0.0024841135543013735</v>
       </c>
     </row>
     <row r="13">
@@ -5642,70 +5642,70 @@
         <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>-0.0055909952398109234</v>
+        <v>-0.0057400804857052849</v>
       </c>
       <c r="C13" s="1">
-        <v>2.5149956979487623e-07</v>
+        <v>2.6975660811602586e-07</v>
       </c>
       <c r="D13" s="1">
-        <v>1.7596591154108668e-06</v>
+        <v>1.8857376836457368e-06</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.1759824142311797e-08</v>
+        <v>-2.3308084781546249e-08</v>
       </c>
       <c r="F13" s="1">
-        <v>-1.663898711954644e-07</v>
+        <v>-1.5096416711540308e-07</v>
       </c>
       <c r="G13" s="1">
-        <v>-9.4373476933446708e-06</v>
+        <v>-1.0017276819240149e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>-2.6986928807212213e-08</v>
+        <v>-2.887593850160006e-08</v>
       </c>
       <c r="I13" s="1">
-        <v>1.1228733379932175e-07</v>
+        <v>1.193913745958328e-07</v>
       </c>
       <c r="J13" s="1">
-        <v>9.2986042328685394e-06</v>
+        <v>9.9439735528284158e-06</v>
       </c>
       <c r="K13" s="1">
-        <v>1.7421114537083598e-05</v>
+        <v>1.865397172100909e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>1.938655486933362e-05</v>
+        <v>2.0761938113873943e-05</v>
       </c>
       <c r="M13" s="1">
-        <v>1.9854748068220714e-05</v>
+        <v>2.1260341403668627e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>5.5212904368207931e-05</v>
+        <v>5.8073100760595842e-05</v>
       </c>
       <c r="O13" s="1">
-        <v>2.6223557869535353e-05</v>
+        <v>2.7562483597335142e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>2.6334541172359565e-05</v>
+        <v>2.767906346485368e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>2.6607845999418355e-05</v>
+        <v>2.7976637391762574e-05</v>
       </c>
       <c r="R13" s="1">
-        <v>6.0612879037040311e-07</v>
+        <v>5.8151070737602963e-07</v>
       </c>
       <c r="S13" s="1">
-        <v>-5.0326543723558223e-08</v>
+        <v>-5.2835539312985675e-08</v>
       </c>
       <c r="T13" s="1">
-        <v>-2.0484027777916082e-06</v>
+        <v>-2.1876132228492987e-06</v>
       </c>
       <c r="U13" s="1">
-        <v>-1.4131059656954673e-07</v>
+        <v>-1.4488900205083447e-07</v>
       </c>
       <c r="V13" s="1">
-        <v>-7.7266189159671815e-05</v>
+        <v>-8.2415342768654866e-05</v>
       </c>
       <c r="W13" s="1">
-        <v>5.2455898638150565e-05</v>
+        <v>5.6202632542799147e-05</v>
       </c>
     </row>
     <row r="14">
@@ -5713,70 +5713,70 @@
         <v>35</v>
       </c>
       <c r="B14" s="1">
-        <v>0.019781822803334459</v>
+        <v>0.019954242457910623</v>
       </c>
       <c r="C14" s="1">
-        <v>-7.2497937398557479e-07</v>
+        <v>-7.6810461532286462e-07</v>
       </c>
       <c r="D14" s="1">
-        <v>-2.1433693691763144e-06</v>
+        <v>-2.2981269626910055e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>2.528213581687567e-08</v>
+        <v>2.7119100347439834e-08</v>
       </c>
       <c r="F14" s="1">
-        <v>-2.2942380001830508e-06</v>
+        <v>-2.4426349661668029e-06</v>
       </c>
       <c r="G14" s="1">
-        <v>2.1034788979253253e-06</v>
+        <v>2.3296081589620497e-06</v>
       </c>
       <c r="H14" s="1">
-        <v>4.4127182160795488e-08</v>
+        <v>4.7034697960784195e-08</v>
       </c>
       <c r="I14" s="1">
-        <v>-1.2590502197977029e-08</v>
+        <v>-1.4872453095041211e-08</v>
       </c>
       <c r="J14" s="1">
-        <v>-8.4997406297836351e-06</v>
+        <v>-9.1443056263636462e-06</v>
       </c>
       <c r="K14" s="1">
-        <v>-1.9380769725766443e-05</v>
+        <v>-2.0797519565117991e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-2.1257406307672501e-05</v>
+        <v>-2.282253271565392e-05</v>
       </c>
       <c r="M14" s="1">
-        <v>-2.1458495492841612e-05</v>
+        <v>-2.3041492570524996e-05</v>
       </c>
       <c r="N14" s="1">
-        <v>2.6223557869535353e-05</v>
+        <v>2.7562483597335142e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>7.2672953178037935e-05</v>
+        <v>7.643875666128093e-05</v>
       </c>
       <c r="P14" s="1">
-        <v>2.7369406509486224e-05</v>
+        <v>2.8798553024842586e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>2.6855445766981229e-05</v>
+        <v>2.8245858025984706e-05</v>
       </c>
       <c r="R14" s="1">
-        <v>2.3302832495415866e-06</v>
+        <v>2.5063139073703615e-06</v>
       </c>
       <c r="S14" s="1">
-        <v>-2.8859692300840721e-08</v>
+        <v>-3.0433746005477112e-08</v>
       </c>
       <c r="T14" s="1">
-        <v>1.0698789766227658e-06</v>
+        <v>1.1666701638874513e-06</v>
       </c>
       <c r="U14" s="1">
-        <v>-1.2768029009950127e-06</v>
+        <v>-1.3478813124456836e-06</v>
       </c>
       <c r="V14" s="1">
-        <v>4.7201468949169018e-05</v>
+        <v>5.1087345135945194e-05</v>
       </c>
       <c r="W14" s="1">
-        <v>-6.3894914669658856e-05</v>
+        <v>-6.849289772809021e-05</v>
       </c>
     </row>
     <row r="15">
@@ -5784,70 +5784,70 @@
         <v>36</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.00024628104430081936</v>
+        <v>-7.5148221523524153e-05</v>
       </c>
       <c r="C15" s="1">
-        <v>1.1035047931850824e-08</v>
+        <v>6.4127094210992326e-09</v>
       </c>
       <c r="D15" s="1">
-        <v>-2.1303960959452357e-06</v>
+        <v>-2.286300209330839e-06</v>
       </c>
       <c r="E15" s="1">
-        <v>2.5148081304804029e-08</v>
+        <v>2.6999929739189855e-08</v>
       </c>
       <c r="F15" s="1">
-        <v>-2.5514086210217328e-06</v>
+        <v>-2.7146725282417185e-06</v>
       </c>
       <c r="G15" s="1">
-        <v>-1.5483297437031937e-06</v>
+        <v>-1.5090293436640138e-06</v>
       </c>
       <c r="H15" s="1">
-        <v>3.8305648314895476e-08</v>
+        <v>4.0955358163867021e-08</v>
       </c>
       <c r="I15" s="1">
-        <v>1.9481302101165153e-08</v>
+        <v>1.8875739900102231e-08</v>
       </c>
       <c r="J15" s="1">
-        <v>-1.0044284433739983e-05</v>
+        <v>-1.0776850246333151e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>-2.1100969449017541e-05</v>
+        <v>-2.2624347616005322e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-2.2987766814459635e-05</v>
+        <v>-2.4662120277920296e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>-2.3613286354808168e-05</v>
+        <v>-2.5327789563786683e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>2.6334541172359565e-05</v>
+        <v>2.767906346485368e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>2.7369406509486224e-05</v>
+        <v>2.8798553024842586e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>5.470732688079102e-05</v>
+        <v>5.7546985861013194e-05</v>
       </c>
       <c r="Q15" s="1">
-        <v>2.6949070985318957e-05</v>
+        <v>2.8344433297377889e-05</v>
       </c>
       <c r="R15" s="1">
-        <v>2.4856350733548306e-06</v>
+        <v>2.6680643232826551e-06</v>
       </c>
       <c r="S15" s="1">
-        <v>-4.5359042264877324e-08</v>
+        <v>-4.775991927130001e-08</v>
       </c>
       <c r="T15" s="1">
-        <v>1.5822250471813385e-06</v>
+        <v>1.7066718892343832e-06</v>
       </c>
       <c r="U15" s="1">
-        <v>-3.4832985096298883e-07</v>
+        <v>-3.7238547102172369e-07</v>
       </c>
       <c r="V15" s="1">
-        <v>4.9554757008236024e-05</v>
+        <v>5.3618551075396687e-05</v>
       </c>
       <c r="W15" s="1">
-        <v>-6.10072983171746e-05</v>
+        <v>-6.5511884890576372e-05</v>
       </c>
     </row>
     <row r="16">
@@ -5855,70 +5855,70 @@
         <v>37</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.019636755600888296</v>
+        <v>-0.019588073301967164</v>
       </c>
       <c r="C16" s="1">
-        <v>7.5953216481798214e-07</v>
+        <v>7.9739640972672343e-07</v>
       </c>
       <c r="D16" s="1">
-        <v>-6.7038047163706636e-07</v>
+        <v>-7.1901973696885623e-07</v>
       </c>
       <c r="E16" s="1">
-        <v>7.8880233373053858e-09</v>
+        <v>8.4642200431817127e-09</v>
       </c>
       <c r="F16" s="1">
-        <v>2.0714775073959332e-07</v>
+        <v>2.0778705016431939e-07</v>
       </c>
       <c r="G16" s="1">
-        <v>2.314120354258204e-06</v>
+        <v>2.4722971044480844e-06</v>
       </c>
       <c r="H16" s="1">
-        <v>-8.9451320988791462e-11</v>
+        <v>1.2196807209398252e-10</v>
       </c>
       <c r="I16" s="1">
-        <v>-7.2141003498394036e-08</v>
+        <v>-7.6386857023494251e-08</v>
       </c>
       <c r="J16" s="1">
-        <v>-3.632798489226808e-06</v>
+        <v>-3.8852626957270861e-06</v>
       </c>
       <c r="K16" s="1">
-        <v>-7.4343586068787462e-06</v>
+        <v>-7.9499442319760225e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>-7.4080580122130805e-06</v>
+        <v>-7.938563931667325e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>-7.2447414872821684e-06</v>
+        <v>-7.7690675595431341e-06</v>
       </c>
       <c r="N16" s="1">
-        <v>2.6607845999418355e-05</v>
+        <v>2.7976637391762574e-05</v>
       </c>
       <c r="O16" s="1">
-        <v>2.6855445766981229e-05</v>
+        <v>2.8245858025984706e-05</v>
       </c>
       <c r="P16" s="1">
-        <v>2.6949070985318957e-05</v>
+        <v>2.8344433297377889e-05</v>
       </c>
       <c r="Q16" s="1">
-        <v>3.7829722435506775e-05</v>
+        <v>3.9782902195410352e-05</v>
       </c>
       <c r="R16" s="1">
-        <v>9.0545308518893389e-07</v>
+        <v>9.6284088090673858e-07</v>
       </c>
       <c r="S16" s="1">
-        <v>-3.9930400098641225e-08</v>
+        <v>-4.19911268933672e-08</v>
       </c>
       <c r="T16" s="1">
-        <v>-9.2283978193022047e-08</v>
+        <v>-8.4325166713421668e-08</v>
       </c>
       <c r="U16" s="1">
-        <v>-8.3524859504991147e-07</v>
+        <v>-8.8063661348011312e-07</v>
       </c>
       <c r="V16" s="1">
-        <v>-1.0225508076369443e-06</v>
+        <v>-6.1785383036175683e-07</v>
       </c>
       <c r="W16" s="1">
-        <v>-1.789162308675783e-05</v>
+        <v>-1.9227088189805177e-05</v>
       </c>
     </row>
     <row r="17">
@@ -5926,70 +5926,70 @@
         <v>38</v>
       </c>
       <c r="B17" s="1">
-        <v>0.089313046402185431</v>
+        <v>0.089901669734390802</v>
       </c>
       <c r="C17" s="1">
-        <v>1.271963702109067e-06</v>
+        <v>1.3088954429141434e-06</v>
       </c>
       <c r="D17" s="1">
-        <v>-1.4164345413678755e-06</v>
+        <v>-1.6346024049031838e-06</v>
       </c>
       <c r="E17" s="1">
-        <v>1.5472056656198025e-08</v>
+        <v>1.8033162584495335e-08</v>
       </c>
       <c r="F17" s="1">
-        <v>-4.3740824761927539e-06</v>
+        <v>-4.683070013901158e-06</v>
       </c>
       <c r="G17" s="1">
-        <v>2.1150473544687655e-06</v>
+        <v>2.415933402049232e-06</v>
       </c>
       <c r="H17" s="1">
-        <v>1.6288223690267113e-07</v>
+        <v>1.7297255238901501e-07</v>
       </c>
       <c r="I17" s="1">
-        <v>2.6881361916250879e-08</v>
+        <v>2.6540834408444402e-08</v>
       </c>
       <c r="J17" s="1">
-        <v>-1.2131121602420204e-05</v>
+        <v>-1.3472275346962693e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>-2.3546433459851598e-05</v>
+        <v>-2.6210698082882097e-05</v>
       </c>
       <c r="L17" s="1">
-        <v>-2.5533167378453458e-05</v>
+        <v>-2.8475284571296805e-05</v>
       </c>
       <c r="M17" s="1">
-        <v>-2.6494759600030859e-05</v>
+        <v>-2.9525704251752482e-05</v>
       </c>
       <c r="N17" s="1">
-        <v>6.0612879037040311e-07</v>
+        <v>5.8151070737602963e-07</v>
       </c>
       <c r="O17" s="1">
-        <v>2.3302832495415866e-06</v>
+        <v>2.5063139073703615e-06</v>
       </c>
       <c r="P17" s="1">
-        <v>2.4856350733548306e-06</v>
+        <v>2.6680643232826551e-06</v>
       </c>
       <c r="Q17" s="1">
-        <v>9.0545308518893389e-07</v>
+        <v>9.6284088090673858e-07</v>
       </c>
       <c r="R17" s="1">
-        <v>0.00015670511443059327</v>
+        <v>0.00016504695200294408</v>
       </c>
       <c r="S17" s="1">
-        <v>7.7410704150196652e-08</v>
+        <v>8.1254028992393744e-08</v>
       </c>
       <c r="T17" s="1">
-        <v>1.5134363629546563e-06</v>
+        <v>1.7394340923994402e-06</v>
       </c>
       <c r="U17" s="1">
-        <v>-1.3500394806490287e-06</v>
+        <v>-1.4351204350959069e-06</v>
       </c>
       <c r="V17" s="1">
-        <v>4.8216145251824444e-05</v>
+        <v>5.5554652863268564e-05</v>
       </c>
       <c r="W17" s="1">
-        <v>-8.8649223544190928e-05</v>
+        <v>-9.7718760005704287e-05</v>
       </c>
     </row>
     <row r="18">
@@ -5997,70 +5997,70 @@
         <v>39</v>
       </c>
       <c r="B18" s="1">
-        <v>0.00092136950778537268</v>
+        <v>0.00092058704806596077</v>
       </c>
       <c r="C18" s="1">
-        <v>-4.6056211331114222e-08</v>
+        <v>-4.8411034740049847e-08</v>
       </c>
       <c r="D18" s="1">
-        <v>-1.7519818906491076e-08</v>
+        <v>-1.7989996463168776e-08</v>
       </c>
       <c r="E18" s="1">
-        <v>1.7314233839552872e-10</v>
+        <v>1.7680560582008252e-10</v>
       </c>
       <c r="F18" s="1">
-        <v>2.563808435029714e-08</v>
+        <v>2.7271364351666146e-08</v>
       </c>
       <c r="G18" s="1">
-        <v>-1.715397334683928e-08</v>
+        <v>-1.8558293265011728e-08</v>
       </c>
       <c r="H18" s="1">
-        <v>3.3239530248624334e-10</v>
+        <v>3.4230708707882334e-10</v>
       </c>
       <c r="I18" s="1">
-        <v>2.3750169529830964e-09</v>
+        <v>2.4984688184266099e-09</v>
       </c>
       <c r="J18" s="1">
-        <v>-3.1125058306251189e-09</v>
+        <v>-1.2048825684587302e-09</v>
       </c>
       <c r="K18" s="1">
-        <v>-1.3170913625806322e-07</v>
+        <v>-1.3409813101910066e-07</v>
       </c>
       <c r="L18" s="1">
-        <v>-2.0578065663118315e-07</v>
+        <v>-2.1148388838450431e-07</v>
       </c>
       <c r="M18" s="1">
-        <v>-2.0345329743264723e-07</v>
+        <v>-2.0891396038138437e-07</v>
       </c>
       <c r="N18" s="1">
-        <v>-5.0326543723558223e-08</v>
+        <v>-5.2835539312985675e-08</v>
       </c>
       <c r="O18" s="1">
-        <v>-2.8859692300840721e-08</v>
+        <v>-3.0433746005477112e-08</v>
       </c>
       <c r="P18" s="1">
-        <v>-4.5359042264877324e-08</v>
+        <v>-4.775991927130001e-08</v>
       </c>
       <c r="Q18" s="1">
-        <v>-3.9930400098641225e-08</v>
+        <v>-4.19911268933672e-08</v>
       </c>
       <c r="R18" s="1">
-        <v>7.7410704150196652e-08</v>
+        <v>8.1254028992393744e-08</v>
       </c>
       <c r="S18" s="1">
-        <v>2.624220070062028e-08</v>
+        <v>2.7589732321808028e-08</v>
       </c>
       <c r="T18" s="1">
-        <v>-3.7672121204795223e-07</v>
+        <v>-3.9649633260905085e-07</v>
       </c>
       <c r="U18" s="1">
-        <v>-4.823175081076111e-07</v>
+        <v>-5.0702305840272274e-07</v>
       </c>
       <c r="V18" s="1">
-        <v>-2.0941076945431973e-06</v>
+        <v>-2.2158947023988059e-06</v>
       </c>
       <c r="W18" s="1">
-        <v>-6.2047212236389585e-07</v>
+        <v>-6.3890218419828884e-07</v>
       </c>
     </row>
     <row r="19">
@@ -6068,70 +6068,70 @@
         <v>40</v>
       </c>
       <c r="B19" s="1">
-        <v>0.0062245012297201712</v>
+        <v>0.0066443195899996334</v>
       </c>
       <c r="C19" s="1">
-        <v>-7.6555364133873366e-07</v>
+        <v>-8.1918500223259498e-07</v>
       </c>
       <c r="D19" s="1">
-        <v>-6.1920262790011074e-06</v>
+        <v>-6.6158182870882466e-06</v>
       </c>
       <c r="E19" s="1">
-        <v>7.5454734888846687e-08</v>
+        <v>8.0604143339492566e-08</v>
       </c>
       <c r="F19" s="1">
-        <v>-2.7753638319107293e-06</v>
+        <v>-2.9907426094821285e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>1.5606146623387442e-05</v>
+        <v>1.6714141832612749e-05</v>
       </c>
       <c r="H19" s="1">
-        <v>5.0381889612308155e-08</v>
+        <v>5.4489139276327301e-08</v>
       </c>
       <c r="I19" s="1">
-        <v>-2.1674460423205684e-07</v>
+        <v>-2.3232083254866523e-07</v>
       </c>
       <c r="J19" s="1">
-        <v>-3.0729180899911556e-05</v>
+        <v>-3.2798552953957071e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>-6.0635308691845765e-05</v>
+        <v>-6.4739378989936457e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>-6.7838067575316406e-05</v>
+        <v>-7.2435166932444464e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>-6.9119289664842202e-05</v>
+        <v>-7.3798377201361631e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>-2.0484027777916082e-06</v>
+        <v>-2.1876132228492987e-06</v>
       </c>
       <c r="O19" s="1">
-        <v>1.0698789766227658e-06</v>
+        <v>1.1666701638874513e-06</v>
       </c>
       <c r="P19" s="1">
-        <v>1.5822250471813385e-06</v>
+        <v>1.7066718892343832e-06</v>
       </c>
       <c r="Q19" s="1">
-        <v>-9.2283978193022047e-08</v>
+        <v>-8.4325166713421668e-08</v>
       </c>
       <c r="R19" s="1">
-        <v>1.5134363629546563e-06</v>
+        <v>1.7394340923994402e-06</v>
       </c>
       <c r="S19" s="1">
-        <v>-3.7672121204795223e-07</v>
+        <v>-3.9649633260905085e-07</v>
       </c>
       <c r="T19" s="1">
-        <v>8.6456088631339234e-05</v>
+        <v>9.1015464197251745e-05</v>
       </c>
       <c r="U19" s="1">
-        <v>1.1219996551260862e-05</v>
+        <v>1.1788795829061196e-05</v>
       </c>
       <c r="V19" s="1">
-        <v>0.0002391492982519858</v>
+        <v>0.00025491966820742271</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.00018580069181388934</v>
+        <v>-0.00019843897999928376</v>
       </c>
     </row>
     <row r="20">
@@ -6139,70 +6139,70 @@
         <v>41</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.016346296665950819</v>
+        <v>-0.01639911443915739</v>
       </c>
       <c r="C20" s="1">
-        <v>-1.4418322794137973e-07</v>
+        <v>-1.4994208914397028e-07</v>
       </c>
       <c r="D20" s="1">
-        <v>1.5354376099694776e-06</v>
+        <v>1.6242005607187921e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.8035694006008437e-08</v>
+        <v>-1.9079819094584789e-08</v>
       </c>
       <c r="F20" s="1">
-        <v>1.4323137028340943e-06</v>
+        <v>1.5133561768445948e-06</v>
       </c>
       <c r="G20" s="1">
-        <v>-8.8262432999707306e-07</v>
+        <v>-9.7524885560773394e-07</v>
       </c>
       <c r="H20" s="1">
-        <v>-4.7653173744185951e-08</v>
+        <v>-5.0248347489915991e-08</v>
       </c>
       <c r="I20" s="1">
-        <v>-3.3126276989111385e-08</v>
+        <v>-3.401247329500109e-08</v>
       </c>
       <c r="J20" s="1">
-        <v>7.4441621883989011e-06</v>
+        <v>7.870326971384273e-06</v>
       </c>
       <c r="K20" s="1">
-        <v>1.4928499224466714e-05</v>
+        <v>1.5779193002745031e-05</v>
       </c>
       <c r="L20" s="1">
-        <v>1.6476605513574525e-05</v>
+        <v>1.7418047478311005e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>1.6922054704051905e-05</v>
+        <v>1.7886488277938537e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-1.4131059656954673e-07</v>
+        <v>-1.4488900205083447e-07</v>
       </c>
       <c r="O20" s="1">
-        <v>-1.2768029009950127e-06</v>
+        <v>-1.3478813124456836e-06</v>
       </c>
       <c r="P20" s="1">
-        <v>-3.4832985096298883e-07</v>
+        <v>-3.7238547102172369e-07</v>
       </c>
       <c r="Q20" s="1">
-        <v>-8.3524859504991147e-07</v>
+        <v>-8.8063661348011312e-07</v>
       </c>
       <c r="R20" s="1">
-        <v>-1.3500394806490287e-06</v>
+        <v>-1.4351204350959069e-06</v>
       </c>
       <c r="S20" s="1">
-        <v>-4.823175081076111e-07</v>
+        <v>-5.0702305840272274e-07</v>
       </c>
       <c r="T20" s="1">
-        <v>1.1219996551260862e-05</v>
+        <v>1.1788795829061196e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>8.8873173955185259e-05</v>
+        <v>9.3456576834488088e-05</v>
       </c>
       <c r="V20" s="1">
-        <v>-3.3628496405687935e-06</v>
+        <v>-3.8577669363485219e-06</v>
       </c>
       <c r="W20" s="1">
-        <v>4.653303613052025e-05</v>
+        <v>4.9189926395625467e-05</v>
       </c>
     </row>
     <row r="21">
@@ -6210,70 +6210,70 @@
         <v>42</v>
       </c>
       <c r="B21" s="1">
-        <v>0.60592151567142871</v>
+        <v>0.62051974585228942</v>
       </c>
       <c r="C21" s="1">
-        <v>-7.7439097670995628e-06</v>
+        <v>-8.6213184368799659e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>-0.00027068070388926749</v>
+        <v>-0.00028826253877510684</v>
       </c>
       <c r="E21" s="1">
-        <v>3.1562671385628023e-06</v>
+        <v>3.3626274142740523e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.00050643826020385001</v>
+        <v>-0.00053510090305155047</v>
       </c>
       <c r="G21" s="1">
-        <v>0.00011809779953667602</v>
+        <v>0.00013500232608632421</v>
       </c>
       <c r="H21" s="1">
-        <v>1.1074650930368207e-05</v>
+        <v>1.1698815107867874e-05</v>
       </c>
       <c r="I21" s="1">
-        <v>2.2420853471717389e-06</v>
+        <v>2.1991471417415414e-06</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.0023200130782038619</v>
+        <v>-0.0024563983393637179</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.0034533272165144999</v>
+        <v>-0.003665101142725162</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.003714004004424125</v>
+        <v>-0.003943425325609845</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.0037972162758293281</v>
+        <v>-0.0040314533905587285</v>
       </c>
       <c r="N21" s="1">
-        <v>-7.7266189159671815e-05</v>
+        <v>-8.2415342768654866e-05</v>
       </c>
       <c r="O21" s="1">
-        <v>4.7201468949169018e-05</v>
+        <v>5.1087345135945194e-05</v>
       </c>
       <c r="P21" s="1">
-        <v>4.9554757008236024e-05</v>
+        <v>5.3618551075396687e-05</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.0225508076369443e-06</v>
+        <v>-6.1785383036175683e-07</v>
       </c>
       <c r="R21" s="1">
-        <v>4.8216145251824444e-05</v>
+        <v>5.5554652863268564e-05</v>
       </c>
       <c r="S21" s="1">
-        <v>-2.0941076945431973e-06</v>
+        <v>-2.2158947023988059e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>0.0002391492982519858</v>
+        <v>0.00025491966820742271</v>
       </c>
       <c r="U21" s="1">
-        <v>-3.3628496405687935e-06</v>
+        <v>-3.8577669363485219e-06</v>
       </c>
       <c r="V21" s="1">
-        <v>0.010014188860887818</v>
+        <v>0.010649810277281502</v>
       </c>
       <c r="W21" s="1">
-        <v>-0.0068633092219344445</v>
+        <v>-0.0073226254993461939</v>
       </c>
     </row>
     <row r="22">
@@ -6281,70 +6281,70 @@
         <v>43</v>
       </c>
       <c r="B22" s="1">
-        <v>-0.52623779443114893</v>
+        <v>-0.53964250587835028</v>
       </c>
       <c r="C22" s="1">
-        <v>9.5290420813499604e-06</v>
+        <v>1.0462758516736962e-05</v>
       </c>
       <c r="D22" s="1">
-        <v>0.000211687281128268</v>
+        <v>0.00022580335629701525</v>
       </c>
       <c r="E22" s="1">
-        <v>-2.5550678443893168e-06</v>
+        <v>-2.7253284330028936e-06</v>
       </c>
       <c r="F22" s="1">
-        <v>0.00015054492978484828</v>
+        <v>0.00016054715518794461</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.0004303779294505138</v>
+        <v>-0.00046228871919541968</v>
       </c>
       <c r="H22" s="1">
-        <v>-3.3633505240804736e-06</v>
+        <v>-3.5832206219967769e-06</v>
       </c>
       <c r="I22" s="1">
-        <v>4.5450041182570334e-06</v>
+        <v>4.9233797541817269e-06</v>
       </c>
       <c r="J22" s="1">
-        <v>0.00098395537889925215</v>
+        <v>0.0010494758674410294</v>
       </c>
       <c r="K22" s="1">
-        <v>0.0020395056304370841</v>
+        <v>0.0021743840649156559</v>
       </c>
       <c r="L22" s="1">
-        <v>0.0022851689451956186</v>
+        <v>0.0024364298419346812</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0023300807872463905</v>
+        <v>0.0024841135543013735</v>
       </c>
       <c r="N22" s="1">
-        <v>5.2455898638150565e-05</v>
+        <v>5.6202632542799147e-05</v>
       </c>
       <c r="O22" s="1">
-        <v>-6.3894914669658856e-05</v>
+        <v>-6.849289772809021e-05</v>
       </c>
       <c r="P22" s="1">
-        <v>-6.10072983171746e-05</v>
+        <v>-6.5511884890576372e-05</v>
       </c>
       <c r="Q22" s="1">
-        <v>-1.789162308675783e-05</v>
+        <v>-1.9227088189805177e-05</v>
       </c>
       <c r="R22" s="1">
-        <v>-8.8649223544190928e-05</v>
+        <v>-9.7718760005704287e-05</v>
       </c>
       <c r="S22" s="1">
-        <v>-6.2047212236389585e-07</v>
+        <v>-6.3890218419828884e-07</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.00018580069181388934</v>
+        <v>-0.00019843897999928376</v>
       </c>
       <c r="U22" s="1">
-        <v>4.653303613052025e-05</v>
+        <v>4.9189926395625467e-05</v>
       </c>
       <c r="V22" s="1">
-        <v>-0.0068633092219344445</v>
+        <v>-0.0073226254993461939</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0063438279733214363</v>
+        <v>0.0067639432951772018</v>
       </c>
     </row>
   </sheetData>
